--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244B2BD6-D252-4662-8407-66AA86871E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4DD696-0F97-4B0F-8C6F-1C8618104A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13932" yWindow="0" windowWidth="9204" windowHeight="12336" tabRatio="599" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1028">
   <si>
     <t>id</t>
   </si>
@@ -426,9 +426,6 @@
     <t>迁入宝马山：永久校园落成</t>
   </si>
   <si>
-    <t>1985年，楼高十二层的教学大楼落成，树仁正式迁入宝马山现址，建立支撑教学、行政与学生生活的永久校园。</t>
-  </si>
-  <si>
     <t>B08</t>
   </si>
   <si>
@@ -441,15 +438,9 @@
     <t>新校舍開幕：校園發展進入穩定階段</t>
   </si>
   <si>
-    <t xml:space="preserve">1986年，樹仁新校舍正式啟用，標誌學院由草創時期的資源緊張，走向較穩定的校園發展階段。 </t>
-  </si>
-  <si>
     <t>新校舍开幕：校园发展进入稳定阶段</t>
   </si>
   <si>
-    <t>1986年，树仁新校舍正式启用，标志学院由草创时期的资源紧张，走向较稳定的校园发展阶段。</t>
-  </si>
-  <si>
     <t>T15</t>
   </si>
   <si>
@@ -465,7 +456,7 @@
     <t xml:space="preserve">1987年，樹仁與北京大學合辦法律本科學士學位課程，成為學院拓展內地學術合作的重要里程碑。 </t>
   </si>
   <si>
-    <t>与北京大学合作：拓展内地学术连系</t>
+    <t>与北京大学合作：拓展内地学术联系</t>
   </si>
   <si>
     <r>
@@ -494,15 +485,9 @@
     <t>再度守護四年制教育</t>
   </si>
   <si>
-    <t>1988年，面對香港高等教育制度的新一輪調整，樹仁再次堅持四年制教育，重申大學教育不應只以效率與財政安排衡量</t>
-  </si>
-  <si>
     <t>再度守护四年制教育</t>
   </si>
   <si>
-    <t>1988年，面对香港高等教育制度的新一轮调整，树仁再次坚持四年制教育，重申大学教育不应只以效率与财政安排衡量</t>
-  </si>
-  <si>
     <t>B09</t>
   </si>
   <si>
@@ -524,9 +509,6 @@
     <t>学生请愿与四年制原则的延续</t>
   </si>
   <si>
-    <t>1990年前后，学生争取政府资助的行动反映私立专上教育的学费压力与公平问题，而树仁仍以维持四年制教育作为接受资助的前提。</t>
-  </si>
-  <si>
     <t>B09, B10</t>
   </si>
   <si>
@@ -542,15 +524,9 @@
     <t xml:space="preserve">圖書館綜合大樓落成：支援學術發展 </t>
   </si>
   <si>
-    <t>1995年，樓高十九層的圖書館綜合大樓落成，為圖書館、電腦中心、研究中心及學生學習空間提供重要支援</t>
-  </si>
-  <si>
     <t>图书馆综合大楼落成：支援学术发展</t>
   </si>
   <si>
-    <t>1995年，楼高十九层的图书馆综合大楼落成，为图书馆、计算机中心、研究中心及学生学习空间提供重要支持</t>
-  </si>
-  <si>
     <t>B11</t>
   </si>
   <si>
@@ -623,13 +599,13 @@
     <t>首批榮譽學士課程通過評審</t>
   </si>
   <si>
-    <t>2001年，中國語言文學、新聞與傳播及會計三個課程率先通過評審，標誌樹仁正式走向學位頒授院校</t>
+    <t>2001年，中國語言文學、新聞與傳播及會計三個課程率先通過評審，標誌樹仁正式走向學位頒授院校。</t>
   </si>
   <si>
     <t>首批荣誉学士课程通过评审</t>
   </si>
   <si>
-    <t>2001年，中国语言文学、新闻与传播及会计三个课程率先通过评审，标志树仁正式走向学位颁授院校</t>
+    <t>2001年，中国语言文学、新闻与传播及会计三个课程率先通过评审，标志树仁正式走向学位颁授院校。</t>
   </si>
   <si>
     <t>B14</t>
@@ -790,7 +766,7 @@
     <t>P03</t>
   </si>
   <si>
-    <t>Shue Yan College Limited adopted its Memorandum and Articles of Association, formally establishing the institution’s corporate and governance framework.</t>
+    <t>Shue Yan College Limited adopted its Memorandum and Articles of Association, formally establishing the institution's corporate and governance framework.</t>
   </si>
   <si>
     <t>樹仁書院有限公司通過組織章程大綱及細則，正式確立院校的法人與管治架構。</t>
@@ -826,7 +802,7 @@
     <t>P06</t>
   </si>
   <si>
-    <t>The campus at 7 Wan Chai Gap Road opened in 1972, serving as Shue Yan’s secondary section during the day and its post-secondary evening division at night.</t>
+    <t>The campus at 7 Wan Chai Gap Road opened in 1972, serving as Shue Yan's secondary section during the day and its post-secondary evening division at night.</t>
   </si>
   <si>
     <t>灣仔峽道7號校舍啟用，日間供樹仁書院中學部學生上課，晚間則由樹仁書院大專部夜組使用。</t>
@@ -838,9 +814,6 @@
     <t>P07</t>
   </si>
   <si>
-    <t>Governor Sir Murray MacLehose paid a private visit to the Wan Chai Gap Road campus and learned about Shue Yan’s founding story and development.</t>
-  </si>
-  <si>
     <t>港督麥理浩爵士私人到訪峽道校舍，了解樹仁的創校經過與發展。</t>
   </si>
   <si>
@@ -850,7 +823,7 @@
     <t>P08</t>
   </si>
   <si>
-    <t>The Education Department made its first formal visit to Shue Yan’s post-secondary campus on Sing Woo Road, Happy Valley.</t>
+    <t>The Education Department made its first formal visit to Shue Yan's post-secondary campus on Sing Woo Road, Happy Valley.</t>
   </si>
   <si>
     <t>教育署首次正式到訪樹仁位於跑馬地成和道的專上校舍。</t>
@@ -1103,9 +1076,6 @@
   </si>
   <si>
     <t>Shue Yan students marched against the proposed conversion of Hong Kong’s four-year undergraduate structure to a three-year system.</t>
-  </si>
-  <si>
-    <t>樹仁學生遊行反對把香港四年制大學本科課程改為三年制。</t>
   </si>
   <si>
     <t>树仁学生游行反对把香港四年制大学本科课程改为三年制。</t>
@@ -3452,9 +3422,6 @@
     </r>
   </si>
   <si>
-    <t>1949–1950年代</t>
-  </si>
-  <si>
     <t>Post-WWII Population Growth and Rising Demand for Higher Education</t>
   </si>
   <si>
@@ -3641,9 +3608,6 @@
     <t>政府宣布大幅增加大学学额，推动高等教育由精英化走向大众化。</t>
   </si>
   <si>
-    <t>1990年代</t>
-  </si>
-  <si>
     <t>Several tertiary institutions attained university status, transforming Hong Kong's higher education landscape.</t>
   </si>
   <si>
@@ -3746,13 +3710,13 @@
     <t>提出打造香港成爲區域教育樞紐理念</t>
   </si>
   <si>
-    <t xml:space="preserve">2004年《施政報告》首提，2006年設跨局委員會，2007年重申。主要措施包括：教資會資助院校非本地學生學額上限由10%提高至20%、、放寬入境、提供獎學金及海外推廣。 </t>
+    <t xml:space="preserve">2004年《施政報告》首提，2006年設跨局委員會，2007年重申。主要措施包括：教資會資助院校非本地學生學額上限由10%提高至20%、放寬入境、提供獎學金及海外推廣。 </t>
   </si>
   <si>
     <t>提出打造香港成为区域教育枢纽理念</t>
   </si>
   <si>
-    <t>2004年《施政报告》首提，2006年设跨局委员会，2007年重申。主要措施包括：教资会资助院校非本地学生学额上限由10%提高至20%、、放宽入境、提供奖学金及海外推广。</t>
+    <t>2004年《施政报告》首提，2006年设跨局委员会，2007年重申。主要措施包括：教资会资助院校非本地学生学额上限由10%提高至20%、放宽入境、提供奖学金及海外推广。</t>
   </si>
   <si>
     <t>B17</t>
@@ -3842,37 +3806,7 @@
     <t>香港特区政府提出建设香港成为国际专上教育枢纽，并将教资会资助大学非本地学生学额上限由20%提高至40%。</t>
   </si>
   <si>
-    <t>政府把樹仁排除於公帑資助大學安排外，學生代表發起四日絕食抗議。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>政府把树仁排除于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>公帑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>资助大学安排外，学生代表发起四日绝食抗议。</t>
-    </r>
+    <t>政府把樹仁排除於公立資助大學安排外，學生代表發起四日絕食抗議。</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -5901,6 +5835,225 @@
   </si>
   <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1990/image58.jpg</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Governor Sir Murray MacLehose paid a private visit to the Wan Chai Gap Road campus and learned about Shue Yan’s founding story and development.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1986</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，樹仁新校舍正式啟用，標誌學院由初創時期的資源緊張，走向較穩定的校園發展階段。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1985</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，楼高十二层的教学大楼落成，树仁正式迁入宝马山现址，建立支撑教学、行政与学生生活的永久校园。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1986</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，树仁新校舍正式启用，标志学院由初创时期的资源紧张，走向较稳定的校园发展阶段。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1988</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，面對香港高等教育制度的新一輪調整，樹仁再次堅持四年制教育，重申大學教育不應只以效率與財政安排衡量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1995</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，樓高十九層的圖書館綜合大樓落成，為圖書館、電腦中心、研究中心及學生學習空間提供重要支援</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1990</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年前后，学生争取政府资助的行动反映私立专上教育的学费压力与公平问题，而树仁仍以维持四年制教育作为接受资助的前提。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1995</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，楼高十九层的图书馆综合大楼落成，为图书馆、计算机中心、研究中心及学生学习空间提供重要支持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1988</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，面对香港高等教育制度的新一轮调整，树仁再次坚持四年制教育，重申大学教育不应只以效率与财政安排衡量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>政府把树仁排除于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公立</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资助大学安排外，学生代表发起四日绝食抗议。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁學生遊行反對把香港四年制大學本科課程改為三年制。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1949–1950</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -5908,7 +6061,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6140,6 +6293,20 @@
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -6649,7 +6816,7 @@
         <v>1949</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>11</v>
@@ -6681,7 +6848,7 @@
         <v>1955</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -6777,10 +6944,10 @@
         <v>1972</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>42</v>
@@ -6935,7 +7102,7 @@
         <v>1980</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>80</v>
@@ -6965,22 +7132,22 @@
         <v>1982</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -6997,7 +7164,7 @@
         <v>1983</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>88</v>
@@ -7042,39 +7209,39 @@
         <v>98</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>99</v>
+        <v>1018</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
       <c r="A15" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15" s="5">
         <v>1986</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="H15" s="7" t="s">
-        <v>106</v>
+        <v>1019</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>62</v>
@@ -7083,448 +7250,448 @@
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2">
         <v>1987</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="G16" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="H16" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B17" s="5">
         <v>1988</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>120</v>
+        <v>1024</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.8">
       <c r="A18" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2">
         <v>1990</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>128</v>
+        <v>1022</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B19" s="5">
         <v>1995</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>134</v>
+        <v>1021</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>136</v>
+        <v>1023</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>62</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="5" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B20" s="2">
         <v>1996</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B21" s="5">
         <v>1999</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B22" s="2">
         <v>2000</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B23" s="5">
         <v>2001</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B24" s="2">
         <v>2002</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B25" s="5">
         <v>2003</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>53</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="68.400000000000006">
       <c r="A26" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B26" s="2">
         <v>2004</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B27" s="5">
         <v>2005</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>53</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B28" s="2">
         <v>2006</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B29" s="5">
         <v>2007</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -7578,19 +7745,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7598,34 +7765,34 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
@@ -7636,28 +7803,28 @@
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -7668,25 +7835,25 @@
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
@@ -7695,28 +7862,28 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>971</v>
+        <v>958</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -7727,28 +7894,28 @@
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -7759,28 +7926,28 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -7791,28 +7958,28 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>229</v>
+        <v>1016</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -7823,28 +7990,28 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -7855,28 +8022,28 @@
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -7887,25 +8054,25 @@
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -7914,25 +8081,25 @@
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -7944,28 +8111,28 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -7976,28 +8143,28 @@
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -8008,28 +8175,28 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8040,28 +8207,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>991</v>
+        <v>978</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8072,28 +8239,28 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>992</v>
+        <v>979</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8104,28 +8271,28 @@
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8136,28 +8303,28 @@
     </row>
     <row r="19" spans="1:14" ht="28.8">
       <c r="A19" s="5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8168,28 +8335,28 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>999</v>
+        <v>986</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8200,28 +8367,28 @@
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8232,25 +8399,25 @@
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>1002</v>
+        <v>989</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8262,25 +8429,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8292,28 +8459,28 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8324,28 +8491,28 @@
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8356,25 +8523,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8385,25 +8552,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8415,28 +8582,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8447,25 +8614,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8477,28 +8644,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8509,25 +8676,25 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>318</v>
+        <v>1026</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8539,28 +8706,28 @@
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>803</v>
+        <v>1025</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8571,25 +8738,25 @@
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8601,25 +8768,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8631,28 +8798,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>1020</v>
+        <v>1007</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8663,28 +8830,28 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8695,25 +8862,25 @@
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8725,28 +8892,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -8757,28 +8924,28 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>1027</v>
+        <v>1014</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -8789,25 +8956,25 @@
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -8819,25 +8986,25 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -8849,28 +9016,28 @@
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -8881,28 +9048,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -8913,25 +9080,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -8943,22 +9110,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8971,28 +9138,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -9003,28 +9170,28 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9035,25 +9202,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9065,25 +9232,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9095,25 +9262,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9125,28 +9292,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9157,25 +9324,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9187,25 +9354,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9217,25 +9384,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9247,28 +9414,28 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
@@ -9279,25 +9446,25 @@
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9309,25 +9476,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9339,25 +9506,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9369,28 +9536,28 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
@@ -9401,25 +9568,25 @@
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
@@ -9431,25 +9598,25 @@
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9461,25 +9628,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9491,25 +9658,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9521,25 +9688,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9551,25 +9718,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9581,25 +9748,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9611,25 +9778,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9641,28 +9808,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9673,28 +9840,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9705,28 +9872,28 @@
     </row>
     <row r="70" spans="1:14" ht="28.8">
       <c r="A70" s="2" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9737,25 +9904,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9767,28 +9934,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9799,25 +9966,25 @@
     </row>
     <row r="73" spans="1:14" ht="55.2">
       <c r="A73" s="5" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -9829,25 +9996,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9859,28 +10026,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -9891,28 +10058,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -9923,22 +10090,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -9951,28 +10118,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -9983,25 +10150,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10013,28 +10180,28 @@
     </row>
     <row r="80" spans="1:14" ht="28.8">
       <c r="A80" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10045,25 +10212,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10075,25 +10242,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10105,22 +10272,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10132,25 +10299,25 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
@@ -10162,25 +10329,25 @@
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
@@ -10192,28 +10359,28 @@
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10224,28 +10391,28 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
@@ -10256,28 +10423,28 @@
     </row>
     <row r="88" spans="1:14" ht="55.2">
       <c r="A88" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10288,28 +10455,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10320,22 +10487,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10348,28 +10515,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10380,60 +10547,60 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="41.4">
       <c r="A93" s="5" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="B93" s="5">
         <v>2021</v>
       </c>
       <c r="C93" s="15"/>
       <c r="D93" s="15" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="E93" s="15"/>
       <c r="F93" s="16" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="G93" s="15"/>
       <c r="H93" s="15" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
@@ -10444,28 +10611,28 @@
     </row>
     <row r="94" spans="1:14" ht="28.8">
       <c r="A94" s="2" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="12" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="G94" s="11"/>
       <c r="H94" s="12" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
@@ -10476,58 +10643,58 @@
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I96" s="32" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
@@ -10538,28 +10705,28 @@
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
@@ -10570,25 +10737,25 @@
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
@@ -10600,305 +10767,305 @@
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
@@ -10910,54 +11077,54 @@
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
@@ -10968,28 +11135,28 @@
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
@@ -11000,28 +11167,28 @@
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
@@ -11032,25 +11199,25 @@
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11062,22 +11229,22 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="I114" s="17"/>
       <c r="J114" s="17"/>
@@ -11085,123 +11252,123 @@
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11209,45 +11376,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11445,103 +11612,103 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>672</v>
+        <v>1027</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11552,22 +11719,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11578,22 +11745,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11604,360 +11771,360 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" s="5">
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>735</v>
+        <v>129</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12050,6 +12217,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12231,25 +12415,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -12261,7 +12428,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4DD696-0F97-4B0F-8C6F-1C8618104A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{769378C5-5EAD-42FD-A4C0-1662B8A26D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13932" yWindow="0" windowWidth="9204" windowHeight="12336" tabRatio="599" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1029">
   <si>
     <t>id</t>
   </si>
@@ -6054,6 +6054,10 @@
   </si>
   <si>
     <t>1949–1950</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6061,7 +6065,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6308,8 +6312,15 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6325,6 +6336,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F7FA"/>
+        <bgColor rgb="FFF2F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFF2F7FA"/>
       </patternFill>
     </fill>
@@ -6368,7 +6391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6463,6 +6486,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9898,8 +9930,8 @@
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
-      <c r="N70" s="2" t="s">
-        <v>53</v>
+      <c r="N70" s="33" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="28.8">
@@ -10206,8 +10238,8 @@
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
-      <c r="N80" s="2" t="s">
-        <v>39</v>
+      <c r="N80" s="33" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="28.8">
@@ -10573,72 +10605,72 @@
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
-      <c r="N92" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="41.4">
-      <c r="A93" s="5" t="s">
+      <c r="N92" s="33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="28.8">
+      <c r="A93" s="33" t="s">
         <v>555</v>
       </c>
-      <c r="B93" s="5">
-        <v>2021</v>
-      </c>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15" t="s">
-        <v>556</v>
-      </c>
-      <c r="E93" s="15"/>
-      <c r="F93" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15" t="s">
-        <v>558</v>
+      <c r="B93" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="E93" s="11"/>
+      <c r="F93" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="G93" s="11"/>
+      <c r="H93" s="12" t="s">
+        <v>563</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
-      <c r="N93" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="28.8">
-      <c r="A94" s="2" t="s">
+      <c r="N93" s="33" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="41.4">
+      <c r="A94" s="34" t="s">
         <v>559</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="G94" s="11"/>
-      <c r="H94" s="12" t="s">
-        <v>563</v>
+      <c r="B94" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="G94" s="15"/>
+      <c r="H94" s="15" t="s">
+        <v>558</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
-      <c r="N94" s="2" t="s">
-        <v>39</v>
+      <c r="N94" s="33" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
@@ -10731,8 +10763,8 @@
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
-      <c r="N97" s="5" t="s">
-        <v>39</v>
+      <c r="N97" s="34" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
@@ -11129,8 +11161,8 @@
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
-      <c r="N110" s="2" t="s">
-        <v>62</v>
+      <c r="N110" s="33" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
@@ -11246,7 +11278,9 @@
       <c r="H114" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="I114" s="17"/>
+      <c r="I114" s="35" t="s">
+        <v>1028</v>
+      </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
@@ -11491,10 +11525,10 @@
     <hyperlink ref="J91" r:id="rId66" xr:uid="{CF681112-984B-4B41-8352-53DEA1E4885B}"/>
     <hyperlink ref="I92" r:id="rId67" xr:uid="{608B7A82-8006-4EF3-BA9C-34BD1F76E850}"/>
     <hyperlink ref="J92" r:id="rId68" xr:uid="{0DF74632-0F1B-4F6A-933A-C0211E1A2386}"/>
-    <hyperlink ref="I93" r:id="rId69" xr:uid="{ABB5A605-9501-48BA-8F3F-7215EB30F557}"/>
-    <hyperlink ref="J93" r:id="rId70" xr:uid="{88FAC45E-4174-4D47-8C58-F2CB9CEE0A21}"/>
-    <hyperlink ref="I94" r:id="rId71" xr:uid="{BFFAE3EC-B872-4956-9F63-00932BA417F2}"/>
-    <hyperlink ref="J94" r:id="rId72" xr:uid="{D01F96F1-BB1E-4853-A4F6-97E7F7AC9859}"/>
+    <hyperlink ref="I94" r:id="rId69" xr:uid="{ABB5A605-9501-48BA-8F3F-7215EB30F557}"/>
+    <hyperlink ref="J94" r:id="rId70" xr:uid="{88FAC45E-4174-4D47-8C58-F2CB9CEE0A21}"/>
+    <hyperlink ref="I93" r:id="rId71" xr:uid="{BFFAE3EC-B872-4956-9F63-00932BA417F2}"/>
+    <hyperlink ref="J93" r:id="rId72" xr:uid="{D01F96F1-BB1E-4853-A4F6-97E7F7AC9859}"/>
     <hyperlink ref="I95" r:id="rId73" xr:uid="{F178BA2B-1E6E-49AE-A821-668B86CC7D7E}"/>
     <hyperlink ref="I96" r:id="rId74" xr:uid="{2FD22D0C-290D-489D-9C4A-BF9346A617C0}"/>
     <hyperlink ref="J96" r:id="rId75" xr:uid="{B9A1DBAD-06F5-4856-99C1-B6475B00DC35}"/>
@@ -11559,10 +11593,11 @@
     <hyperlink ref="I38" r:id="rId134" xr:uid="{61894759-FBF0-4B26-90D5-C9218A470158}"/>
     <hyperlink ref="J38" r:id="rId135" xr:uid="{4270A5FD-04C6-4AF2-AFF7-EB417B86DCD8}"/>
     <hyperlink ref="J32" r:id="rId136" xr:uid="{B268696E-8BE6-4EE9-AA45-EA6E0A6C3A77}"/>
+    <hyperlink ref="I114" r:id="rId137" xr:uid="{EDE37357-F5DB-4B8D-8FDF-357693D758F4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId137"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId138"/>
+  <legacyDrawing r:id="rId139"/>
 </worksheet>
 </file>
 
@@ -12217,23 +12252,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12415,20 +12433,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{769378C5-5EAD-42FD-A4C0-1662B8A26D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF61B53B-B55B-4AA3-8D80-8049824D1085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1032">
   <si>
     <t>id</t>
   </si>
@@ -2720,9 +2720,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>P92</t>
-  </si>
-  <si>
     <t>In 2020/21, HKSYU received HK$16.4 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Arts, Culture and Technology.</t>
   </si>
   <si>
@@ -2783,9 +2780,6 @@
       </rPr>
       <t>一千六百四十万元，发展艺术、文化及科技荣誉社会科学学士课程。</t>
     </r>
-  </si>
-  <si>
-    <t>P93</t>
   </si>
   <si>
     <t>2021-2025</t>
@@ -6058,6 +6052,26 @@
   </si>
   <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>P92</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>P93</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6313,9 +6327,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9.5"/>
-      <color rgb="FFFF0000"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -6341,14 +6353,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF2F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFF2F7FA"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -6391,7 +6403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6487,13 +6499,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6848,7 +6863,7 @@
         <v>1949</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>11</v>
@@ -6880,7 +6895,7 @@
         <v>1955</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -6976,10 +6991,10 @@
         <v>1972</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>42</v>
@@ -7134,7 +7149,7 @@
         <v>1980</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>80</v>
@@ -7164,22 +7179,22 @@
         <v>1982</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E12" s="23" t="s">
+        <v>837</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>839</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>841</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>842</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>53</v>
@@ -7196,7 +7211,7 @@
         <v>1983</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>88</v>
@@ -7241,7 +7256,7 @@
         <v>98</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>62</v>
@@ -7258,7 +7273,7 @@
         <v>1986</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>101</v>
@@ -7267,13 +7282,13 @@
         <v>102</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G15" s="15" t="s">
         <v>103</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>62</v>
@@ -7329,13 +7344,13 @@
         <v>114</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>115</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>39</v>
@@ -7367,7 +7382,7 @@
         <v>122</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>39</v>
@@ -7393,13 +7408,13 @@
         <v>127</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>128</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>62</v>
@@ -7448,10 +7463,10 @@
         <v>1999</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>138</v>
@@ -7480,10 +7495,10 @@
         <v>2000</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>144</v>
@@ -7638,7 +7653,7 @@
         <v>2005</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>180</v>
@@ -7670,16 +7685,16 @@
         <v>2006</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>187</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>188</v>
@@ -7705,7 +7720,7 @@
         <v>191</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>192</v>
@@ -7746,8 +7761,7 @@
     <col min="6" max="6" width="65.88671875" style="10" customWidth="1"/>
     <col min="7" max="7" width="37.109375" customWidth="1"/>
     <col min="8" max="8" width="47.33203125" customWidth="1"/>
-    <col min="9" max="10" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="42.33203125" customWidth="1"/>
+    <col min="9" max="13" width="42.33203125" customWidth="1"/>
     <col min="14" max="14" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7780,16 +7794,16 @@
         <v>197</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>946</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7806,13 +7820,13 @@
         <v>199</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>200</v>
@@ -7821,10 +7835,10 @@
         <v>201</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
@@ -7842,21 +7856,21 @@
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -7885,7 +7899,7 @@
         <v>207</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
@@ -7912,10 +7926,10 @@
         <v>211</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -7944,10 +7958,10 @@
         <v>215</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -7976,10 +7990,10 @@
         <v>219</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -7997,7 +8011,7 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
@@ -8008,10 +8022,10 @@
         <v>222</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -8040,10 +8054,10 @@
         <v>226</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -8072,10 +8086,10 @@
         <v>230</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -8104,7 +8118,7 @@
         <v>234</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -8131,7 +8145,7 @@
         <v>238</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -8161,10 +8175,10 @@
         <v>242</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -8182,21 +8196,21 @@
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -8225,10 +8239,10 @@
         <v>247</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8257,10 +8271,10 @@
         <v>251</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8289,10 +8303,10 @@
         <v>255</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8321,10 +8335,10 @@
         <v>259</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8342,7 +8356,7 @@
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
@@ -8353,10 +8367,10 @@
         <v>262</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8385,10 +8399,10 @@
         <v>266</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8406,7 +8420,7 @@
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
@@ -8417,10 +8431,10 @@
         <v>269</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8449,7 +8463,7 @@
         <v>273</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8479,7 +8493,7 @@
         <v>277</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8509,10 +8523,10 @@
         <v>281</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8541,10 +8555,10 @@
         <v>285</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8573,7 +8587,7 @@
         <v>289</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8602,7 +8616,7 @@
         <v>293</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8632,10 +8646,10 @@
         <v>297</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8664,7 +8678,7 @@
         <v>302</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8694,10 +8708,10 @@
         <v>306</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8719,14 +8733,14 @@
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
         <v>309</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8749,17 +8763,17 @@
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8788,7 +8802,7 @@
         <v>315</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8818,7 +8832,7 @@
         <v>319</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8848,10 +8862,10 @@
         <v>323</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8880,10 +8894,10 @@
         <v>327</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8909,10 +8923,10 @@
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8942,10 +8956,10 @@
         <v>334</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -8963,7 +8977,7 @@
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
@@ -8971,13 +8985,13 @@
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -9006,7 +9020,7 @@
         <v>340</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -9453,7 +9467,7 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
@@ -9464,16 +9478,16 @@
         <v>417</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
-      <c r="N55" s="2" t="s">
-        <v>53</v>
+      <c r="N55" s="36" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
@@ -9496,7 +9510,7 @@
         <v>421</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9526,7 +9540,7 @@
         <v>425</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9556,7 +9570,7 @@
         <v>429</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9586,16 +9600,16 @@
         <v>433</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
-      <c r="N59" s="5" t="s">
-        <v>53</v>
+      <c r="N59" s="36" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
@@ -9618,14 +9632,14 @@
         <v>437</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
-      <c r="N60" s="5" t="s">
-        <v>53</v>
+      <c r="N60" s="36" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
@@ -9648,7 +9662,7 @@
         <v>441</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9678,7 +9692,7 @@
         <v>445</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9708,7 +9722,7 @@
         <v>449</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9738,7 +9752,7 @@
         <v>453</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9765,10 +9779,10 @@
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9795,10 +9809,10 @@
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9825,10 +9839,10 @@
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9847,7 +9861,7 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
@@ -9858,10 +9872,10 @@
         <v>465</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9890,10 +9904,10 @@
         <v>469</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9922,15 +9936,15 @@
         <v>473</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
-      <c r="N70" s="33" t="s">
+      <c r="N70" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9954,7 +9968,7 @@
         <v>477</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9984,10 +9998,10 @@
         <v>481</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -10005,18 +10019,18 @@
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -10046,7 +10060,7 @@
         <v>486</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -10076,10 +10090,10 @@
         <v>490</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -10108,10 +10122,10 @@
         <v>494</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -10168,10 +10182,10 @@
         <v>502</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -10200,7 +10214,7 @@
         <v>506</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10230,15 +10244,15 @@
         <v>510</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
-      <c r="N80" s="33" t="s">
+      <c r="N80" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10262,14 +10276,14 @@
         <v>514</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
-      <c r="N81" s="5" t="s">
-        <v>16</v>
+      <c r="N81" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="28.8">
@@ -10281,7 +10295,7 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
@@ -10292,7 +10306,7 @@
         <v>517</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10349,14 +10363,14 @@
         <v>525</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
-      <c r="N84" s="2" t="s">
-        <v>39</v>
+      <c r="N84" s="36" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
@@ -10379,14 +10393,14 @@
         <v>529</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
-      <c r="N85" s="5" t="s">
-        <v>39</v>
+      <c r="N85" s="36" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
@@ -10409,10 +10423,10 @@
         <v>533</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10441,16 +10455,16 @@
         <v>538</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
-      <c r="N87" s="5" t="s">
-        <v>16</v>
+      <c r="N87" s="36" t="s">
+        <v>1031</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="55.2">
@@ -10462,21 +10476,21 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10494,7 +10508,7 @@
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
@@ -10505,10 +10519,10 @@
         <v>543</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10530,11 +10544,11 @@
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10565,10 +10579,10 @@
         <v>549</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10597,103 +10611,103 @@
         <v>553</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
-      <c r="N92" s="33" t="s">
-        <v>16</v>
+      <c r="N92" s="5" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
-      <c r="A93" s="33" t="s">
-        <v>555</v>
+      <c r="A93" s="34" t="s">
+        <v>1027</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
-      <c r="N93" s="33" t="s">
+      <c r="N93" s="5" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
-      <c r="A94" s="34" t="s">
-        <v>559</v>
+      <c r="A94" s="35" t="s">
+        <v>1028</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
-      <c r="N94" s="33" t="s">
+      <c r="N94" s="5" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
@@ -10705,119 +10719,119 @@
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I96" s="32" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
-      <c r="N96" s="2" t="s">
-        <v>16</v>
+      <c r="N96" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
-      <c r="N97" s="34" t="s">
+      <c r="N97" s="5" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
-      <c r="N98" s="2" t="s">
-        <v>39</v>
+      <c r="N98" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
@@ -10829,28 +10843,28 @@
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
@@ -10861,25 +10875,25 @@
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
@@ -10891,28 +10905,28 @@
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
@@ -10923,28 +10937,28 @@
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
@@ -10955,28 +10969,28 @@
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
@@ -10987,28 +11001,28 @@
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
@@ -11019,25 +11033,25 @@
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
@@ -11049,25 +11063,25 @@
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
@@ -11079,55 +11093,55 @@
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
-      <c r="N108" s="2" t="s">
-        <v>39</v>
+      <c r="N108" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="N109" s="5" t="s">
         <v>554</v>
@@ -11135,121 +11149,121 @@
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
-      <c r="N110" s="33" t="s">
-        <v>16</v>
+      <c r="N110" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
-      <c r="N111" s="2" t="s">
-        <v>39</v>
+      <c r="N111" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>39</v>
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11261,25 +11275,25 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="I114" s="35" t="s">
-        <v>1028</v>
+        <v>639</v>
+      </c>
+      <c r="I114" s="33" t="s">
+        <v>1026</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
@@ -11291,28 +11305,28 @@
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
@@ -11323,28 +11337,28 @@
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
@@ -11355,28 +11369,28 @@
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
@@ -11387,22 +11401,22 @@
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11415,37 +11429,37 @@
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="J119" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>947</v>
+      </c>
+      <c r="L119" s="17" t="s">
         <v>948</v>
       </c>
-      <c r="K119" s="17" t="s">
+      <c r="M119" s="17" t="s">
         <v>949</v>
-      </c>
-      <c r="L119" s="17" t="s">
-        <v>950</v>
-      </c>
-      <c r="M119" s="17" t="s">
-        <v>951</v>
       </c>
       <c r="N119" s="5" t="s">
         <v>554</v>
@@ -11647,103 +11661,103 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>665</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>678</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>683</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>685</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11754,22 +11768,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>691</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11780,22 +11794,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>697</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11806,22 +11820,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -11832,22 +11846,22 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>709</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
@@ -11858,48 +11872,48 @@
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>714</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>720</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
@@ -11910,74 +11924,74 @@
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>726</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>730</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>733</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>734</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>740</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
@@ -11988,48 +12002,48 @@
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>746</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
@@ -12037,129 +12051,129 @@
         <v>196</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>831</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>758</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>765</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="G19" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="H19" s="7" t="s">
         <v>772</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>780</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>785</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>787</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">

--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71B4182C-6FE2-44EE-8A62-4453AD4F757C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B2AB5F-B950-4708-AB53-8C33CF0CB5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1086,9 +1086,6 @@
     <t>Shue Yan established its Board of Governors, bringing together prominent leaders to advance university affairs and campus development. The Board of Governors included Chairman Wilfred Wong Sien-bing, and other members such as Sir Run Run Shaw, Ms. Aw Sian from Sing Tao Daily, Mr. Ngan Shing-kwan, founder of China Motor Corporation, Mr. Ting Hsiung-chao, one of the founders of the Hong Kong Plastics Manufacturers Association, Dr. Maurice J. Anderson, Mr. T. K. Ann, Bishop Gilbert Baker, Barrister Brook Bernacchi, Mr. Cha Chi Ming, Mr. Chan Po Fun, Mr. Chen Chan-yen, Dr. Dr. Chung Chi-yung, Rev. Fergus Cronin, Mr. Dr. Hu Hung-lick, Mr. Huo Pao-tsai, Barrister Henry Litton, Mr. Liu Han-tang, Mr. Y. B. Loo, Mr. Peter P. K. Ng, Mr. Shum Choi Sang, Mr. Shum Wai-yau, Mr. Peter H. M. Tsang, Mr. C. S. Wan, and Mr. Yuen Ngan Ming.</t>
   </si>
   <si>
-    <t>胡鴻烈與鐘期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
-  </si>
-  <si>
     <r>
       <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
     </r>
@@ -1119,10 +1116,6 @@
     <t>树仁成立校董会，汇聚贤达，推动校务与校舍建设。校董会成员包括主席黄宣平议员，校董成员包括邵逸夫先生、来自《星岛日报》的胡仙女士、中华汽车创办人颜成坤议员、香港塑料业厂商会创会人之一丁熊照先生、晏务理博士、安子介议员、白约翰主教、贝纳祺御用大律师、查济民先生、陈普芬议员、陈存仁先生、钟期荣博士、龚乐年神父、胡鸿烈议员、霍宝材先生、烈显伦御用大律师、刘汉栋先生、陆荫百先生、伍秉坚议员、岑才生先生、岑维休先生、曾汉文先生、万春先先生、阮雁鸣先生。</t>
   </si>
   <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971/image1.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971/image2.jpg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1169,9 +1162,6 @@
   </si>
   <si>
     <t>校監胡鴻烈代表樹仁書院赴美考察，與多所大學商討學術合作。</t>
-  </si>
-  <si>
-    <t>校监胡鸿烈代表树仁书院赴美考察，与多所大学商讨学术合作。</t>
   </si>
   <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image7.jpg</t>
@@ -5757,6 +5747,18 @@
   </si>
   <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1996/image71.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>校监胡鸿烈代表树仁书院赴美考察，与多所大学商讨学术合作。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971/image1.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡鴻烈與鐘期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6938,7 +6940,7 @@
         <v>92</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="F12" s="39" t="s">
         <v>93</v>
@@ -6970,7 +6972,7 @@
         <v>98</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="F13" s="42" t="s">
         <v>99</v>
@@ -7062,7 +7064,7 @@
         <v>119</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F16" s="39" t="s">
         <v>120</v>
@@ -7447,7 +7449,7 @@
         <v>211</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="G28" s="40" t="s">
         <v>212</v>
@@ -7479,7 +7481,7 @@
         <v>217</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="G29" s="43" t="s">
         <v>218</v>
@@ -7576,24 +7578,23 @@
         <v>228</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F2" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="G2" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="14" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="2" t="s">
@@ -7602,28 +7603,28 @@
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -7634,25 +7635,25 @@
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
@@ -7661,28 +7662,28 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>248</v>
+        <v>1029</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -7693,28 +7694,28 @@
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -7725,28 +7726,28 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -7757,28 +7758,28 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -7789,28 +7790,28 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -7821,28 +7822,28 @@
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -7853,25 +7854,25 @@
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -7880,25 +7881,25 @@
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -7910,28 +7911,28 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -7942,28 +7943,28 @@
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -7974,28 +7975,28 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8006,28 +8007,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8038,28 +8039,28 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8070,28 +8071,28 @@
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8102,28 +8103,28 @@
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="36" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8134,28 +8135,28 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8166,28 +8167,28 @@
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8198,25 +8199,25 @@
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8228,25 +8229,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8258,28 +8259,28 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8290,28 +8291,28 @@
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8322,25 +8323,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8351,25 +8352,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8381,28 +8382,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8413,25 +8414,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8443,28 +8444,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8475,25 +8476,25 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8505,28 +8506,28 @@
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8537,25 +8538,25 @@
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8567,25 +8568,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8597,28 +8598,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8629,28 +8630,28 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8661,25 +8662,25 @@
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8691,28 +8692,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -8723,28 +8724,28 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -8755,25 +8756,25 @@
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -8785,25 +8786,25 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -8815,28 +8816,28 @@
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -8847,28 +8848,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -8879,25 +8880,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -8909,22 +8910,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8937,28 +8938,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -8969,28 +8970,28 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9001,25 +9002,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9031,25 +9032,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9061,25 +9062,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9091,28 +9092,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9123,25 +9124,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9153,25 +9154,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9183,25 +9184,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9213,57 +9214,57 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9275,25 +9276,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9305,25 +9306,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9335,87 +9336,87 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9427,25 +9428,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9457,25 +9458,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9487,25 +9488,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9517,25 +9518,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9547,25 +9548,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9577,25 +9578,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9607,28 +9608,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9639,28 +9640,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9671,28 +9672,28 @@
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9703,25 +9704,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9733,28 +9734,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9765,25 +9766,25 @@
     </row>
     <row r="73" spans="1:14" ht="55.2">
       <c r="A73" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -9795,25 +9796,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9825,28 +9826,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -9857,28 +9858,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -9889,22 +9890,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -9917,28 +9918,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -9949,25 +9950,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -9979,28 +9980,28 @@
     </row>
     <row r="80" spans="1:14" ht="28.8">
       <c r="A80" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10011,25 +10012,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10041,25 +10042,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10071,22 +10072,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10098,88 +10099,88 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10190,60 +10191,60 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="55.2">
       <c r="A88" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10254,28 +10255,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10286,22 +10287,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10314,28 +10315,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10346,677 +10347,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11028,148 +11029,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11177,45 +11178,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
+        <v>878</v>
+      </c>
+      <c r="I119" s="17" t="s">
+        <v>879</v>
+      </c>
+      <c r="J119" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="K119" s="17" t="s">
         <v>881</v>
       </c>
-      <c r="I119" s="17" t="s">
+      <c r="L119" s="17" t="s">
         <v>882</v>
       </c>
-      <c r="J119" s="17" t="s">
+      <c r="M119" s="17" t="s">
         <v>883</v>
       </c>
-      <c r="K119" s="17" t="s">
-        <v>884</v>
-      </c>
-      <c r="L119" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="M119" s="17" t="s">
-        <v>886</v>
-      </c>
       <c r="N119" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11337,30 +11338,30 @@
     <hyperlink ref="K119" r:id="rId111" xr:uid="{BA3BE9F0-D6A4-4C5F-AE8E-A59F1F8FD507}"/>
     <hyperlink ref="L119" r:id="rId112" xr:uid="{77F39965-BB5C-4769-8858-829F66951E14}"/>
     <hyperlink ref="M119" r:id="rId113" xr:uid="{2FB33C56-1380-41A4-8706-3AE88BB47AA5}"/>
-    <hyperlink ref="I2" r:id="rId114" xr:uid="{7650B5A9-5549-4EA3-8B19-B0259AD3AA3C}"/>
-    <hyperlink ref="J2" r:id="rId115" xr:uid="{6AA6360E-BA23-4011-8A8B-8B6B48D41607}"/>
-    <hyperlink ref="I3" r:id="rId116" xr:uid="{3369FE77-05E7-492D-B47D-BFF18361A91E}"/>
-    <hyperlink ref="J3" r:id="rId117" xr:uid="{C504A209-9B4B-41CA-A7A9-A9643186FCD5}"/>
-    <hyperlink ref="I4" r:id="rId118" xr:uid="{14C7CBAD-625B-42FA-B4DC-347ECDE4B9A3}"/>
-    <hyperlink ref="I5" r:id="rId119" xr:uid="{29581AA1-42F1-410A-8408-DD01408A517A}"/>
-    <hyperlink ref="J5" r:id="rId120" xr:uid="{73D12E80-4944-4ECF-9CF6-F825474098DB}"/>
-    <hyperlink ref="I6" r:id="rId121" xr:uid="{8B33FD58-153A-4A6D-9B51-1274943187B3}"/>
-    <hyperlink ref="J6" r:id="rId122" xr:uid="{1BEE3F19-B0F9-47A8-B6FF-49DB8E81AE46}"/>
-    <hyperlink ref="I7" r:id="rId123" xr:uid="{35D916A7-77D8-4CD8-9E4B-E06B91FF13E9}"/>
-    <hyperlink ref="J7" r:id="rId124" xr:uid="{B7DC80A4-8D2E-45A7-A817-151E3462388E}"/>
-    <hyperlink ref="I8" r:id="rId125" xr:uid="{A4F597B9-46E3-42C8-9A76-1416442A2CAF}"/>
-    <hyperlink ref="I9" r:id="rId126" xr:uid="{1EB90F7B-7A03-4D0E-AD32-6CE743341F52}"/>
-    <hyperlink ref="I13" r:id="rId127" xr:uid="{BEB48E04-21FA-444F-865F-51B7812747C9}"/>
-    <hyperlink ref="I15" r:id="rId128" xr:uid="{37100297-D071-4069-80E2-2E2CF445969B}"/>
-    <hyperlink ref="I16" r:id="rId129" xr:uid="{71529AF7-55FF-449D-8F76-D35CAF6EFBF4}"/>
-    <hyperlink ref="I26" r:id="rId130" xr:uid="{BEB30A1F-4CBE-431A-8F70-E712E32B859F}"/>
-    <hyperlink ref="I29" r:id="rId131" xr:uid="{03622D52-D916-471C-9257-4D1B9914B139}"/>
-    <hyperlink ref="I30" r:id="rId132" xr:uid="{D973163B-0132-45CD-8734-2D5E41D02B20}"/>
-    <hyperlink ref="I38" r:id="rId133" xr:uid="{61894759-FBF0-4B26-90D5-C9218A470158}"/>
-    <hyperlink ref="J38" r:id="rId134" xr:uid="{4270A5FD-04C6-4AF2-AFF7-EB417B86DCD8}"/>
-    <hyperlink ref="J32" r:id="rId135" xr:uid="{B268696E-8BE6-4EE9-AA45-EA6E0A6C3A77}"/>
-    <hyperlink ref="I114" r:id="rId136" xr:uid="{EDE37357-F5DB-4B8D-8FDF-357693D758F4}"/>
-    <hyperlink ref="I42" r:id="rId137" xr:uid="{DA636E22-38CB-43D2-A7D9-A41E55F76349}"/>
+    <hyperlink ref="J2" r:id="rId114" xr:uid="{6AA6360E-BA23-4011-8A8B-8B6B48D41607}"/>
+    <hyperlink ref="I3" r:id="rId115" xr:uid="{3369FE77-05E7-492D-B47D-BFF18361A91E}"/>
+    <hyperlink ref="J3" r:id="rId116" xr:uid="{C504A209-9B4B-41CA-A7A9-A9643186FCD5}"/>
+    <hyperlink ref="I4" r:id="rId117" xr:uid="{14C7CBAD-625B-42FA-B4DC-347ECDE4B9A3}"/>
+    <hyperlink ref="I5" r:id="rId118" xr:uid="{29581AA1-42F1-410A-8408-DD01408A517A}"/>
+    <hyperlink ref="J5" r:id="rId119" xr:uid="{73D12E80-4944-4ECF-9CF6-F825474098DB}"/>
+    <hyperlink ref="I6" r:id="rId120" xr:uid="{8B33FD58-153A-4A6D-9B51-1274943187B3}"/>
+    <hyperlink ref="J6" r:id="rId121" xr:uid="{1BEE3F19-B0F9-47A8-B6FF-49DB8E81AE46}"/>
+    <hyperlink ref="I7" r:id="rId122" xr:uid="{35D916A7-77D8-4CD8-9E4B-E06B91FF13E9}"/>
+    <hyperlink ref="J7" r:id="rId123" xr:uid="{B7DC80A4-8D2E-45A7-A817-151E3462388E}"/>
+    <hyperlink ref="I8" r:id="rId124" xr:uid="{A4F597B9-46E3-42C8-9A76-1416442A2CAF}"/>
+    <hyperlink ref="I9" r:id="rId125" xr:uid="{1EB90F7B-7A03-4D0E-AD32-6CE743341F52}"/>
+    <hyperlink ref="I13" r:id="rId126" xr:uid="{BEB48E04-21FA-444F-865F-51B7812747C9}"/>
+    <hyperlink ref="I15" r:id="rId127" xr:uid="{37100297-D071-4069-80E2-2E2CF445969B}"/>
+    <hyperlink ref="I16" r:id="rId128" xr:uid="{71529AF7-55FF-449D-8F76-D35CAF6EFBF4}"/>
+    <hyperlink ref="I26" r:id="rId129" xr:uid="{BEB30A1F-4CBE-431A-8F70-E712E32B859F}"/>
+    <hyperlink ref="I29" r:id="rId130" xr:uid="{03622D52-D916-471C-9257-4D1B9914B139}"/>
+    <hyperlink ref="I30" r:id="rId131" xr:uid="{D973163B-0132-45CD-8734-2D5E41D02B20}"/>
+    <hyperlink ref="I38" r:id="rId132" xr:uid="{61894759-FBF0-4B26-90D5-C9218A470158}"/>
+    <hyperlink ref="J38" r:id="rId133" xr:uid="{4270A5FD-04C6-4AF2-AFF7-EB417B86DCD8}"/>
+    <hyperlink ref="J32" r:id="rId134" xr:uid="{B268696E-8BE6-4EE9-AA45-EA6E0A6C3A77}"/>
+    <hyperlink ref="I114" r:id="rId135" xr:uid="{EDE37357-F5DB-4B8D-8FDF-357693D758F4}"/>
+    <hyperlink ref="I42" r:id="rId136" xr:uid="{DA636E22-38CB-43D2-A7D9-A41E55F76349}"/>
+    <hyperlink ref="I2" r:id="rId137" xr:uid="{DE4DE85E-7A5B-4792-9373-BDBB5D7A94CB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId138"/>
@@ -11414,103 +11415,103 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>890</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>895</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>897</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>898</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>899</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>904</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>909</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>913</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11521,22 +11522,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>917</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>918</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11547,22 +11548,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>923</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>924</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>925</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11573,22 +11574,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>929</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -11599,22 +11600,22 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>935</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>937</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
@@ -11625,48 +11626,48 @@
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>939</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>946</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>947</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>948</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>949</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>950</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
@@ -11677,74 +11678,74 @@
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>954</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>956</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>958</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>959</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>961</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>962</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>963</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>966</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>968</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
@@ -11755,48 +11756,48 @@
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>972</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>974</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>975</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>982</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>983</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
@@ -11804,129 +11805,129 @@
         <v>220</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>987</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>989</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>990</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>994</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>996</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>997</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>1001</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>1003</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>1009</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="H20" s="4" t="s">
         <v>1011</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>1016</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>1018</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">

--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B2AB5F-B950-4708-AB53-8C33CF0CB5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9755D3B3-7960-4184-B99E-6A3910944FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1232,12 +1232,6 @@
     <t>P08</t>
   </si>
   <si>
-    <t>The Education Department made its first formal visit to Shue Yan's post-secondary campus on Sing Woo Road, Happy Valley.</t>
-  </si>
-  <si>
-    <t>教育署首次正式到訪樹仁位於跑馬地成和道的專上校舍。</t>
-  </si>
-  <si>
     <t>教育署首次正式到访树仁位于跑马地成和道的专上校舍。</t>
   </si>
   <si>
@@ -1249,9 +1243,6 @@
   </si>
   <si>
     <t>P09</t>
-  </si>
-  <si>
-    <t>Education Department specialists conducted Shue Yan’s first academic assessment, followed by a further inspection by Director K. W. J. Topley.</t>
   </si>
   <si>
     <t>教育署專家首次評核樹仁學術水平，其後教育署署長 K. W. J. Topley 再次視察。 </t>
@@ -1536,35 +1527,6 @@
     <t>P18</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Shue Yan and The University of Alabama in the United States jointly launched their first Master of Social Work programme to meet the demand </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>for professionals</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in the field.</t>
-    </r>
-  </si>
-  <si>
     <t>樹仁與美國阿拉巴馬大學合辦首個社會工作碩士課程，回應專業人才需求。</t>
   </si>
   <si>
@@ -1680,9 +1642,6 @@
   </si>
   <si>
     <t>P25</t>
-  </si>
-  <si>
-    <t>A delegation from the State Education Commission visited Shue Yan; Peking University President Ding Shisun addressed the welcoming speech.</t>
   </si>
   <si>
     <t>國家教育委員會代表團訪問樹仁；北京大學校長丁石孫在歡迎會致辭。</t>
@@ -3322,9 +3281,6 @@
     <t>P66</t>
   </si>
   <si>
-    <t>The  Faculty of Commerce underwent its five-year periodic programme review on 29 and 30 May.</t>
-  </si>
-  <si>
     <t>商學院於5月29至30日進行課程五年定期覆審。</t>
   </si>
   <si>
@@ -3404,99 +3360,76 @@
     <t>P67</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> The Hong Kong Government approved the</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+    <t>香港政府批准樹仁學院正名為香港樹仁大學，成為全港首所私立大學。</t>
+  </si>
+  <si>
+    <t>香港政府批准树仁学院正名为香港树仁大学，成为全港首所私立大学。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2006/image105.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2006/image106.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P68</t>
+  </si>
+  <si>
+    <t>Chief Executive Donald Tsang and distinguished guests attended the official ceremony celebrating Hong Kong Shue Yan University’s new name and university status.</t>
+  </si>
+  <si>
+    <t>行政長官曾蔭權與嘉賓出席香港樹仁大學正名典禮，慶祝新校名與大學地位。 </t>
+  </si>
+  <si>
+    <t>行政长官曾荫权与嘉宾出席香港树仁大学正名典礼，庆祝新校名与大学地位。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image107.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image108.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P69</t>
+  </si>
+  <si>
+    <t>The Hong Kong Institute of Education awarded honorary doctorates to Dr. Hu Hung-lick and Dr. Chung Chi-yung in recognition of their exceptional contributions to education.</t>
+  </si>
+  <si>
+    <t>香港教育學院向胡鴻烈與鍾期榮頒授榮譽博士，表揚兩人的卓越教育貢獻。 </t>
+  </si>
+  <si>
+    <t>香港教育学院向胡鸿烈与钟期荣颁授荣誉博士，表扬两人的卓越教育贡献。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image109.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image110.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P70</t>
+  </si>
+  <si>
+    <t>In 2007, Dr. Hu Hung-lick and Dr. Chung Chi-yung were named Persons of the Year of ‘Touching China’ for their lifelong dedication to education.</t>
+  </si>
+  <si>
+    <t>2007年，創辦人胡鴻烈博士及鍾期榮博士獲選為「感動中國」年度人物，以表彰二人畢生奉獻教育。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> change of title from Shue Yan College to Hong Kong Shue Yan University, making it the c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>ity’s first private university.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>香港政府批准樹仁學院正名為香港樹仁大學，成為全港首所私立大學。</t>
-  </si>
-  <si>
-    <t>香港政府批准树仁学院正名为香港树仁大学，成为全港首所私立大学。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2006/image105.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2006/image106.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P68</t>
-  </si>
-  <si>
-    <t>Chief Executive Donald Tsang and distinguished guests attended the official ceremony celebrating Hong Kong Shue Yan University’s new name and university status.</t>
-  </si>
-  <si>
-    <t>行政長官曾蔭權與嘉賓出席香港樹仁大學正名典禮，慶祝新校名與大學地位。 </t>
-  </si>
-  <si>
-    <t>行政长官曾荫权与嘉宾出席香港树仁大学正名典礼，庆祝新校名与大学地位。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image107.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image108.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P69</t>
-  </si>
-  <si>
-    <t>The Hong Kong Institute of Education awarded honorary doctorates to Dr. Hu Hung-lick and Dr. Chung Chi-yung in recognition of their exceptional contributions to education.</t>
-  </si>
-  <si>
-    <t>香港教育學院向胡鴻烈與鍾期榮頒授榮譽博士，表揚兩人的卓越教育貢獻。 </t>
-  </si>
-  <si>
-    <t>香港教育学院向胡鸿烈与钟期荣颁授荣誉博士，表扬两人的卓越教育贡献。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image109.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2007/image110.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P70</t>
-  </si>
-  <si>
-    <t>In 2007, Dr. Hu Hung-lick and Dr. Chung Chi-yung were named Persons of the Year of ‘Touching China’ for their lifelong dedication to education.</t>
-  </si>
-  <si>
-    <t>2007年，創辦人胡鴻烈博士及鍾期榮博士獲選為「感動中國」年度人物，以表彰二人畢生奉獻教育。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t>2007</t>
     </r>
     <r>
@@ -3535,16 +3468,6 @@
   </si>
   <si>
     <t>P72</t>
-  </si>
-  <si>
-    <t>The University launched its first independently offered master’s degree programme —  the Master of Social Sciences in Counselling Psychology.
-Source: Shue Yan Newsletter May 2010 Issue</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大學首次獨立開辦碩士學位課程——輔導心理學社會科學碩士。 
-來源： 《樹仁簡訊》2010年5月刊</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>大学首次独立开办硕士学位课程——辅导心理学社会科学硕士。
@@ -3642,9 +3565,6 @@
     <t>Since 2012/13, Shue Yan University has received HK$125.6 million in funding from the Quality Enhancement Support Scheme (QESS) for 13 projects. These initiatives have advanced teaching and learning, digital resources, internships and career development, artificial intelligence education, and student wellbeing.</t>
   </si>
   <si>
-    <t>仁大自2012/13年度起，獲「質素提升支援計劃」資助合共1.256億港元，推展13個項目。這些項目促進了教與學、數碼資源、實習及職涯發展、人工智能教育，以及學生身心健康。</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -3911,16 +3831,6 @@
   </si>
   <si>
     <t>P87</t>
-  </si>
-  <si>
-    <t>Shue Yan enrolled its first cohort of Master of Philosophy and Doctor of Philosophy research students.
-Source: Shue Yan Newsletter November 2017 Issue</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>樹仁招收首屆哲學碩士及哲學博士研究生。 
-來源：《樹仁簡訊》2017年11月刊</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3969,16 +3879,78 @@
     <t>2019-2020</t>
   </si>
   <si>
-    <r>
-      <t>Shue Yan received HK$20 million  from the iFREE Group to develop</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+    <t>樹仁獲iFREE集團捐款二千萬港元，建設機械人實驗室及大數據設施。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>树仁获</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> a robotics laboratory</t>
+      <t>iFREE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>集团捐款二千万港元，建设机械人实验室及大数据设施。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2019-2020/image135.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2019-2020/image136.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P89</t>
+  </si>
+  <si>
+    <t>Hong Kong Shue Yan University entered the QS Asia University Rankings for the first time in the 401–450 band, marking a new stage in its recognition in Asian higher education.</t>
+  </si>
+  <si>
+    <r>
+      <t>香港樹仁大學首次進入 QS 亞洲大學排名，位列 401–450 組別，標誌大學在亞洲高等教育界的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>認可性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>邁進新階段。 </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>香港树仁大学首次进入</t>
     </r>
     <r>
       <rPr>
@@ -3987,14 +3959,8 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> and big-data facilities. </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>樹仁獲iFREE集團捐款二千萬港元，建設機械人實驗室及大數據設施。</t>
-  </si>
-  <si>
+      <t xml:space="preserve"> QS </t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4002,7 +3968,7 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>树仁获</t>
+      <t>亚洲大学排名，位列</t>
     </r>
     <r>
       <rPr>
@@ -4011,7 +3977,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>iFREE</t>
+      <t xml:space="preserve"> 401</t>
     </r>
     <r>
       <rPr>
@@ -4019,36 +3985,36 @@
         <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
-      </rPr>
-      <t>集团捐款二千万港元，建设机械人实验室及大数据设施。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2019-2020/image135.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2019-2020/image136.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P89</t>
-  </si>
-  <si>
-    <t>Hong Kong Shue Yan University entered the QS Asia University Rankings for the first time in the 401–450 band, marking a new stage in its recognition in Asian higher education.</t>
-  </si>
-  <si>
-    <r>
-      <t>香港樹仁大學首次進入 QS 亞洲大學排名，位列 401–450 組別，標誌大學在亞洲高等教育界的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+        <charset val="134"/>
+      </rPr>
+      <t>–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">450 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
+      </rPr>
+      <t>组别，标志大学在亚洲高等教育界的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>認可性</t>
+      <t>认可性</t>
     </r>
     <r>
       <rPr>
@@ -4057,14 +4023,82 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>邁進新階段。 </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>香港树仁大学首次进入</t>
-    </r>
+      <t>迈进新阶段。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P90</t>
+  </si>
+  <si>
+    <t>The Department of Applied Data Science was established to offer Shue Yan’s first bachelor of science program.</t>
+  </si>
+  <si>
+    <t>應用數據科學學系成立，開辦樹仁首個理學學士課程。 </t>
+  </si>
+  <si>
+    <t>应用数据科学学系成立，开办树仁首个理学学士课程。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2020/image137.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2020/image138.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P91</t>
+  </si>
+  <si>
+    <t>The University celebrated President Dr. Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
+  </si>
+  <si>
+    <t>大學為校監胡鴻烈一百零一歲壽辰舉行小型慶祝會，表揚其畢生服務。</t>
+  </si>
+  <si>
+    <t>大学为校监胡鸿烈一百零一岁寿辰举行小型庆祝会，表扬其毕生服务。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image139.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image140.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P92</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021-2025</t>
+  </si>
+  <si>
+    <t>大学五年策略发展计划倡议在数字时代重塑博雅教育。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021-2025/image143.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021-2025/image144.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>P93</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2020/21, HKSYU received HK$16.4 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Arts, Culture and Technology.</t>
+  </si>
+  <si>
+    <t>2020/21 年, 樹仁獲自資專上教育提升及啟動補助金 一千六百四十萬元，發展藝術、文化及科技榮譽社會科學學士課程。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4072,7 +4106,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> QS </t>
+      <t xml:space="preserve">2020/21 </t>
     </r>
     <r>
       <rPr>
@@ -4081,7 +4115,7 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>亚洲大学排名，位列</t>
+      <t>年</t>
     </r>
     <r>
       <rPr>
@@ -4090,7 +4124,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 401</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -4098,10 +4132,210 @@
         <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
+      </rPr>
+      <t>树仁获自资专上教育提升及启动补助金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>一千六百四十万元，发展艺术、文化及科技荣誉社会科学学士课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image141.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image142.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P94</t>
+  </si>
+  <si>
+    <t>The Dr. Francis Cheung Business Analytics Research Centre was established with a donation from Dr. Francis Cheung to advance interdisciplinary big-data research and evidence-based decision-making across sectors.</t>
+  </si>
+  <si>
+    <t>由張舜堯博士捐款成立的張舜堯博士商業分析研究中心啟用，致力推動跨學科大數據研究及各界循證決策。</t>
+  </si>
+  <si>
+    <t>由张舜尧博士捐款成立的张舜尧博士商业分析研究中心启用，致力推动跨学科大数据研究及各界循证决策。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image145.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>Shue Yan launched Hong Kong’s first virtual museum of national intangible cultural heritage, digitally showcasing the Yulan Festival. This digital humanities project was selected as one of the 25 representative showcase projects at the Innotech Expo, organised by Our Hong Kong Foundation.  </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>树仁推出香港首个国家级非物质文化遗产虚拟博物馆，以数字形式展示盂兰胜会。该数字人文项目获团结香港基金主办的创科博览选为香港</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>个创科代表性展示项目之一。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image146.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image147.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P96</t>
+  </si>
+  <si>
+    <t>In 2022/23, Shue Yan received HK$19.5 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSc (Hons) in Digital Solutions for Entertainment and Game Applications.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2022/23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>年度，仁大获批自资专上教育提升及启动补助金一千九百五十万元，发展娱乐及游戏应用数码方案荣誉理学士课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image148.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image149.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P97</t>
+  </si>
+  <si>
+    <t>The Social Work Department launched a government-commissioned one-stop digital information gateway for carers, improving timely access to support information.</t>
+  </si>
+  <si>
+    <t>社会工作学系推出政府委托的一站式照顾者数码资讯闸道，改善支援资讯的及时获取。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image150.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>An interdisciplinary conference on youth-identity translated longitudinal research into practical insights for programmes, policy, and evidence-based youth development.</t>
+  </si>
+  <si>
+    <r>
+      <t>跨學科青年身份認同會議把縱向研究轉化為課程、政策及循證青年發展的實務</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>–</t>
-    </r>
+      <t>洞察</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>。 </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>跨学科青年身份认同会议把纵向研究转化为课程、政策及循证青年发展的实务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洞察</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image151.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>In 2023/24, Shue Yan received HK$14. 6 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Forensic and Investigative Psychology.</t>
+  </si>
+  <si>
+    <t>2023/24年，仁大獲批自資專上教育提升及啟動補助一千四百六十萬元，發展法證及偵緝心理學榮譽社會科學學士課程。 </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4109,7 +4343,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">450 </t>
+      <t>2023/24</t>
     </r>
     <r>
       <rPr>
@@ -4117,18 +4351,419 @@
         <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
-      </rPr>
-      <t>组别，标志大学在亚洲高等教育界的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，仁大获批自资专上教育提升及启动补助一千四百六十万元，发展法证及侦缉心理学荣誉社会科学学士课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image152.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image153.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>An AI- and VR-enabled martial arts exhibition documented Ving Tsun and Tai Chi, preserving cultural heritage and encouraging youth participation.</t>
+  </si>
+  <si>
+    <t>結合人工智能及虛擬實境的武術展覽記錄詠春與太極，保存文化並鼓勵青年參與。 </t>
+  </si>
+  <si>
+    <t>结合人工智能及虚拟实境的武术展览记录咏春与太极，保存文化并鼓励青年参与。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image154.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>The Mrs. Dorothy Koo and Dr. Ti Hua Koo Plaza, redeveloped with their donations, opened with advanced audiovisual facilities.</t>
+  </si>
+  <si>
+    <t>由顧鐵華、費肇芬捐款重建的伉儷廣場啟用，並配備先進影音設施。</t>
+  </si>
+  <si>
+    <t>由顾铁华、费肇芬捐款重建的伉俪广场启用，并配备先进影音设施。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image155.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image156.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P102</t>
+  </si>
+  <si>
+    <t>The Tin Ka Ping Teaching and Research Centre for Filial Piety opened to connect interdisciplinary research, moral education, cultural heritage, and school outreach.</t>
+  </si>
+  <si>
+    <t>田家炳孝道文化教研中心啟用，連結跨學科研究、品德教育、文化傳承及學校外展。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
+      </rPr>
+      <t>田家炳孝道文化教研中心启用，连结跨学科研究、品德教育、文化传承及学校外展。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image157.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image158.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P103</t>
+  </si>
+  <si>
+    <t>The University launched Hong Kong’s first one-year International Foundation Year Programme for international students, with a certificate awarded upon completion.</t>
+  </si>
+  <si>
+    <t>大學推出香港首個專為國際學生而設的一年制大學先修課程證書。</t>
+  </si>
+  <si>
+    <t>大学推出香港首个专为国际学生而设的一年制大学先修课程证书。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image159.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image160.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P104</t>
+  </si>
+  <si>
+    <t>Yang Wei from the Department of Sociology became Shue Yan’s first Doctor of Philosophy graduate, marking a milestone for the Graduate School.</t>
+  </si>
+  <si>
+    <t>社會學系楊薇成為樹仁首位哲學博士畢業生，標誌研究院重要里程碑。 </t>
+  </si>
+  <si>
+    <t>社会学系杨薇成为树仁首位哲学博士毕业生，标志研究院重要里程碑。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image161.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image162.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P105</t>
+  </si>
+  <si>
+    <t>An interdisciplinary esports project promoted youth empowerment while addressing gaming addiction through psychological, social, business, and policy research.</t>
+  </si>
+  <si>
+    <t>跨學科電競項目透過心理、社會、商業及政策研究，在應對遊戲成癮同時促進青年賦權。 </t>
+  </si>
+  <si>
+    <t>跨学科电竞项目透过心理、社会、商业及政策研究，在应对游戏成瘾同时促进青年赋权。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image163.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P106</t>
+  </si>
+  <si>
+    <t>The Emotion World project gamified evidence-based social-emotional learning and invited students to design AI-assisted characters to promote wellbeing education.</t>
+  </si>
+  <si>
+    <t>「情緒世界」把循證社交情緒學習遊戲化，並邀請學生設計人工智能輔助角色，推動福祉教育。 </t>
+  </si>
+  <si>
+    <t>「情绪世界」把循证社交情绪学习游戏化，并邀请学生设计人工智能辅助角色，推动福祉教育。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image164.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P107</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Bridging Grey Digital Divide and diversity in older ICT users post-COVID project advanced research on older adults’ use of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>technology and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> promoted age-inclusive digital innovation. </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨越灰色数码鸿沟研究长者科技使用，推动年龄共融的数码创新。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image165.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P108</t>
+  </si>
+  <si>
+    <t>A longitudinal study of more than 8,000 participants examined resilience across adulthood to inform family, organisational, and public policy.</t>
+  </si>
+  <si>
+    <t>追蹤逾八千人的縱向研究，探討成年各階段的韌性，為家庭、機構及公共政策提供依據。</t>
+  </si>
+  <si>
+    <t>追踪逾八千人的纵向研究，探讨成年各阶段的韧性，为家庭、机构及公共政策提供依据。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image166.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P109</t>
+  </si>
+  <si>
+    <t>Founding President Dr. Hu Hung-lick passed away at the age of 105; the University community held a funeral and memorial services honouring his legacy.</t>
+  </si>
+  <si>
+    <t>創校校監胡鴻烈於一百零五歲逝世，大學社群舉行喪禮及追思會，紀念其貢獻。 </t>
+  </si>
+  <si>
+    <t>创校校监胡鸿烈于一百零五岁逝世，大学社群举行丧礼及追思会，纪念其贡献。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image167.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image168.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P111</t>
+  </si>
+  <si>
+    <t>Shue Yan University participated in a special exhibition at the Guangdong Museum, creating an extension display on digital architectural heritage art.</t>
+  </si>
+  <si>
+    <t>仁大参与广东省博物馆特展，策划数码建筑遗产艺术延伸展区。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image170.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image171.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P112</t>
+  </si>
+  <si>
+    <t>Shue Yan University supported the Hong Kong Maritime Museum’s immersive VR archaeology exhibition “Voyage into Shu”, providing academic and curatorial advice.</t>
+  </si>
+  <si>
+    <t>仁大支持香港海事博物館「浮海探蜀」沉浸式考古VR展，並提供學術與策展顧問。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>仁大支持香港海事博物馆「浮海探蜀」沉浸式考古</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>VR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>展，并提供学术与策展顾问。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image172.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image173.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P110</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu fai-chung as President.</t>
+  </si>
+  <si>
+    <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
+  </si>
+  <si>
+    <t>香港树仁大学委任长期服务的常务副校监胡怀中出任校长。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025-2026/image169.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P113</t>
+  </si>
+  <si>
+    <t>In 2024/25, Shue Yan University received HK$25.1 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary education to develop an applied degree in Surveying and Dispute Resolution.</t>
+  </si>
+  <si>
+    <t>2024/2025年，仁大獲批自資專上教育提升及啟動補助金兩千五百一十萬元，發展測量及爭議解決學應用學位課程。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2024/2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>认可性</t>
-    </r>
+      <t>年，仁大获批自资专上教育提升及启动补助金两千五百一十万元，发展测量及争议解决学应用学位课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P114</t>
+  </si>
+  <si>
+    <t>Shue Yan launched a digital humanities project using a virtual-reality and a mixed-reality platform to digitally document, transmit, and promote Cheung Chau’s Jiao Festival, which is a national intangible cultural heritage.</t>
+  </si>
+  <si>
+    <t>仁大开展一项数码人文项目，运用虚拟现实和混合实境平台数字化记录、传承并推广长洲太平清醮这项国家级非物质文化遗产。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image174.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image175.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P115</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A one-stop internship platform </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>began its</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trial operation, integrating e-portfolios, employer connections, learning resources, and AI-assisted job matching.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>一站式實習平台投入試行，整合電子履歷、僱主聯繫、學習資源及人工智能職位配對。</t>
+  </si>
+  <si>
+    <t>一站式实习平台投入试行，整合电子履历、雇主联系、学习资源及人工智能职位配对。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image176.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image177.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P116</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Shue Yan rose to 360th in the QS Asia rankings and entered the QS World University Rankings  in the band of 1001–1200, becoming the first private university in Hong Kong to be listed.</t>
+  </si>
+  <si>
+    <t>仁大在QS亞洲排名升至第360位，並首登QS世界大學排名1001至1200位，成為首所上榜的香港私立大學。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4136,88 +4771,8 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>迈进新阶段。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P90</t>
-  </si>
-  <si>
-    <t>The Department of Applied Data Science was established to offer Shue Yan’s first bachelor of science program.</t>
-  </si>
-  <si>
-    <t>應用數據科學學系成立，開辦樹仁首個理學學士課程。 </t>
-  </si>
-  <si>
-    <t>应用数据科学学系成立，开办树仁首个理学学士课程。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2020/image137.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2020/image138.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P91</t>
-  </si>
-  <si>
-    <t>The University celebrated President Dr. Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
-  </si>
-  <si>
-    <t>大學為校監胡鴻烈一百零一歲壽辰舉行小型慶祝會，表揚其畢生服務。</t>
-  </si>
-  <si>
-    <t>大学为校监胡鸿烈一百零一岁寿辰举行小型庆祝会，表扬其毕生服务。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image139.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image140.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P92</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021-2025</t>
-  </si>
-  <si>
-    <t>The University’s Five-year Strategic Plan   advocates reinventing liberal arts education for the digital era.</t>
-  </si>
-  <si>
-    <t>大學五年策略發展計劃倡議在數字時代重塑博雅教育。</t>
-  </si>
-  <si>
-    <t>大学五年策略发展计划倡议在数字时代重塑博雅教育。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021-2025/image143.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021-2025/image144.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>P93</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>In 2020/21, HKSYU received HK$16.4 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Arts, Culture and Technology.</t>
-  </si>
-  <si>
-    <t>2020/21 年, 樹仁獲自資專上教育提升及啟動補助金 一千六百四十萬元，發展藝術、文化及科技榮譽社會科學學士課程。</t>
-  </si>
-  <si>
+      <t>仁大在</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4225,7 +4780,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">2020/21 </t>
+      <t>QS</t>
     </r>
     <r>
       <rPr>
@@ -4234,7 +4789,7 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>年</t>
+      <t>亚洲排名升至第</t>
     </r>
     <r>
       <rPr>
@@ -4243,7 +4798,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t>360</t>
     </r>
     <r>
       <rPr>
@@ -4252,7 +4807,7 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>树仁获自资专上教育提升及启动补助金</t>
+      <t>位，并首登</t>
     </r>
     <r>
       <rPr>
@@ -4261,7 +4816,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>QS</t>
     </r>
     <r>
       <rPr>
@@ -4270,43 +4825,17 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>一千六百四十万元，发展艺术、文化及科技荣誉社会科学学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image141.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image142.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P94</t>
-  </si>
-  <si>
-    <t>The Dr. Francis Cheung Business Analytics Research Centre was established with a donation from Dr. Francis Cheung to advance interdisciplinary big-data research and evidence-based decision-making across sectors.</t>
-  </si>
-  <si>
-    <t>由張舜堯博士捐款成立的張舜堯博士商業分析研究中心啟用，致力推動跨學科大數據研究及各界循證決策。</t>
-  </si>
-  <si>
-    <t>由张舜尧博士捐款成立的张舜尧博士商业分析研究中心启用，致力推动跨学科大数据研究及各界循证决策。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image145.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P95</t>
-  </si>
-  <si>
-    <t>Shue Yan launched Hong Kong’s first virtual museum of national intangible cultural heritage, digitally showcasing the Yulan Festival. This digital humanities project was selected as one of the 25 representative showcase projects at the Innotech Expo, organised by Our Hong Kong Foundation.  </t>
-  </si>
-  <si>
-    <t>樹仁推出香港首個國家級非物質文化遺產虛擬博物館，以數字形式展示盂蘭勝會。該數字人文項目獲團結香港基金主辦的創科博覽選為香港25個創科代表性展示項目之一。 </t>
-  </si>
-  <si>
+      <t>世界大学排名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1001</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4314,7 +4843,7 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>树仁推出香港首个国家级非物质文化遗产虚拟博物馆，以数字形式展示盂兰胜会。该数字人文项目获团结香港基金主办的创科博览选为香港</t>
+      <t>至</t>
     </r>
     <r>
       <rPr>
@@ -4323,7 +4852,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>25</t>
+      <t>1200</t>
     </r>
     <r>
       <rPr>
@@ -4332,138 +4861,32 @@
         <rFont val="微软雅黑"/>
         <family val="2"/>
       </rPr>
-      <t>个创科代表性展示项目之一。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image146.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image147.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P96</t>
-  </si>
-  <si>
-    <t>In 2022/23, Shue Yan received HK$19.5 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSc (Hons) in Digital Solutions for Entertainment and Game Applications.</t>
-  </si>
-  <si>
-    <t>2022/23 年度，仁大獲批自資專上教育提升及啟動補助金一千九百五十萬元，發展娛樂及遊戲應用數碼方案榮譽理學士課程。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
+      <t>位，成为首所上榜的香港私立大学。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image178.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image179.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P117</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shue Yan established its fourth Faculty, the Faculty of Communication, Information and Creative Industries. The faculty comprises the Department of Journalism and Communication and the Department of Data Science and Digital Innovation, formerly known as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">2022/23 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>年度，仁大获批自资专上教育提升及启动补助金一千九百五十万元，发展娱乐及游戏应用数码方案荣誉理学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image148.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image149.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P97</t>
-  </si>
-  <si>
-    <t>The Social Work Department launched a government-commissioned one-stop digital information gateway for carers, improving timely access to support information.</t>
-  </si>
-  <si>
-    <t>社會工作學系推出政府委託的一站式照顧者數碼資訊閘道，改善支援資訊的及時獲取。</t>
-  </si>
-  <si>
-    <t>社会工作学系推出政府委托的一站式照顾者数码资讯闸道，改善支援资讯的及时获取。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image150.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P98</t>
-  </si>
-  <si>
-    <t>An interdisciplinary conference on youth-identity translated longitudinal research into practical insights for programmes, policy, and evidence-based youth development.</t>
-  </si>
-  <si>
-    <r>
-      <t>跨學科青年身份認同會議把縱向研究轉化為課程、政策及循證青年發展的實務</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>洞察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>。 </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>跨学科青年身份认同会议把纵向研究转化为课程、政策及循证青年发展的实务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>洞察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image151.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P99</t>
-  </si>
-  <si>
-    <t>In 2023/24, Shue Yan received HK$14. 6 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Forensic and Investigative Psychology.</t>
-  </si>
-  <si>
-    <t>2023/24年，仁大獲批自資專上教育提升及啟動補助一千四百六十萬元，發展法證及偵緝心理學榮譽社會科學學士課程。 </t>
-  </si>
-  <si>
+      <t>the Department of Applied Data Science</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4471,574 +4894,11 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>2023/24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，仁大获批自资专上教育提升及启动补助一千四百六十万元，发展法证及侦缉心理学荣誉社会科学学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image152.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image153.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P100</t>
-  </si>
-  <si>
-    <t>An AI- and VR-enabled martial arts exhibition documented Ving Tsun and Tai Chi, preserving cultural heritage and encouraging youth participation.</t>
-  </si>
-  <si>
-    <t>結合人工智能及虛擬實境的武術展覽記錄詠春與太極，保存文化並鼓勵青年參與。 </t>
-  </si>
-  <si>
-    <t>结合人工智能及虚拟实境的武术展览记录咏春与太极，保存文化并鼓励青年参与。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image154.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P101</t>
-  </si>
-  <si>
-    <t>The Mrs. Dorothy Koo and Dr. Ti Hua Koo Plaza, redeveloped with their donations, opened with advanced audiovisual facilities.</t>
-  </si>
-  <si>
-    <t>由顧鐵華、費肇芬捐款重建的伉儷廣場啟用，並配備先進影音設施。</t>
-  </si>
-  <si>
-    <t>由顾铁华、费肇芬捐款重建的伉俪广场启用，并配备先进影音设施。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image155.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image156.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P102</t>
-  </si>
-  <si>
-    <t>The Tin Ka Ping Teaching and Research Centre for Filial Piety opened to connect interdisciplinary research, moral education, cultural heritage, and school outreach.</t>
-  </si>
-  <si>
-    <t>田家炳孝道文化教研中心啟用，連結跨學科研究、品德教育、文化傳承及學校外展。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>田家炳孝道文化教研中心启用，连结跨学科研究、品德教育、文化传承及学校外展。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image157.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image158.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P103</t>
-  </si>
-  <si>
-    <t>The University launched Hong Kong’s first one-year International Foundation Year Programme for international students, with a certificate awarded upon completion.</t>
-  </si>
-  <si>
-    <t>大學推出香港首個專為國際學生而設的一年制大學先修課程證書。</t>
-  </si>
-  <si>
-    <t>大学推出香港首个专为国际学生而设的一年制大学先修课程证书。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image159.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image160.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P104</t>
-  </si>
-  <si>
-    <t>Yang Wei from the Department of Sociology became Shue Yan’s first Doctor of Philosophy graduate, marking a milestone for the Graduate School.</t>
-  </si>
-  <si>
-    <t>社會學系楊薇成為樹仁首位哲學博士畢業生，標誌研究院重要里程碑。 </t>
-  </si>
-  <si>
-    <t>社会学系杨薇成为树仁首位哲学博士毕业生，标志研究院重要里程碑。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image161.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image162.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P105</t>
-  </si>
-  <si>
-    <t>An interdisciplinary esports project promoted youth empowerment while addressing gaming addiction through psychological, social, business, and policy research.</t>
-  </si>
-  <si>
-    <t>跨學科電競項目透過心理、社會、商業及政策研究，在應對遊戲成癮同時促進青年賦權。 </t>
-  </si>
-  <si>
-    <t>跨学科电竞项目透过心理、社会、商业及政策研究，在应对游戏成瘾同时促进青年赋权。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image163.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P106</t>
-  </si>
-  <si>
-    <t>The Emotion World project gamified evidence-based social-emotional learning and invited students to design AI-assisted characters to promote wellbeing education.</t>
-  </si>
-  <si>
-    <t>「情緒世界」把循證社交情緒學習遊戲化，並邀請學生設計人工智能輔助角色，推動福祉教育。 </t>
-  </si>
-  <si>
-    <t>「情绪世界」把循证社交情绪学习游戏化，并邀请学生设计人工智能辅助角色，推动福祉教育。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image164.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P107</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The Bridging Grey Digital Divide and diversity in older ICT users post-COVID project advanced research on older adults’ use of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>technology and</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> promoted age-inclusive digital innovation. </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>跨越灰色數碼鴻溝研究長者科技使用，推動年齡共融的數碼創新。 </t>
-  </si>
-  <si>
-    <t>跨越灰色数码鸿沟研究长者科技使用，推动年龄共融的数码创新。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image165.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P108</t>
-  </si>
-  <si>
-    <t>A longitudinal study of more than 8,000 participants examined resilience across adulthood to inform family, organisational, and public policy.</t>
-  </si>
-  <si>
-    <t>追蹤逾八千人的縱向研究，探討成年各階段的韌性，為家庭、機構及公共政策提供依據。</t>
-  </si>
-  <si>
-    <t>追踪逾八千人的纵向研究，探讨成年各阶段的韧性，为家庭、机构及公共政策提供依据。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image166.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P109</t>
-  </si>
-  <si>
-    <t>Founding President Dr. Hu Hung-lick passed away at the age of 105; the University community held a funeral and memorial services honouring his legacy.</t>
-  </si>
-  <si>
-    <t>創校校監胡鴻烈於一百零五歲逝世，大學社群舉行喪禮及追思會，紀念其貢獻。 </t>
-  </si>
-  <si>
-    <t>创校校监胡鸿烈于一百零五岁逝世，大学社群举行丧礼及追思会，纪念其贡献。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image167.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image168.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P111</t>
-  </si>
-  <si>
-    <t>Shue Yan University participated in a special exhibition at the Guangdong Museum, creating an extension display on digital architectural heritage art.</t>
-  </si>
-  <si>
-    <t>仁大參與廣東省博物館特展，策劃數碼建築遺產藝術延伸展區。 </t>
-  </si>
-  <si>
-    <t>仁大参与广东省博物馆特展，策划数码建筑遗产艺术延伸展区。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image170.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image171.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P112</t>
-  </si>
-  <si>
-    <t>Shue Yan University supported the Hong Kong Maritime Museum’s immersive VR archaeology exhibition “Voyage into Shu”, providing academic and curatorial advice.</t>
-  </si>
-  <si>
-    <t>仁大支持香港海事博物館「浮海探蜀」沉浸式考古VR展，並提供學術與策展顧問。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>仁大支持香港海事博物馆「浮海探蜀」沉浸式考古</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>VR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>展，并提供学术与策展顾问。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image172.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image173.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P110</t>
-  </si>
-  <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
-    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu fai-chung as President.</t>
-  </si>
-  <si>
-    <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
-  </si>
-  <si>
-    <t>香港树仁大学委任长期服务的常务副校监胡怀中出任校长。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025-2026/image169.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P113</t>
-  </si>
-  <si>
-    <t>In 2024/25, Shue Yan University received HK$25.1 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary education to develop an applied degree in Surveying and Dispute Resolution.</t>
-  </si>
-  <si>
-    <t>2024/2025年，仁大獲批自資專上教育提升及啟動補助金兩千五百一十萬元，發展測量及爭議解決學應用學位課程。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>2024/2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，仁大获批自资专上教育提升及启动补助金两千五百一十万元，发展测量及争议解决学应用学位课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P114</t>
-  </si>
-  <si>
-    <t>Shue Yan launched a digital humanities project using a virtual-reality and a mixed-reality platform to digitally document, transmit, and promote Cheung Chau’s Jiao Festival, which is a national intangible cultural heritage.</t>
-  </si>
-  <si>
-    <t>仁大開展一項數碼人文項目，運用虛擬現實和混合實境平台數字化記錄、傳承並推廣長洲太平清醮這項國家級非物質文化遺產。</t>
-  </si>
-  <si>
-    <t>仁大开展一项数码人文项目，运用虚拟现实和混合实境平台数字化记录、传承并推广长洲太平清醮这项国家级非物质文化遗产。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image174.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image175.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P115</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A one-stop internship platform </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>began its</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> trial operation, integrating e-portfolios, employer connections, learning resources, and AI-assisted job matching.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>一站式實習平台投入試行，整合電子履歷、僱主聯繫、學習資源及人工智能職位配對。</t>
-  </si>
-  <si>
-    <t>一站式实习平台投入试行，整合电子履历、雇主联系、学习资源及人工智能职位配对。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image176.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image177.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P116</t>
-  </si>
-  <si>
-    <t>2026-2027</t>
-  </si>
-  <si>
-    <t>Shue Yan rose to 360th in the QS Asia rankings and entered the QS World University Rankings  in the band of 1001–1200, becoming the first private university in Hong Kong to be listed.</t>
-  </si>
-  <si>
-    <t>仁大在QS亞洲排名升至第360位，並首登QS世界大學排名1001至1200位，成為首所上榜的香港私立大學。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>仁大在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>QS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>亚洲排名升至第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>360</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>位，并首登</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>QS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>世界大学排名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1001</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>位，成为首所上榜的香港私立大学。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image178.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image179.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P117</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Shue Yan established its fourth Faculty, the Faculty of Communication, Information and Creative Industries. The faculty comprises the Department of Journalism and Communication and the Department of Data Science and Digital Innovation, formerly known as </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Department of Applied Data Science</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t>.</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>仁大成立第四個學院——傳播、資訊及創意產業學院。該學院由新聞與傳播學系，以及前稱應用數據科學的數據科學及數碼創新學系組成。</t>
-  </si>
-  <si>
     <t>仁大成立第四个学院——传播、资讯及创意产业学院。该学院由新闻与传播学系，以及前称应用数据科学的数据科学及数码创新学系组成。</t>
   </si>
   <si>
@@ -5046,12 +4906,6 @@
   </si>
   <si>
     <t>2026-2031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shue Yan’s 2026-2031 Five-year Strategic Plan: Enhancing global competence through a digitally enabled liberal arts education. The Strategic Plan ADORN aims to amplify digital competence and interdisciplinarity, develop strategic areas of excellence with social impact optimize engagement with communities and professional sectors, renew campus facilities with digital infrastructure and sustainable practices, as well as nurture glocal citizens through cultural education. </t>
-  </si>
-  <si>
-    <t>仁大的五年(2026-2031)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數碼基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
   </si>
   <si>
     <r>
@@ -5759,6 +5613,166 @@
   </si>
   <si>
     <t>胡鴻烈與鐘期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Education Department's specialists made its first formal visit to Shue Yan's post-secondary campus on Sing Woo Road, Happy Valley.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Education Department's specialists conducted Shue Yan’s first academic assessment, followed by a further inspection by Director K. W. J. Topley.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育署首次派專家正式到訪樹仁位於跑馬地成和道的專上校舍。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Shue Yan and the University of Alabama in the United States jointly launched their first Master of Social Work programme to meet the demand </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>for professionals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the field.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A delegation from the State Education Commission visited Shue Yan; Peking University President Ding Shisun gave the welcoming speech.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>The Hong Kong Government approved the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> change of title from Shue Yan College to Hong Kong Shue Yan University, making it the c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ity’s first private university.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Faculty of Commerce underwent its five-year periodic programme review on 29 and 30 May.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The University launched its first independently offered master’s degree programme —  the Master of Social Sciences in Counselling Psychology.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大學首次獨立開辦碩士學位課程——輔導心理學社會科學碩士。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大自2012/13年度起，獲「質素提升支援計劃」資助合共1.256億港元，推展13個項目。這些項目促進了教與學、數字資源、實習及職涯發展、人工智能教育，以及學生身心健康。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shue Yan enrolled its first cohort of Master of Philosophy and Doctor of Philosophy research students.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁招收首屆哲學碩士及哲學博士研究生。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Shue Yan received HK$20 million from the iFREE Group to develop</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a robotics laboratory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and big-data facilities. </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The University’s Five-year Strategic Plan advocates reinventing liberal arts education for the digital era.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大學五年策略發展計劃倡議在數字時代重塑博雅教育。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁推出香港首個國家級非物質文化遺產虛擬博物館，以數字形式展示盂蘭勝會。該數字人文項目獲團結香港基金主辦的創科博覽選為香港25個創科代表性展示項目之一。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022/23 年度，仁大獲批自資專上教育提升及啟動補助金一千九百五十萬元，發展娛樂及遊戲應用數字方案榮譽理學士課程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>社會工作學系推出政府委託的一站式照顧者數字資訊閘道，改善支援資訊的及時獲取。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Shue Yan’s 2026-2031 Five-year Strategic Plan: Enhancing global competence through a digitally enabled liberal arts education. The Strategic Plan ADORN aims to amplify digital competence and interdisciplinarity, develop strategic areas of excellence with social impact, optimize engagement with communities and professional sectors, renew campus facilities with digital infrastructure and sustainable practices, as well as nurture glocal citizens through cultural education. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨越灰色數字鴻溝研究長者科技使用，推動年齡共融的數字創新。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大參與廣東省博物館特展，策劃數字建築遺產藝術延伸展區。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大開展一項數字人文項目，運用虛擬現實和混合實境平台數字化記錄、傳承並推廣長洲太平清醮這項國家級非物質文化遺產。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大成立第四個學院——傳播、資訊及創意產業學院。該學院由新聞與傳播學系，以及前稱應用數據科學的數據科學及數字創新學系組成。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大的五年(2026-2031)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數字基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -5766,7 +5780,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="45">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5982,12 +5996,6 @@
     </font>
     <font>
       <sz val="9.5"/>
-      <color rgb="FF262626"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -6128,7 +6136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6233,11 +6241,11 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6245,25 +6253,22 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6611,888 +6616,888 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="91.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="36">
         <v>1949</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="91.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="41">
+      <c r="B3" s="40">
         <v>1955</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="40" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="79.8">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="36">
         <v>1966</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="91.2">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="40">
         <v>1971</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="91.2">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="36">
         <v>1972</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="H6" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="40">
         <v>1976</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="36">
         <v>1977</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="37"/>
+      <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="68.400000000000006">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="40">
         <v>1978</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="40" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="68.400000000000006">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="36">
         <v>1979</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="36" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="40">
         <v>1980</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="41"/>
+      <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="79.8">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="36">
         <v>1982</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="46" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="45" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="38" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="39" t="s">
+      <c r="H12" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="36" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.8">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="40">
         <v>1983</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="45" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F13" s="42" t="s">
+      <c r="E13" s="44" t="s">
+        <v>999</v>
+      </c>
+      <c r="F13" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="41"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="68.400000000000006">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="36">
         <v>1985</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="36" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="40">
         <v>1986</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="43" t="s">
+      <c r="G15" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="41"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="57">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="36">
         <v>1987</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="46" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F16" s="39" t="s">
+      <c r="E16" s="45" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F16" s="38" t="s">
         <v>120</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="36" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="40">
         <v>1988</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="G17" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="I17" s="41" t="s">
+      <c r="I17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="40" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.8">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="36">
         <v>1990</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="I18" s="37" t="s">
+      <c r="I18" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="37" t="s">
+      <c r="J18" s="36" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="40">
         <v>1995</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="J19" s="41" t="s">
+      <c r="J19" s="40" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="36">
         <v>1996</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="I20" s="37" t="s">
+      <c r="I20" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="40">
         <v>1999</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E21" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="43" t="s">
+      <c r="G21" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="41" t="s">
+      <c r="I21" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J21" s="40" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="36">
         <v>2000</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37" t="s">
+      <c r="I22" s="36"/>
+      <c r="J22" s="36" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="40">
         <v>2001</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="G23" s="43" t="s">
+      <c r="G23" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="I23" s="41" t="s">
+      <c r="I23" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="J23" s="41" t="s">
+      <c r="J23" s="40" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="36">
         <v>2002</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="I24" s="37" t="s">
+      <c r="I24" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="36" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="41">
+      <c r="B25" s="40">
         <v>2003</v>
       </c>
-      <c r="C25" s="43" t="s">
+      <c r="C25" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="F25" s="42" t="s">
+      <c r="F25" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="43" t="s">
+      <c r="G25" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="H25" s="42" t="s">
+      <c r="H25" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="I25" s="41" t="s">
+      <c r="I25" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="J25" s="41" t="s">
+      <c r="J25" s="40" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="68.400000000000006">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="36">
         <v>2004</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="H26" s="39" t="s">
+      <c r="H26" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="I26" s="37" t="s">
+      <c r="I26" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="J26" s="37" t="s">
+      <c r="J26" s="36" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="41">
+      <c r="B27" s="40">
         <v>2005</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="E27" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="G27" s="43" t="s">
+      <c r="G27" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="H27" s="42" t="s">
+      <c r="H27" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="I27" s="41" t="s">
+      <c r="I27" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="J27" s="41" t="s">
+      <c r="J27" s="40" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="36">
         <v>2006</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="40" t="s">
+      <c r="E28" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="39" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G28" s="40" t="s">
+      <c r="F28" s="38" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G28" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="H28" s="39" t="s">
+      <c r="H28" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="I28" s="37" t="s">
+      <c r="I28" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J28" s="37" t="s">
+      <c r="J28" s="36" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="40">
         <v>2007</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D29" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G29" s="43" t="s">
+      <c r="F29" s="41" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G29" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="H29" s="42" t="s">
+      <c r="H29" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="J29" s="41" t="s">
+      <c r="J29" s="40" t="s">
         <v>220</v>
       </c>
     </row>
@@ -7578,7 +7583,7 @@
         <v>228</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1031</v>
+        <v>1007</v>
       </c>
       <c r="F2" s="28" t="s">
         <v>229</v>
@@ -7590,7 +7595,7 @@
         <v>231</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1030</v>
+        <v>1006</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>232</v>
@@ -7614,11 +7619,11 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>1020</v>
+        <v>996</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>1021</v>
+        <v>997</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>236</v>
@@ -7677,7 +7682,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>1029</v>
+        <v>1005</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>246</v>
@@ -7709,7 +7714,7 @@
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>1022</v>
+        <v>998</v>
       </c>
       <c r="I6" s="14" t="s">
         <v>251</v>
@@ -7797,21 +7802,21 @@
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>266</v>
+        <v>1008</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>267</v>
+        <v>1010</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>268</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -7822,28 +7827,28 @@
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>272</v>
+        <v>1009</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -7854,25 +7859,25 @@
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -7881,25 +7886,25 @@
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -7911,28 +7916,28 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -7943,28 +7948,28 @@
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -7975,28 +7980,28 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8007,28 +8012,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>1019</v>
+        <v>995</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8039,28 +8044,28 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8071,28 +8076,28 @@
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8103,28 +8108,28 @@
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
-      <c r="D19" s="36" t="s">
-        <v>323</v>
+      <c r="D19" s="11" t="s">
+        <v>1011</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8135,28 +8140,28 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8167,28 +8172,28 @@
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8199,25 +8204,25 @@
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8229,25 +8234,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8259,28 +8264,28 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8291,28 +8296,28 @@
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8323,25 +8328,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>363</v>
+        <v>1012</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8352,25 +8357,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8382,28 +8387,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8414,25 +8419,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8444,28 +8449,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8476,25 +8481,25 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8506,28 +8511,28 @@
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8538,25 +8543,25 @@
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8568,25 +8573,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8598,28 +8603,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8630,28 +8635,28 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8662,25 +8667,25 @@
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8692,28 +8697,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -8724,28 +8729,28 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -8756,25 +8761,25 @@
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -8786,25 +8791,25 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -8816,28 +8821,28 @@
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>1028</v>
+        <v>1004</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -8848,28 +8853,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -8880,25 +8885,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -8910,22 +8915,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8938,28 +8943,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -8970,28 +8975,28 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9002,25 +9007,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9032,25 +9037,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9062,25 +9067,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9092,28 +9097,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9124,25 +9129,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9154,25 +9159,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9184,25 +9189,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9214,57 +9219,57 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9276,25 +9281,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9306,25 +9311,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9336,87 +9341,87 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9428,25 +9433,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9458,25 +9463,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9488,25 +9493,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9518,25 +9523,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9548,25 +9553,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9578,25 +9583,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>583</v>
+        <v>1014</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9608,28 +9613,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>588</v>
+        <v>1013</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9640,28 +9645,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9672,28 +9677,28 @@
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9704,25 +9709,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9734,28 +9739,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9764,27 +9769,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="55.2">
+    <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>617</v>
+        <v>1015</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>618</v>
+        <v>1016</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -9796,25 +9801,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9826,28 +9831,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -9858,28 +9863,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>634</v>
+        <v>1017</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -9890,22 +9895,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -9918,28 +9923,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -9950,25 +9955,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -9980,28 +9985,28 @@
     </row>
     <row r="80" spans="1:14" ht="28.8">
       <c r="A80" s="2" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10012,25 +10017,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10042,25 +10047,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10072,22 +10077,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10099,88 +10104,88 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10191,60 +10196,60 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="55.2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>698</v>
+        <v>1018</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>699</v>
+        <v>1019</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10255,28 +10260,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>705</v>
+        <v>1020</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10287,22 +10292,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10315,28 +10320,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10347,677 +10352,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>728</v>
+        <v>1021</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>729</v>
+        <v>1022</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>747</v>
+        <v>1023</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>753</v>
+        <v>1024</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>754</v>
+        <v>737</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>756</v>
+        <v>739</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>759</v>
+        <v>1025</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>814</v>
+        <v>1027</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>830</v>
+        <v>1028</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>836</v>
+        <v>816</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11029,148 +11034,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>853</v>
+        <v>1029</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>854</v>
+        <v>833</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>856</v>
+        <v>835</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>857</v>
+        <v>836</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>858</v>
+        <v>837</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>861</v>
+        <v>840</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>863</v>
+        <v>842</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>864</v>
+        <v>843</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>865</v>
+        <v>844</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>864</v>
+        <v>843</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>872</v>
+        <v>1030</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>873</v>
+        <v>851</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11178,45 +11183,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>874</v>
+        <v>852</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>875</v>
+        <v>853</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>876</v>
+        <v>1026</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>877</v>
+        <v>1031</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>880</v>
+        <v>856</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>881</v>
+        <v>857</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>882</v>
+        <v>858</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>883</v>
+        <v>859</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11415,103 +11420,103 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>884</v>
+        <v>860</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>888</v>
+        <v>864</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>889</v>
+        <v>865</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>890</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>891</v>
+        <v>867</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>892</v>
+        <v>868</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>893</v>
+        <v>869</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>894</v>
+        <v>870</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>895</v>
+        <v>871</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>897</v>
+        <v>873</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>898</v>
+        <v>874</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>903</v>
+        <v>879</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>908</v>
+        <v>884</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>909</v>
+        <v>885</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>910</v>
+        <v>886</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>911</v>
+        <v>887</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11522,22 +11527,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>914</v>
+        <v>890</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>915</v>
+        <v>891</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>916</v>
+        <v>892</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>917</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11548,22 +11553,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>918</v>
+        <v>894</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>919</v>
+        <v>895</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>920</v>
+        <v>896</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>921</v>
+        <v>897</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11574,22 +11579,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>924</v>
+        <v>900</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>925</v>
+        <v>901</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>928</v>
+        <v>904</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -11600,22 +11605,22 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>930</v>
+        <v>906</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>931</v>
+        <v>907</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>933</v>
+        <v>909</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>934</v>
+        <v>910</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>935</v>
+        <v>911</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
@@ -11626,48 +11631,48 @@
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>938</v>
+        <v>914</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>939</v>
+        <v>915</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>945</v>
+        <v>921</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>946</v>
+        <v>922</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>947</v>
+        <v>923</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>948</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
@@ -11678,74 +11683,74 @@
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>949</v>
+        <v>925</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>950</v>
+        <v>926</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>951</v>
+        <v>927</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>956</v>
+        <v>932</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>958</v>
+        <v>934</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>961</v>
+        <v>937</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>962</v>
+        <v>938</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>963</v>
+        <v>939</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
@@ -11756,48 +11761,48 @@
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>973</v>
+        <v>949</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>974</v>
+        <v>950</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>975</v>
+        <v>951</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>976</v>
+        <v>952</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>977</v>
+        <v>953</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>978</v>
+        <v>954</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>982</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
@@ -11805,129 +11810,129 @@
         <v>220</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>983</v>
+        <v>959</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>985</v>
+        <v>961</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>986</v>
+        <v>962</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>987</v>
+        <v>963</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>988</v>
+        <v>964</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>989</v>
+        <v>965</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>990</v>
+        <v>966</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>993</v>
+        <v>969</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>994</v>
+        <v>970</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>995</v>
+        <v>971</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>996</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>997</v>
+        <v>973</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>998</v>
+        <v>974</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>999</v>
+        <v>975</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1000</v>
+        <v>976</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>1001</v>
+        <v>977</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>1002</v>
+        <v>978</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>1003</v>
+        <v>979</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1004</v>
+        <v>980</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1005</v>
+        <v>981</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1006</v>
+        <v>982</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1007</v>
+        <v>983</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1008</v>
+        <v>984</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1009</v>
+        <v>985</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1010</v>
+        <v>986</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>1011</v>
+        <v>987</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>1012</v>
+        <v>988</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1013</v>
+        <v>989</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1014</v>
+        <v>990</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1015</v>
+        <v>991</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1016</v>
+        <v>992</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>1017</v>
+        <v>993</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>1018</v>
+        <v>994</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12020,23 +12025,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12218,25 +12206,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12252,4 +12239,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9755D3B3-7960-4184-B99E-6A3910944FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -12025,6 +12025,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12206,24 +12223,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12239,22 +12257,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9755D3B3-7960-4184-B99E-6A3910944FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4751DB0F-34BD-4C5A-9FB1-A8E9F45E0432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1033">
   <si>
     <t>id</t>
   </si>
@@ -214,15 +214,9 @@
     <t>兩人移居香港：走向教育與公共服務</t>
   </si>
   <si>
-    <t xml:space="preserve">1955年前後，胡鴻烈博士與鍾期榮博士移居香港，分別投身法律、公共服務與中文專上教育，逐步形成日後創辦樹仁的社會關懷與教育視野。 </t>
-  </si>
-  <si>
     <t>两人移居香港：走向教育与公共服务</t>
   </si>
   <si>
-    <t>1955年前后，胡鸿烈博士与钟期荣博士移居香港，分别投身法律、公共服务与中文专上教育，逐步形成日后创办树仁的社会关怀与教育视野。</t>
-  </si>
-  <si>
     <t>B01, B02</t>
   </si>
   <si>
@@ -331,13 +325,7 @@
     <t>Shue Yan relocated to Monmouth Path in Wan Chai and, after years of application, was granted a permanent campus site at Braemar Hill, laying the foundation for long-term campus development.</t>
   </si>
   <si>
-    <t xml:space="preserve">遷往灣仔萬茂徑，獲批寶馬山校址 </t>
-  </si>
-  <si>
     <t xml:space="preserve">樹仁遷往灣仔萬茂徑，並在經過多年申請後獲批寶馬山永久校址，為長遠校園建設奠定基礎。 </t>
-  </si>
-  <si>
-    <t>迁往湾仔万茂径，获批宝马山校址</t>
   </si>
   <si>
     <t>树仁迁往湾仔万茂径，并在经过多年申请后获批宝马山永久校址，为长远校园建设奠定基础。</t>
@@ -525,9 +513,6 @@
   </si>
   <si>
     <t>1983年，寶馬山新校舉行奠基典禮；因校址位處陡峭山坡，校方需花近六年半打入176根水泥柱，方能為校舍建立穩固地基。</t>
-  </si>
-  <si>
-    <t>新校奠基：陡坡建校的工程考验</t>
   </si>
   <si>
     <t>1983年，宝马山新校举行奠基典礼；因校址位处陡峭山坡，校方需花近六年半打入176根水泥柱，方能为校舍建立稳固地基。</t>
@@ -1040,12 +1025,6 @@
     <t>T28</t>
   </si>
   <si>
-    <t>New University Name Officially Adopted: Entering a New Stage of University Development</t>
-  </si>
-  <si>
-    <t>In February 2007, Hong Kong Shue Yan University held its inauguration ceremony, officially adopting its new name and marking Shue Yan's transition from a post-secondary college to a new stage of university development.</t>
-  </si>
-  <si>
     <t>新校名正式啟用：進入大學發展階段</t>
   </si>
   <si>
@@ -4051,9 +4030,6 @@
     <t>P91</t>
   </si>
   <si>
-    <t>The University celebrated President Dr. Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
-  </si>
-  <si>
     <t>大學為校監胡鴻烈一百零一歲壽辰舉行小型慶祝會，表揚其畢生服務。</t>
   </si>
   <si>
@@ -4989,9 +4965,6 @@
   </si>
   <si>
     <t>戰後人口增長與中文高等教育需求上升</t>
-  </si>
-  <si>
-    <t>戰後从内地进入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
   </si>
   <si>
     <t>战后人口增长与中文高等教育需求上升</t>
@@ -5345,9 +5318,6 @@
     <t>推行副學士課程項目</t>
   </si>
   <si>
-    <t>為達至六成青年接受專上教育的目標，政府於2000年推出副學士課程，鼓勵大學及私立院校開辦自資專上課程。</t>
-  </si>
-  <si>
     <t>推行副学士课程项目</t>
   </si>
   <si>
@@ -5384,9 +5354,6 @@
   </si>
   <si>
     <t>提出打造香港成爲區域教育樞紐理念</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2004年《施政報告》首提，2006年設跨局委員會，2007年重申。主要措施包括：教資會資助院校非本地學生學額上限由10%提高至20%、放寬入境、提供獎學金及海外推廣。 </t>
   </si>
   <si>
     <t>提出打造香港成为区域教育枢纽理念</t>
@@ -5519,10 +5486,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>新校奠基：陡坡建校的工程考驗</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>畢業生資格與專業認可的考驗</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5773,6 +5736,137 @@
   </si>
   <si>
     <t>仁大的五年(2026-2031)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數字基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>University Title Officially Adopted: Entering a New Stage of University Development</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In February 2007, Hong Kong Shue Yan University held its inauguration ceremony, officially adopting its title and marking Shue Yan's transition from a post-secondary college to a new stage of university development.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>遷往灣仔萬茂里，獲批寶馬山校址</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迁往湾仔万茂里，获批宝马山校址</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>從戰後内地進入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1955</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，胡鴻烈博士與鍾期榮博士移居香港，分別投身法律、公共服務與中文專上教育，逐步形成日後創辦樹仁的社會關懷與教育視野。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1955</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，胡鸿烈博士与钟期荣博士移居香港，分别投身法律、公共服务与中文专上教育，逐步形成日后创办树仁的社会关怀与教育视野。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新校舍奠基：陡坡建校的工程考驗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新校舍奠基：陡坡建校的工程考验</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>為達至六成青年接受專上教育的目標，政府於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年推出副學士課程，鼓勵大學及私立院校開辦自資專上課程。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>區域教育中心計畫於 2004 年在施政報告中提出，2006 年由跨部門督導委員會推進，2007 年再次確認，該計畫將大學教育資助委員會資助大學的非本地學生配額從 10% 提高到 20%，放寬入學規則，提供獎學金，並促進香港教育走向海外。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The University celebrated President Dr. Henry Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -5780,7 +5874,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6064,6 +6158,27 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6136,7 +6251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6269,6 +6384,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6664,45 +6794,45 @@
         <v>22</v>
       </c>
       <c r="F3" s="41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="42" t="s">
-        <v>24</v>
-      </c>
       <c r="H3" s="41" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="79.8">
       <c r="A4" s="36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="36">
         <v>1966</v>
       </c>
       <c r="C4" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="F4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="G4" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="H4" s="38" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>33</v>
       </c>
       <c r="I4" s="36" t="s">
         <v>17</v>
@@ -6713,63 +6843,63 @@
     </row>
     <row r="5" spans="1:10" ht="91.2">
       <c r="A5" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="40">
         <v>1971</v>
       </c>
       <c r="C5" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="F5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="G5" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="H5" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="I5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="40" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="91.2">
       <c r="A6" s="36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" s="36">
         <v>1972</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="F6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="G6" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="H6" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>49</v>
-      </c>
       <c r="I6" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J6" s="36" t="s">
         <v>18</v>
@@ -6777,728 +6907,728 @@
     </row>
     <row r="7" spans="1:10" ht="57">
       <c r="A7" s="36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="40">
         <v>1976</v>
       </c>
       <c r="C7" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="F7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="G7" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="H7" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="I7" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>56</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57">
       <c r="A8" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="36">
         <v>1977</v>
       </c>
       <c r="C8" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="G8" s="45" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H8" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="I8" s="36" t="s">
         <v>62</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>66</v>
       </c>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="68.400000000000006">
       <c r="A9" s="36" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" s="40">
         <v>1978</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="H9" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="I9" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="40" t="s">
         <v>70</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="68.400000000000006">
       <c r="A10" s="40" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B10" s="36">
         <v>1979</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="H10" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="I10" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="36" t="s">
         <v>78</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57">
       <c r="A11" s="36" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" s="40">
         <v>1980</v>
       </c>
       <c r="C11" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="H11" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>89</v>
-      </c>
       <c r="I11" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="79.8">
       <c r="A12" s="36" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B12" s="36">
         <v>1982</v>
       </c>
       <c r="C12" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>988</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>95</v>
-      </c>
       <c r="I12" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.8">
       <c r="A13" s="40" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B13" s="40">
         <v>1983</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>100</v>
+        <v>1028</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="68.400000000000006">
       <c r="A14" s="36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B14" s="36">
         <v>1985</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="I14" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>104</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
       <c r="A15" s="40" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B15" s="40">
         <v>1986</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>116</v>
-      </c>
       <c r="I15" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="36" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16" s="36">
         <v>1987</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="36" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B17" s="40">
         <v>1988</v>
       </c>
       <c r="C17" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="I17" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" s="40" t="s">
         <v>125</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" s="40" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.8">
       <c r="A18" s="40" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B18" s="36">
         <v>1990</v>
       </c>
       <c r="C18" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="I18" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="36" t="s">
         <v>133</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="36" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B19" s="40">
         <v>1995</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="I19" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="40" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B20" s="36">
         <v>1996</v>
       </c>
       <c r="C20" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>153</v>
-      </c>
       <c r="I20" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B21" s="40">
         <v>1999</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="I21" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="40" t="s">
         <v>156</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="36" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B22" s="36">
         <v>2000</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="38" t="s">
         <v>163</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>168</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="40" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B23" s="40">
         <v>2001</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="I23" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="40" t="s">
         <v>172</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="36" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B24" s="36">
         <v>2002</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="I24" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="36" t="s">
         <v>180</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="40" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B25" s="40">
         <v>2003</v>
       </c>
       <c r="C25" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>192</v>
-      </c>
       <c r="I25" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="68.400000000000006">
       <c r="A26" s="36" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B26" s="36">
         <v>2004</v>
       </c>
       <c r="C26" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="D26" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>199</v>
-      </c>
       <c r="I26" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="36" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B27" s="40">
         <v>2005</v>
       </c>
       <c r="C27" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="H27" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="I27" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="40" t="s">
         <v>202</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J27" s="40" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="40" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B28" s="36">
         <v>2006</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J28" s="36" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="36" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B29" s="40">
         <v>2007</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>215</v>
+      <c r="C29" s="46" t="s">
+        <v>1020</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>216</v>
+        <v>1021</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -7551,19 +7681,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7571,220 +7701,220 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -7795,116 +7925,116 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -7916,466 +8046,466 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8387,28 +8517,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8419,179 +8549,179 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8603,89 +8733,89 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8697,240 +8827,240 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
       <c r="M42" s="19"/>
       <c r="N42" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8938,33 +9068,33 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -8975,87 +9105,87 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9067,638 +9197,638 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9709,25 +9839,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9739,28 +9869,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9771,55 +9901,55 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9831,28 +9961,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -9863,54 +9993,54 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -9918,33 +10048,33 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -9955,58 +10085,58 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="28.8">
       <c r="A80" s="2" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10017,297 +10147,297 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10315,867 +10445,867 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>708</v>
+        <v>1031</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>718</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
       <c r="M113" s="17"/>
       <c r="N113" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11183,45 +11313,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11420,519 +11550,519 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>864</v>
+        <v>855</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>1024</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B7" s="5">
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2">
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B9" s="5">
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2">
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>955</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>956</v>
+        <v>946</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>1029</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>962</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>963</v>
+        <v>952</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>1030</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12025,23 +12155,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12223,25 +12336,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12257,4 +12369,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9755D3B3-7960-4184-B99E-6A3910944FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4751DB0F-34BD-4C5A-9FB1-A8E9F45E0432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1033">
   <si>
     <t>id</t>
   </si>
@@ -214,15 +214,9 @@
     <t>兩人移居香港：走向教育與公共服務</t>
   </si>
   <si>
-    <t xml:space="preserve">1955年前後，胡鴻烈博士與鍾期榮博士移居香港，分別投身法律、公共服務與中文專上教育，逐步形成日後創辦樹仁的社會關懷與教育視野。 </t>
-  </si>
-  <si>
     <t>两人移居香港：走向教育与公共服务</t>
   </si>
   <si>
-    <t>1955年前后，胡鸿烈博士与钟期荣博士移居香港，分别投身法律、公共服务与中文专上教育，逐步形成日后创办树仁的社会关怀与教育视野。</t>
-  </si>
-  <si>
     <t>B01, B02</t>
   </si>
   <si>
@@ -331,13 +325,7 @@
     <t>Shue Yan relocated to Monmouth Path in Wan Chai and, after years of application, was granted a permanent campus site at Braemar Hill, laying the foundation for long-term campus development.</t>
   </si>
   <si>
-    <t xml:space="preserve">遷往灣仔萬茂徑，獲批寶馬山校址 </t>
-  </si>
-  <si>
     <t xml:space="preserve">樹仁遷往灣仔萬茂徑，並在經過多年申請後獲批寶馬山永久校址，為長遠校園建設奠定基礎。 </t>
-  </si>
-  <si>
-    <t>迁往湾仔万茂径，获批宝马山校址</t>
   </si>
   <si>
     <t>树仁迁往湾仔万茂径，并在经过多年申请后获批宝马山永久校址，为长远校园建设奠定基础。</t>
@@ -525,9 +513,6 @@
   </si>
   <si>
     <t>1983年，寶馬山新校舉行奠基典禮；因校址位處陡峭山坡，校方需花近六年半打入176根水泥柱，方能為校舍建立穩固地基。</t>
-  </si>
-  <si>
-    <t>新校奠基：陡坡建校的工程考验</t>
   </si>
   <si>
     <t>1983年，宝马山新校举行奠基典礼；因校址位处陡峭山坡，校方需花近六年半打入176根水泥柱，方能为校舍建立稳固地基。</t>
@@ -1040,12 +1025,6 @@
     <t>T28</t>
   </si>
   <si>
-    <t>New University Name Officially Adopted: Entering a New Stage of University Development</t>
-  </si>
-  <si>
-    <t>In February 2007, Hong Kong Shue Yan University held its inauguration ceremony, officially adopting its new name and marking Shue Yan's transition from a post-secondary college to a new stage of university development.</t>
-  </si>
-  <si>
     <t>新校名正式啟用：進入大學發展階段</t>
   </si>
   <si>
@@ -4051,9 +4030,6 @@
     <t>P91</t>
   </si>
   <si>
-    <t>The University celebrated President Dr. Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
-  </si>
-  <si>
     <t>大學為校監胡鴻烈一百零一歲壽辰舉行小型慶祝會，表揚其畢生服務。</t>
   </si>
   <si>
@@ -4989,9 +4965,6 @@
   </si>
   <si>
     <t>戰後人口增長與中文高等教育需求上升</t>
-  </si>
-  <si>
-    <t>戰後从内地进入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
   </si>
   <si>
     <t>战后人口增长与中文高等教育需求上升</t>
@@ -5345,9 +5318,6 @@
     <t>推行副學士課程項目</t>
   </si>
   <si>
-    <t>為達至六成青年接受專上教育的目標，政府於2000年推出副學士課程，鼓勵大學及私立院校開辦自資專上課程。</t>
-  </si>
-  <si>
     <t>推行副学士课程项目</t>
   </si>
   <si>
@@ -5384,9 +5354,6 @@
   </si>
   <si>
     <t>提出打造香港成爲區域教育樞紐理念</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2004年《施政報告》首提，2006年設跨局委員會，2007年重申。主要措施包括：教資會資助院校非本地學生學額上限由10%提高至20%、放寬入境、提供獎學金及海外推廣。 </t>
   </si>
   <si>
     <t>提出打造香港成为区域教育枢纽理念</t>
@@ -5519,10 +5486,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>新校奠基：陡坡建校的工程考驗</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>畢業生資格與專業認可的考驗</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5773,6 +5736,137 @@
   </si>
   <si>
     <t>仁大的五年(2026-2031)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數字基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>University Title Officially Adopted: Entering a New Stage of University Development</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In February 2007, Hong Kong Shue Yan University held its inauguration ceremony, officially adopting its title and marking Shue Yan's transition from a post-secondary college to a new stage of university development.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>遷往灣仔萬茂里，獲批寶馬山校址</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迁往湾仔万茂里，获批宝马山校址</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>從戰後内地進入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1955</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，胡鴻烈博士與鍾期榮博士移居香港，分別投身法律、公共服務與中文專上教育，逐步形成日後創辦樹仁的社會關懷與教育視野。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1955</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，胡鸿烈博士与钟期荣博士移居香港，分别投身法律、公共服务与中文专上教育，逐步形成日后创办树仁的社会关怀与教育视野。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新校舍奠基：陡坡建校的工程考驗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新校舍奠基：陡坡建校的工程考验</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>為達至六成青年接受專上教育的目標，政府於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年推出副學士課程，鼓勵大學及私立院校開辦自資專上課程。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>區域教育中心計畫於 2004 年在施政報告中提出，2006 年由跨部門督導委員會推進，2007 年再次確認，該計畫將大學教育資助委員會資助大學的非本地學生配額從 10% 提高到 20%，放寬入學規則，提供獎學金，並促進香港教育走向海外。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The University celebrated President Dr. Henry Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -5780,7 +5874,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6064,6 +6158,27 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6136,7 +6251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6269,6 +6384,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6664,45 +6794,45 @@
         <v>22</v>
       </c>
       <c r="F3" s="41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="42" t="s">
-        <v>24</v>
-      </c>
       <c r="H3" s="41" t="s">
-        <v>25</v>
+        <v>1026</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="79.8">
       <c r="A4" s="36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="36">
         <v>1966</v>
       </c>
       <c r="C4" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="F4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="G4" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="H4" s="38" t="s">
         <v>31</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>33</v>
       </c>
       <c r="I4" s="36" t="s">
         <v>17</v>
@@ -6713,63 +6843,63 @@
     </row>
     <row r="5" spans="1:10" ht="91.2">
       <c r="A5" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="40">
         <v>1971</v>
       </c>
       <c r="C5" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="F5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="G5" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="H5" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="I5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="40" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="91.2">
       <c r="A6" s="36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" s="36">
         <v>1972</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="F6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="G6" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="H6" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>49</v>
-      </c>
       <c r="I6" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J6" s="36" t="s">
         <v>18</v>
@@ -6777,728 +6907,728 @@
     </row>
     <row r="7" spans="1:10" ht="57">
       <c r="A7" s="36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="40">
         <v>1976</v>
       </c>
       <c r="C7" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="F7" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="G7" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="H7" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="I7" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>56</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57">
       <c r="A8" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="36">
         <v>1977</v>
       </c>
       <c r="C8" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="G8" s="45" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H8" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="I8" s="36" t="s">
         <v>62</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>66</v>
       </c>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="68.400000000000006">
       <c r="A9" s="36" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" s="40">
         <v>1978</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="H9" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="I9" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="40" t="s">
         <v>70</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="68.400000000000006">
       <c r="A10" s="40" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B10" s="36">
         <v>1979</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="H10" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="I10" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="36" t="s">
         <v>78</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57">
       <c r="A11" s="36" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" s="40">
         <v>1980</v>
       </c>
       <c r="C11" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="H11" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>89</v>
-      </c>
       <c r="I11" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="79.8">
       <c r="A12" s="36" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B12" s="36">
         <v>1982</v>
       </c>
       <c r="C12" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>988</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>95</v>
-      </c>
       <c r="I12" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.8">
       <c r="A13" s="40" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B13" s="40">
         <v>1983</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>100</v>
+        <v>1028</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="68.400000000000006">
       <c r="A14" s="36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B14" s="36">
         <v>1985</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="I14" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>104</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
       <c r="A15" s="40" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B15" s="40">
         <v>1986</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>116</v>
-      </c>
       <c r="I15" s="40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="36" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B16" s="36">
         <v>1987</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="36" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B17" s="40">
         <v>1988</v>
       </c>
       <c r="C17" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="I17" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" s="40" t="s">
         <v>125</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" s="40" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.8">
       <c r="A18" s="40" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B18" s="36">
         <v>1990</v>
       </c>
       <c r="C18" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="I18" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="36" t="s">
         <v>133</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="36" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B19" s="40">
         <v>1995</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="I19" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="40" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B20" s="36">
         <v>1996</v>
       </c>
       <c r="C20" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>153</v>
-      </c>
       <c r="I20" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B21" s="40">
         <v>1999</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="I21" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="40" t="s">
         <v>156</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="36" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B22" s="36">
         <v>2000</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="38" t="s">
         <v>163</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>168</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="40" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B23" s="40">
         <v>2001</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="I23" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="40" t="s">
         <v>172</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="36" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B24" s="36">
         <v>2002</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="I24" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="36" t="s">
         <v>180</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="40" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B25" s="40">
         <v>2003</v>
       </c>
       <c r="C25" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>192</v>
-      </c>
       <c r="I25" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="68.400000000000006">
       <c r="A26" s="36" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B26" s="36">
         <v>2004</v>
       </c>
       <c r="C26" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="D26" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>199</v>
-      </c>
       <c r="I26" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="36" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B27" s="40">
         <v>2005</v>
       </c>
       <c r="C27" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="H27" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="I27" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="40" t="s">
         <v>202</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="J27" s="40" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="40" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B28" s="36">
         <v>2006</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J28" s="36" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="36" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B29" s="40">
         <v>2007</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>215</v>
+      <c r="C29" s="46" t="s">
+        <v>1020</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>216</v>
+        <v>1021</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -7551,19 +7681,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7571,220 +7701,220 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -7795,116 +7925,116 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -7916,466 +8046,466 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8387,28 +8517,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8419,179 +8549,179 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8603,89 +8733,89 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8697,240 +8827,240 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
       <c r="M42" s="19"/>
       <c r="N42" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -8938,33 +9068,33 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -8975,87 +9105,87 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9067,638 +9197,638 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9709,25 +9839,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9739,28 +9869,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9771,55 +9901,55 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9831,28 +9961,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -9863,54 +9993,54 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -9918,33 +10048,33 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -9955,58 +10085,58 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="28.8">
       <c r="A80" s="2" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10017,297 +10147,297 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10315,867 +10445,867 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>708</v>
+        <v>1031</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>718</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
       <c r="M113" s="17"/>
       <c r="N113" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11183,45 +11313,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11420,519 +11550,519 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>864</v>
+        <v>855</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>1024</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B7" s="5">
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2">
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B9" s="5">
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2">
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>955</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>956</v>
+        <v>946</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>1029</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>962</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>963</v>
+        <v>952</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>1030</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">

--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -12155,6 +12155,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12336,24 +12353,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12369,22 +12387,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4751DB0F-34BD-4C5A-9FB1-A8E9F45E0432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE319E95-573E-4CC7-9938-6F3DEAB988F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -178,12 +178,6 @@
     <t>T01</t>
   </si>
   <si>
-    <t>Hu Hung-lick and Chung Chi-yung Studied in Europe: From Law to Educational Commitment</t>
-  </si>
-  <si>
-    <t>After the war, Dr. Hu Hung-lick and Dr. Chung Chi-yung went to France to further their studies in law. Their exposure to different legal systems, social institutions, and educational philosophies in Europe laid the foundation for their later efforts to address youth and social issues through institutional reform.</t>
-  </si>
-  <si>
     <t>胡鴻烈、鍾期榮赴歐深造：從法律走向教育關懷</t>
   </si>
   <si>
@@ -208,9 +202,6 @@
     <t>The Couple Moved to Hong Kong: Toward Education and Public Service</t>
   </si>
   <si>
-    <t>Around 1955, Dr. Hu Hung-lick and Dr. Chung Chi-yung moved to Hong Kong, where they devoted themselves respectively to law, public service, and Chinese post-secondary education. This gradually shaped the social commitment and educational vision that would later lead to the founding of Shue Yan.</t>
-  </si>
-  <si>
     <t>兩人移居香港：走向教育與公共服務</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
     <t>Shue Yan College Founded: Transforming Educational Thought into Institutional Practice</t>
   </si>
   <si>
-    <t>In 1971, Dr. Hu Hung-lick and Dr. Chung Chi-yung founded Shue Yan College, further transforming their earlier commitment to children's, youth, and social education into a higher education initiative responding to the shortage of further education opportunities in Hong Kong.</t>
-  </si>
-  <si>
     <t xml:space="preserve">樹仁書院創立：把教育思考轉化為制度實踐 </t>
   </si>
   <si>
@@ -411,40 +399,6 @@
   </si>
   <si>
     <t>In the early 1980s, Shue Yan graduates continued to face institutional constraints in terms of remuneration, professional prospects, and qualification recognition, reflecting the complex position of private post-secondary education within Hong Kong's higher education system.</t>
-  </si>
-  <si>
-    <r>
-      <t>1980</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年代初，樹仁畢業生在薪酬待遇、專業出路及資</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-      </rPr>
-      <t>格認可上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>仍面對制度限制，反映私立專上教育在香港高等教育體系中的複雜位置。</t>
-    </r>
   </si>
   <si>
     <t>毕业生资格与专业认可的考验</t>
@@ -1059,12 +1013,6 @@
     <t>P01</t>
   </si>
   <si>
-    <t>Dr. Hu Hung-lick and Dr. Chung Chi-yung founded Hong Kong Shue Yan College on Sing Woo Road, Happy Valley, to address the shortage of places in local post-secondary education.</t>
-  </si>
-  <si>
-    <t>Shue Yan established its Board of Governors, bringing together prominent leaders to advance university affairs and campus development. The Board of Governors included Chairman Wilfred Wong Sien-bing, and other members such as Sir Run Run Shaw, Ms. Aw Sian from Sing Tao Daily, Mr. Ngan Shing-kwan, founder of China Motor Corporation, Mr. Ting Hsiung-chao, one of the founders of the Hong Kong Plastics Manufacturers Association, Dr. Maurice J. Anderson, Mr. T. K. Ann, Bishop Gilbert Baker, Barrister Brook Bernacchi, Mr. Cha Chi Ming, Mr. Chan Po Fun, Mr. Chen Chan-yen, Dr. Dr. Chung Chi-yung, Rev. Fergus Cronin, Mr. Dr. Hu Hung-lick, Mr. Huo Pao-tsai, Barrister Henry Litton, Mr. Liu Han-tang, Mr. Y. B. Loo, Mr. Peter P. K. Ng, Mr. Shum Choi Sang, Mr. Shum Wai-yau, Mr. Peter H. M. Tsang, Mr. C. S. Wan, and Mr. Yuen Ngan Ming.</t>
-  </si>
-  <si>
     <r>
       <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
     </r>
@@ -1137,9 +1085,6 @@
     <t>P04</t>
   </si>
   <si>
-    <t>President Dr. Hu Hung-lick toured the United States on behalf of Shue Yan College, and he discussed academic cooperation with several universities.</t>
-  </si>
-  <si>
     <t>校監胡鴻烈代表樹仁書院赴美考察，與多所大學商討學術合作。</t>
   </si>
   <si>
@@ -1636,9 +1581,6 @@
     <t>P26</t>
   </si>
   <si>
-    <t>Dr. Hu Hung-lick Hung-lick was appointed a member of the sixth National Committee of the Chinese People’s Political Consultative Conference in 1987. He subsequently served on the Seventh National Committee and, from 1993, as a Standing Committee member of the Eighth and Ninth National Committees.</t>
-  </si>
-  <si>
     <t>胡鴻烈於1987年獲委任為第六屆全國政協委員，後續任第七屆委員，並於1993年起出任第八、九屆全國政協常委。</t>
   </si>
   <si>
@@ -1649,9 +1591,6 @@
   </si>
   <si>
     <t>P27</t>
-  </si>
-  <si>
-    <t>Dr. Hu Hung-lick attended the fifth session of the sixth National Committee of the Chinese People’s Political Consultative Conference in Beijing.</t>
   </si>
   <si>
     <t>胡鴻烈赴北京出席中國人民政治協商會議第六屆全國委員會第五次會議。</t>
@@ -1891,9 +1830,6 @@
     <t>P38</t>
   </si>
   <si>
-    <t>Governor Chris Patten joined Dr. Chung Chi-yung and Dr. Hu Hung-lick in hosting the opening of Shue Yan’s HK$100-million Library Complex, which greatly expanded campus resources.</t>
-  </si>
-  <si>
     <t>港督彭定康與鍾期榮、胡鴻烈主持耗資一億元的圖書館綜合大樓啟用，顯著擴充校園資源。</t>
   </si>
   <si>
@@ -2018,9 +1954,6 @@
   </si>
   <si>
     <t>P45</t>
-  </si>
-  <si>
-    <t>Chief Executive Tung Chee-hwa presented Dr. Hu Hung-lick with the Gold Bauhinia Star for distinguished service to Hong Kong.</t>
   </si>
   <si>
     <t>行政長官董建華向胡鴻烈頒授金紫荊星章，表揚其對香港的卓越服務。</t>
@@ -3376,9 +3309,6 @@
     <t>P69</t>
   </si>
   <si>
-    <t>The Hong Kong Institute of Education awarded honorary doctorates to Dr. Hu Hung-lick and Dr. Chung Chi-yung in recognition of their exceptional contributions to education.</t>
-  </si>
-  <si>
     <t>香港教育學院向胡鴻烈與鍾期榮頒授榮譽博士，表揚兩人的卓越教育貢獻。 </t>
   </si>
   <si>
@@ -3396,9 +3326,6 @@
     <t>P70</t>
   </si>
   <si>
-    <t>In 2007, Dr. Hu Hung-lick and Dr. Chung Chi-yung were named Persons of the Year of ‘Touching China’ for their lifelong dedication to education.</t>
-  </si>
-  <si>
     <t>2007年，創辦人胡鴻烈博士及鍾期榮博士獲選為「感動中國」年度人物，以表彰二人畢生奉獻教育。 </t>
   </si>
   <si>
@@ -3427,9 +3354,6 @@
   </si>
   <si>
     <t>P71</t>
-  </si>
-  <si>
-    <t>Chief Executive Donald Tsang presented Dr. Hu Hung-lick with the Grand Bauhinia Medal at Government House, Hong Kong.</t>
   </si>
   <si>
     <t>行政長官曾蔭權在香港禮賓府向胡鴻烈頒授大紫荊勳章。</t>
@@ -3461,9 +3385,6 @@
     <t>P73</t>
   </si>
   <si>
-    <t>Dr. Hu Hung-lick and Dr. Chung Chi-yung were named among the inaugural Hong Kong Loving Hearts honourees by Asia Television, with more than 130 supporters attending the ceremony.</t>
-  </si>
-  <si>
     <t>胡鴻烈與鍾期榮獲亞洲電視首屆「感動香港十大人物」，逾一百三十名支持者到場見證。 </t>
   </si>
   <si>
@@ -3668,9 +3589,6 @@
     <t>P79</t>
   </si>
   <si>
-    <t>The University of Hong Kong awarded Dr. Hu Hung-lick an honorary Doctor of Social Sciences for his long-standing contributions to education and public service.</t>
-  </si>
-  <si>
     <t>香港大學向胡鴻烈頒授榮譽社會科學博士，表揚其長期教育與公共服務。 </t>
   </si>
   <si>
@@ -3747,9 +3665,6 @@
   </si>
   <si>
     <t>P84</t>
-  </si>
-  <si>
-    <t>Dr. Hu Hung-lick received a lifetime achievement award in recognition of his enduring contributions to Shue Yan and education in Hong Kong.</t>
   </si>
   <si>
     <t>胡鴻烈博士獲頒終身成就獎，以表揚其畢生對樹仁及香港教育的貢獻。</t>
@@ -4538,9 +4453,6 @@
     <t>P109</t>
   </si>
   <si>
-    <t>Founding President Dr. Hu Hung-lick passed away at the age of 105; the University community held a funeral and memorial services honouring his legacy.</t>
-  </si>
-  <si>
     <t>創校校監胡鴻烈於一百零五歲逝世，大學社群舉行喪禮及追思會，紀念其貢獻。 </t>
   </si>
   <si>
@@ -4622,9 +4534,6 @@
   </si>
   <si>
     <t>2025-2026</t>
-  </si>
-  <si>
-    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu fai-chung as President.</t>
   </si>
   <si>
     <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
@@ -5575,10 +5484,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>胡鴻烈與鐘期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>The Education Department's specialists made its first formal visit to Shue Yan's post-secondary campus on Sing Woo Road, Happy Valley.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5867,6 +5772,121 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung founded Hong Kong Shue Yan College on Sing Woo Road, Happy Valley, to address the shortage of places in local post-secondary education.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>President Dr. Henry Hu Hung-lick toured the United States on behalf of Shue Yan College, and he discussed academic cooperation with several universities.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick Hung-lick was appointed a member of the sixth National Committee of the Chinese People’s Political Consultative Conference in 1987. He subsequently served on the Seventh National Committee and, from 1993, as a Standing Committee member of the Eighth and Ninth National Committees.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick attended the fifth session of the sixth National Committee of the Chinese People’s Political Consultative Conference in Beijing.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Governor Chris Patten joined Dr. Chung Chi-yung and Dr. Henry Hu Hung-lick in hosting the opening of Shue Yan’s HK$100-million Library Complex, which greatly expanded campus resources.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chief Executive Tung Chee-hwa presented Dr. Henry Hu Hung-lick with the Gold Bauhinia Star for distinguished service to Hong Kong.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Hong Kong Institute of Education awarded honorary doctorates to Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung in recognition of their exceptional contributions to education.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2007, Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung were named Persons of the Year of ‘Touching China’ for their lifelong dedication to education.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chief Executive Donald Tsang presented Dr. Henry Hu Hung-lick with the Grand Bauhinia Medal at Government House, Hong Kong.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung were named among the inaugural Hong Kong Loving Hearts honourees by Asia Television, with more than 130 supporters attending the ceremony.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick received a lifetime achievement award in recognition of his enduring contributions to Shue Yan and education in Hong Kong.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founding President Dr. Henry Hu Hung-lick passed away at the age of 105; the University community held a funeral and memorial services honouring his legacy.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu fai-chung as President.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>After the war, Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung went to France to further their studies in law. Their exposure to different legal systems, social institutions, and educational philosophies in Europe laid the foundation for their later efforts to address youth and social issues through institutional reform.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hu Hung-lick and Chung Chi-yung Studied in Europe: From Law to Educational Commitment</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Around 1955, Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung moved to Hong Kong, where they devoted themselves respectively to law, public service, and Chinese post-secondary education. This gradually shaped the social commitment and educational vision that would later lead to the founding of Shue Yan.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 1971, Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung founded Shue Yan College, further transforming their earlier commitment to children's, youth, and social education into a higher education initiative responding to the shortage of further education opportunities in Hong Kong.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1980</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年代初，樹仁畢業生在薪酬待遇、專業出路及資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+      </rPr>
+      <t>格認可上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>仍面對制度限制，反映私立專上教育在香港高等教育體系中的複雜位置。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡鴻烈與鍾期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shue Yan established its Board of Governors, bringing together prominent leaders to advance university affairs and campus development. The Board of Governors included Chairman Wilfred Wong Sien-bing, and other members such as Sir Run Run Shaw, Ms. Aw Sian from Sing Tao Daily, Mr. Ngan Shing-kwan, founder of China Motor Corporation, Mr. Ting Hsiung-chao, one of the founders of the Hong Kong Plastics Manufacturers Association, Dr. Maurice J. Anderson, Mr. T. K. Ann, Bishop Gilbert Baker, Barrister Brook Bernacchi, Mr. Cha Chi Ming, Mr. Chan Po Fun, Mr. Chen Chan-yen, Dr. Dr. Chung Chi-yung, Rev. Fergus Cronin, Mr. Dr. Henry Hu Hung-lick, Mr. Huo Pao-tsai, Barrister Henry Litton, Mr. Liu Han-tang, Mr. Y. B. Loo, Mr. Peter P. K. Ng, Mr. Shum Choi Sang, Mr. Shum Wai-yau, Mr. Peter H. M. Tsang, Mr. C. S. Wan, and Mr. Yuen Ngan Ming.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The University of Hong Kong awarded Dr. Henry Hu Hung-lick an honorary Doctor of Social Sciences for his long-standing contributions to education and public service.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6753,882 +6773,882 @@
         <v>1949</v>
       </c>
       <c r="C2" s="37" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="F2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="G2" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="H2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="I2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="J2" s="36" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="36" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="91.2">
       <c r="A3" s="40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="40">
         <v>1955</v>
       </c>
       <c r="C3" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="H3" s="41" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="40" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>1026</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="40" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="79.8">
       <c r="A4" s="36" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="36">
         <v>1966</v>
       </c>
       <c r="C4" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="G4" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="H4" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" s="36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="91.2">
       <c r="A5" s="40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B5" s="40">
         <v>1971</v>
       </c>
       <c r="C5" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="H5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="I5" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="J5" s="40" t="s">
         <v>36</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="40" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="91.2">
       <c r="A6" s="36" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B6" s="36">
         <v>1972</v>
       </c>
       <c r="C6" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="H6" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>47</v>
-      </c>
       <c r="I6" s="36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57">
       <c r="A7" s="36" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B7" s="40">
         <v>1976</v>
       </c>
       <c r="C7" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="H7" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="I7" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="J7" s="40" t="s">
         <v>52</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57">
       <c r="A8" s="40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B8" s="36">
         <v>1977</v>
       </c>
       <c r="C8" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="36" t="s">
         <v>58</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>62</v>
       </c>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="68.400000000000006">
       <c r="A9" s="36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B9" s="40">
         <v>1978</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="H9" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="I9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="40" t="s">
         <v>66</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="68.400000000000006">
       <c r="A10" s="40" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B10" s="36">
         <v>1979</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="H10" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="I10" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="36" t="s">
         <v>74</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57">
       <c r="A11" s="36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B11" s="40">
         <v>1980</v>
       </c>
       <c r="C11" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="H11" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>85</v>
-      </c>
       <c r="I11" s="40" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="79.8">
       <c r="A12" s="36" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B12" s="36">
         <v>1982</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>89</v>
+        <v>1029</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.8">
       <c r="A13" s="40" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B13" s="40">
         <v>1983</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1027</v>
+        <v>1006</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="68.400000000000006">
       <c r="A14" s="36" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B14" s="36">
         <v>1985</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="I14" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>99</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
       <c r="A15" s="40" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B15" s="40">
         <v>1986</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>111</v>
-      </c>
       <c r="I15" s="40" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="36" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B16" s="36">
         <v>1987</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="36" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B17" s="40">
         <v>1988</v>
       </c>
       <c r="C17" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="I17" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="40" t="s">
         <v>120</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="40" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.8">
       <c r="A18" s="40" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B18" s="36">
         <v>1990</v>
       </c>
       <c r="C18" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H18" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="I18" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="36" t="s">
         <v>128</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="36" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B19" s="40">
         <v>1995</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="I19" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="40" t="s">
         <v>136</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="40" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B20" s="36">
         <v>1996</v>
       </c>
       <c r="C20" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>148</v>
-      </c>
       <c r="I20" s="36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="36" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B21" s="40">
         <v>1999</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="I21" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="40" t="s">
         <v>151</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="40" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="36" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B22" s="36">
         <v>2000</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="38" t="s">
         <v>158</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>163</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="40" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B23" s="40">
         <v>2001</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="I23" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" s="40" t="s">
         <v>167</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>168</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="36" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B24" s="36">
         <v>2002</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="I24" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="36" t="s">
         <v>175</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="40" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B25" s="40">
         <v>2003</v>
       </c>
       <c r="C25" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>187</v>
-      </c>
       <c r="I25" s="40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="68.400000000000006">
       <c r="A26" s="36" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B26" s="36">
         <v>2004</v>
       </c>
       <c r="C26" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>194</v>
-      </c>
       <c r="I26" s="36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="36" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B27" s="40">
         <v>2005</v>
       </c>
       <c r="C27" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="I27" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="40" t="s">
         <v>197</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="J27" s="40" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="40" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B28" s="36">
         <v>2006</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>991</v>
+        <v>971</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J28" s="36" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="36" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B29" s="40">
         <v>2007</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>1020</v>
+        <v>999</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>1021</v>
+        <v>1000</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -7681,19 +7701,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7701,1366 +7721,1366 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>220</v>
+        <v>1012</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>221</v>
+        <v>1031</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>995</v>
+        <v>1030</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>994</v>
+        <v>974</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>237</v>
+        <v>1013</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>996</v>
+        <v>975</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>998</v>
+        <v>977</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>997</v>
+        <v>976</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>984</v>
+        <v>964</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>1000</v>
+        <v>979</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>356</v>
+        <v>1014</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>361</v>
+        <v>1015</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
       <c r="N28" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>423</v>
+        <v>1016</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>992</v>
+        <v>972</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
       <c r="M42" s="19"/>
       <c r="N42" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -9068,979 +9088,979 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>459</v>
+        <v>1017</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>1002</v>
+        <v>981</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>1001</v>
+        <v>980</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>586</v>
+        <v>1018</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>592</v>
+        <v>1019</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>597</v>
+        <v>1020</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>1003</v>
+        <v>982</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>1004</v>
+        <v>983</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>606</v>
+        <v>1021</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>1005</v>
+        <v>984</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -10048,396 +10068,396 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="28.8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="41.4">
       <c r="A80" s="2" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>637</v>
+        <v>1032</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>662</v>
+        <v>1022</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>1006</v>
+        <v>985</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>1008</v>
+        <v>987</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
       <c r="N89" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10445,867 +10465,867 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>1031</v>
+        <v>1010</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>1009</v>
+        <v>988</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>1010</v>
+        <v>989</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>1011</v>
+        <v>990</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>1012</v>
+        <v>991</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>1013</v>
+        <v>992</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>796</v>
+        <v>1023</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>800</v>
+        <v>781</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>1032</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>1016</v>
+        <v>995</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>814</v>
+        <v>1024</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
       <c r="M113" s="17"/>
       <c r="N113" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>1017</v>
+        <v>996</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>836</v>
+        <v>816</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>1018</v>
+        <v>997</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11313,45 +11333,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>1014</v>
+        <v>993</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>1019</v>
+        <v>998</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11547,522 +11567,522 @@
     </row>
     <row r="2" spans="1:8" ht="24.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>1024</v>
+        <v>1003</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>857</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>874</v>
+        <v>854</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2">
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B7" s="5">
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>887</v>
+        <v>867</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>889</v>
+        <v>869</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2">
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>893</v>
+        <v>873</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B9" s="5">
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>901</v>
+        <v>881</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>902</v>
+        <v>882</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B12" s="2">
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>917</v>
+        <v>897</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>924</v>
+        <v>904</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>1029</v>
+        <v>1008</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>1030</v>
+        <v>1009</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>963</v>
+        <v>943</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>964</v>
+        <v>944</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12155,23 +12175,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12353,25 +12356,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12387,4 +12389,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE319E95-573E-4CC7-9938-6F3DEAB988F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73290A89-E957-4457-8479-850229D53E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
     <sheet name="圖片" sheetId="3" r:id="rId2"/>
-    <sheet name="香港教育史" sheetId="2" r:id="rId3"/>
+    <sheet name="高等教育重點政策" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="1032">
   <si>
     <t>id</t>
   </si>
@@ -577,20 +577,6 @@
     <t>与北京大学合作：拓展内地学术联系</t>
   </si>
   <si>
-    <r>
-      <t>1987</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，树仁与北京大学合办法律本科学士学位课程，成为学院拓展内地学术合作的重要里程碑。</t>
-    </r>
-  </si>
-  <si>
     <t>T16</t>
   </si>
   <si>
@@ -662,34 +648,10 @@
     <t>T17</t>
   </si>
   <si>
-    <t>Student Petitions and the Continuation of the Four-Year Principle</t>
-  </si>
-  <si>
-    <t>Around 1990, students' campaigns for government funding reflected the tuition pressures and fairness issues facing private post-secondary education, while Shue Yan continued to make the maintenance of four-year education a precondition for accepting funding.</t>
-  </si>
-  <si>
     <t>學生請願與四年制原則的延續</t>
   </si>
   <si>
-    <t xml:space="preserve">1990年前後，學生爭取政府資助的行動反映私立專上教育的學費壓力與公平問題，而樹仁仍以維持四年制教育作為接受資助的前提。 </t>
-  </si>
-  <si>
     <t>学生请愿与四年制原则的延续</t>
-  </si>
-  <si>
-    <r>
-      <t>1990</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年前后，学生争取政府资助的行动反映私立专上教育的学费压力与公平问题，而树仁仍以维持四年制教育作为接受资助的前提。</t>
-    </r>
   </si>
   <si>
     <t>B09, B10</t>
@@ -892,9 +854,6 @@
     <t>商科、輔導及心理學課程通過評審</t>
   </si>
   <si>
-    <t xml:space="preserve">2003年，工商管理系、輔導及心理學系獲准開辦榮譽學士課程，進一步擴大樹仁的學位課程架構。 </t>
-  </si>
-  <si>
     <t>商科、辅导及心理学课程通过评审</t>
   </si>
   <si>
@@ -907,793 +866,770 @@
     <t>Economics Programme Accredited</t>
   </si>
   <si>
-    <t>In 2004, the Department of Economics was approved to offer an honours bachelor's degree programme, marking the continued refinement of Shue Yan's business and social science programme system.</t>
-  </si>
-  <si>
     <t>經濟學課程通過評審</t>
   </si>
   <si>
-    <t xml:space="preserve">2004年，經濟學系獲准開辦榮譽學士課程，標誌樹仁的商科與社會科學課程體系繼續完善。 </t>
-  </si>
-  <si>
     <t>经济学课程通过评审</t>
   </si>
   <si>
-    <r>
-      <t>2004</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>Multiple Programmes Complete Accreditation; First Cohort of Bachelor's Students Graduated</t>
+  </si>
+  <si>
+    <t>In 2005, programmes in History, Sociology, and English Language and Literature passed accreditation, the first cohort of honours bachelor's students graduated, and the Residential and Amenities Building was completed.</t>
+  </si>
+  <si>
+    <t>多個課程完成評審，首批學士學生畢業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005年，歷史、社會學及英國語言文學等課程通過評審，首批榮譽學士學生畢業，宿舍文康大樓亦落成。 </t>
+  </si>
+  <si>
+    <t>多个课程完成评审，首批学士学生毕业</t>
+  </si>
+  <si>
+    <t>2005年，历史、社会学及英国语言文学等课程通过评审，首批荣誉学士学生毕业，宿舍文康大楼亦落成。</t>
+  </si>
+  <si>
+    <t>B14, B16</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>Title Changed to Hong Kong Shue Yan University—Hong Kong's First Private University</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>正名為香港樹仁大學：香港首間私立大學</t>
+  </si>
+  <si>
+    <t>正名为香港树仁大学：香港首间私立大学</t>
+  </si>
+  <si>
+    <t>2006年，树仁获行政长官会同行政会议批准正名为香港树仁大学，成为香港首间私立大学。</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>新校名正式啟用：進入大學發展階段</t>
+  </si>
+  <si>
+    <t>新校名正式启用：进入大学发展阶段</t>
+  </si>
+  <si>
+    <t>2007年2月，香港树仁大学举行正名典礼，新校名正式启用，标志树仁由专上学院进入大学发展的新阶段。</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>photo-1</t>
+  </si>
+  <si>
+    <t>photo-2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>photo-3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>photo-4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>photo-5</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P01</t>
+  </si>
+  <si>
+    <r>
+      <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>萬春先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>先生、阮雁鳴先生</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡鸿烈与钟期荣在跑马地成和道创办香港树仁书院，以响应本地专上教育学额不足。</t>
+  </si>
+  <si>
+    <t>树仁成立校董会，汇聚贤达，推动校务与校舍建设。校董会成员包括主席黄宣平议员，校董成员包括邵逸夫先生、来自《星岛日报》的胡仙女士、中华汽车创办人颜成坤议员、香港塑料业厂商会创会人之一丁熊照先生、晏务理博士、安子介议员、白约翰主教、贝纳祺御用大律师、查济民先生、陈普芬议员、陈存仁先生、钟期荣博士、龚乐年神父、胡鸿烈议员、霍宝材先生、烈显伦御用大律师、刘汉栋先生、陆荫百先生、伍秉坚议员、岑才生先生、岑维休先生、曾汉文先生、万春先先生、阮雁鸣先生。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971/image2.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>1971–1972</t>
+  </si>
+  <si>
+    <t>Shue Yan had already established scholarships in its early years and entered into an academic collaboration with Northeast Louisiana University in the United States, thereby expanding overseas learning opportunities for students.
+Source: (Left) Wah Kiu Yat Po, 29 June 1971 ; (Right) Wah Kiu Yat Po, 4 August 1971</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971-1972/image3.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971-1972/image4.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P03</t>
+  </si>
+  <si>
+    <t>Shue Yan College Limited adopted its Memorandum and Articles of Association, formally establishing the institution's corporate and governance framework.</t>
+  </si>
+  <si>
+    <t>樹仁書院有限公司通過組織章程大綱及細則，正式確立院校的法人與管治架構。</t>
+  </si>
+  <si>
+    <t>树仁书院有限公司通过组织章程大纲及细则，正式确立院校的法人与管治架构。 </t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image6.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P04</t>
+  </si>
+  <si>
+    <t>校監胡鴻烈代表樹仁書院赴美考察，與多所大學商討學術合作。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image7.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image8.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P05</t>
+  </si>
+  <si>
+    <t>Shue Yan and Northeast Louisiana University jointly launched their first credit-bearing summer programme, taught by visiting scholars and American student tutors.</t>
+  </si>
+  <si>
+    <t>樹仁與美國東北路易斯安那大學合辦首個可計學分暑期課程，由訪港學者及美國學生導師授課。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image9.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image10.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P06</t>
+  </si>
+  <si>
+    <t>The campus at no. 7 Wan Chai Gap Road opened in 1972, serving as Shue Yan's secondary section during the day and its post-secondary evening division at night.</t>
+  </si>
+  <si>
+    <t>灣仔峽道7號校舍啟用，日間供樹仁書院中學部學生上課，晚間則由樹仁書院大專部夜組使用。</t>
+  </si>
+  <si>
+    <t>湾仔峡道7号校舍启用，日间供树仁书院中学部学生上课，晚间则由树仁书院大专部夜组使用。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image11.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image12.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>Governor Sir Murray MacLehose paid a private visit to the Wan Chai Gap Road campus and learned about Shue Yan’s founding story and development.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>港督麥理浩爵士私人到訪峽道校舍，了解樹仁的創校經過與發展。</t>
+  </si>
+  <si>
+    <t>港督麦理浩爵士私人到访峡道校舍，了解树仁的创校经过与发展。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image13.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image14.jpg</t>
+  </si>
+  <si>
+    <t>P08</t>
+  </si>
+  <si>
+    <t>教育署首次正式到访树仁位于跑马地成和道的专上校舍。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image15.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image16.jpg</t>
+  </si>
+  <si>
+    <t>P09</t>
+  </si>
+  <si>
+    <t>教育署專家首次評核樹仁學術水平，其後教育署署長 K. W. J. Topley 再次視察。 </t>
+  </si>
+  <si>
+    <t>教育署专家首次评核树仁学术水平，其后教育署署长 K. W. J. Topley 再次视察。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1975/image17.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1975/image18.jpg</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>Shue Yan was registered under the Post Secondary Colleges Ordinance, became authorised to award post-secondary diplomas, and formally adopted the name Shue Yan College.</t>
+  </si>
+  <si>
+    <t>樹仁按《專上學院條例》註冊，獲准頒授專上文憑，並正式定名為樹仁學院。</t>
+  </si>
+  <si>
+    <t>树仁按《专上学院条例》注册，获准颁授专上文凭，并正式定名为树仁学院。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1976/image20.jpg</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>Governor Sir Murray MacLehose presented Dr. Hu Hung-lick with the insignia of an Officer of the Order of the British Empire in recognition of his public service.</t>
+  </si>
+  <si>
+    <t>港督麥理浩爵士向胡鴻烈頒授大英帝國官佐勳章，表揚其公共服務。</t>
+  </si>
+  <si>
+    <t>港督麦理浩爵士向胡鸿烈颁授大英帝国官佐勋章，表扬其公共服务。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1976/image21.jpg</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>Shue Yan College moved to a seven-storey campus on Monmouth Path in Wan Chai, expanding its teaching space.</t>
+  </si>
+  <si>
+    <t>樹仁學院遷入灣仔萬茂里七層高的獨立校舍，擴充教學空間。</t>
+  </si>
+  <si>
+    <t>树仁学院迁入湾仔万茂里七层高的独立校舍，扩充教学空间。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1977/image22.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1977/image23.jpg</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>Students overwhelmingly backed the four-year curriculum; the College declined government funding and rejected the proposed 2-2-1 system.
+Source: (Right) The Kung Sheung Daily News, 4 November 1978</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>學生以壓倒性多數支持四年制；學院拒絕政府資助，不接受建議的「二二一」學制。
+來源: (右) 《香港工商日報》1978年11月4日</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学生以压倒性多数支持四年制；学院拒绝政府资助，不接受建议的「二二一」学制。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>来源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>右</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《香港工商日报》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1978</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1978/image24.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1978/image25.jpg</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>Shue Yan joined the Association of Southeast Asian Institutions of Higher Learning, gaining regional recognition for its academic standards.</t>
+  </si>
+  <si>
+    <t>樹仁加入東南亞高等教育協會，其學術水平獲區域認可。</t>
+  </si>
+  <si>
+    <t>树仁加入东南亚高等教育协会，其学术水平获区域认可。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image26.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image27.jpg</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>Shue Yan and Northeast Louisiana University jointly launched the College’s first  MBA programme, creating a new pathway for postgraduate study.</t>
+  </si>
+  <si>
+    <t>樹仁與東北路易斯安那大學合辦學院首個工商管理碩士課程，開拓研究生進修途徑。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image28.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image29.jpg</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>Student representatives presented the Director of Education, K. W. J. Topley, with a campus-wide petition defending Shue Yan’s four-year curriculum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 學生代表向教育署署長 K. W. J. Topley 遞交全校聯署，捍衛樹仁四年制課程。</t>
+  </si>
+  <si>
+    <t>学生代表向教育署署长 K. W. J. Topley 递交全校联署，捍卫树仁四年制课程。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image30.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image31.jpg</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>Acting Governor Sir Denys Roberts visited Shue Yan, meeting staff and students and inspecting its teaching environment.</t>
+  </si>
+  <si>
+    <t>署理港督羅弼時爵士到訪樹仁，會見學院師生並視察教學環境。</t>
+  </si>
+  <si>
+    <t>署理港督罗弼时爵士到访树仁，会见学院师生并视察教学环境。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1980/image32.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1980/image33.jpg</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>樹仁與美國阿拉巴馬大學合辦首個社會工作碩士課程，回應專業人才需求。</t>
+  </si>
+  <si>
+    <t>树仁与美国阿拉巴马大学合办首个社会工作硕士课程，响应专业人才需求。 </t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1981/image34.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1981/image35.jpg</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>Governor Sir Edward Youde attended the foundation stone-laying ceremony for Shue Yan College’s new Braemar Hill campus. The self-financed development required 176 concrete piles to be driven into the steep hillside, marking a major milestone in the College’s campus development.</t>
+  </si>
+  <si>
+    <t>港督尤德爵士出席樹仁學院寶馬山新校舍奠基禮。這項自資建校工程須在陡峭山坡打下176根水泥樁，標誌學院校園發展邁出重要一步。</t>
+  </si>
+  <si>
+    <t>港督尤德爵士出席树仁学院宝马山新校舍奠基礼。这项自资建校工程须在陡峭山坡打下176根水泥桩，标志学院校园发展迈出重要一步。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1983/image36.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1983/image37.jpg</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>Shue Yan College held the topping-off ceremony for its Main Academic Building on the Braemar Hill campus, marking the gradual completion of the new campus construction. </t>
+  </si>
+  <si>
+    <t>樹仁學院於寶馬山教學大樓舉行平頂禮，見證新校舍工程逐步完成。</t>
+  </si>
+  <si>
+    <t>树仁学院于宝马山新教学大楼举行平顶礼，见证新校舍工程逐步完成。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image38.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image39.jpg</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>China’s Vice Minister of Education, Huang Xinbai, visited Shue Yan, strengthening the College’s growing academic ties with mainland China.</t>
+  </si>
+  <si>
+    <t>中國教育部副部長黃辛白訪問樹仁，加強學院與內地逐步建立的學術聯繫。</t>
+  </si>
+  <si>
+    <t>中国教育部副部长黄辛白访问树仁，加强学院与内地逐步建立的学术联系。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image40.jpg</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>Hu Fai-chung joined Shue Yan College in 1985, beginning a long-term contribution to the University’s administration, teaching and learning development, campus expansion, and pursuit of university status.</t>
+  </si>
+  <si>
+    <t>胡懷中於1985年加入樹仁學院，自此在大學行政管理、教與學發展、校舍擴充及大學正名等方面作出長期貢獻。</t>
+  </si>
+  <si>
+    <t>胡怀中于1985年加入树仁学院，自此在大学行政管理、教与学发展、校舍扩充及大学正名等方面作出长期贡献。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1985/image41.jpg</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>The new Shue Yan College campus on Braemar Hill officially opened, providing a permanent base for the College’s teaching and institutional development.</t>
+  </si>
+  <si>
+    <t>樹仁學院寶馬山新校舍正式啟用，為學院教學與長遠發展提供永久校園基礎。</t>
+  </si>
+  <si>
+    <t>树仁学院宝马山新校舍正式启用，为学院教学与长远发展提供永久校园基础。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image42.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image43.jpg</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>Shue Yan and Peking University signed a five-year academic cooperation agreement covering faculty and student exchanges, postgraduate training, and legal education.</t>
+  </si>
+  <si>
+    <t>樹仁與北京大學簽署五年學術合作協議，涵蓋師生交流、研究生培養及法律教育。 </t>
+  </si>
+  <si>
+    <t>树仁与北京大学签署五年学术合作协议，涵盖师生交流、研究生培养及法律教育。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image44.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image45.jpg</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>國家教育委員會代表團訪問樹仁；北京大學校長丁石孫在歡迎會致辭。</t>
+  </si>
+  <si>
+    <t>国家教育委员会代表团访问树仁；北京大学校长丁石孙在欢迎会致辞。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image46.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P26</t>
+  </si>
+  <si>
+    <t>胡鴻烈於1987年獲委任為第六屆全國政協委員，後續任第七屆委員，並於1993年起出任第八、九屆全國政協常委。</t>
+  </si>
+  <si>
+    <t>胡鸿烈于1987年获委任为第六届全国政协委员，后续任第七届委员，并于1993年起出任第八、九届全国政协常委。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image48.jpg</t>
+  </si>
+  <si>
+    <t>P27</t>
+  </si>
+  <si>
+    <t>胡鴻烈赴北京出席中國人民政治協商會議第六屆全國委員會第五次會議。</t>
+  </si>
+  <si>
+    <t>胡鸿烈赴北京出席中国人民政治协商会议第六届全国委员会第五次会议。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image49.jpg</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image50.jpg</t>
+  </si>
+  <si>
+    <t>P28</t>
+  </si>
+  <si>
+    <t>1987—1988</t>
+  </si>
+  <si>
+    <t>Shue Yan and Peking University jointly offered a Bachelor of Laws programme, which became Shue Yan’s first degree programme recognised by China’s State Education Commission.</t>
+  </si>
+  <si>
+    <t>樹仁與北京大學合辦法律學士課程，成為樹仁首個獲中國國家教育委員會認可的學位課程。</t>
+  </si>
+  <si>
+    <t>树仁与北京大学合办法律学士课程，成为树仁首个获中国国家教育委员会认可的学位课程。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987-1988/image51.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>China’s State Education Commission donated more than 2,000 volumes on literature and history  to Shue Yan, enriching the College’s academic collection.</t>
+  </si>
+  <si>
+    <t>國家教育委員會向樹仁贈送逾二千冊文史典籍，充實學院的學術館藏。</t>
+  </si>
+  <si>
+    <t>国家教育委员会向树仁赠送逾二千册文史典籍，充实学院的学术馆藏。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image53.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image54.jpg</t>
+  </si>
+  <si>
+    <t>P30</t>
+  </si>
+  <si>
+    <t>Shue Yan students marched against the proposed conversion of Hong Kong’s four-year undergraduate structure to a three-year system.</t>
+  </si>
+  <si>
+    <t>樹仁學生遊行反對把香港四年制大學本科課程改為三年制。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>树仁学生游行反对把香港四年制大学本科课程改为三年制。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image55.jpg</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>Student representatives staged a four-day hunger strike after the government excluded Shue Yan from the publicly funded university system.</t>
+  </si>
+  <si>
+    <t>政府把樹仁排除於公立資助大學安排外，學生代表發起四日絕食抗議。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>政府把树仁排除于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>年，经济学系获准开办荣誉学士课程，标志树仁的商科与社会科学课程体系继续完善。</t>
-    </r>
-  </si>
-  <si>
-    <t>T26</t>
-  </si>
-  <si>
-    <t>Multiple Programmes Complete Accreditation; First Cohort of Bachelor's Students Graduated</t>
-  </si>
-  <si>
-    <t>In 2005, programmes in History, Sociology, and English Language and Literature passed accreditation, the first cohort of honours bachelor's students graduated, and the Residential and Amenities Building was completed.</t>
-  </si>
-  <si>
-    <t>多個課程完成評審，首批學士學生畢業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2005年，歷史、社會學及英國語言文學等課程通過評審，首批榮譽學士學生畢業，宿舍文康大樓亦落成。 </t>
-  </si>
-  <si>
-    <t>多个课程完成评审，首批学士学生毕业</t>
-  </si>
-  <si>
-    <t>2005年，历史、社会学及英国语言文学等课程通过评审，首批荣誉学士学生毕业，宿舍文康大楼亦落成。</t>
-  </si>
-  <si>
-    <t>B14, B16</t>
-  </si>
-  <si>
-    <t>T27</t>
-  </si>
-  <si>
-    <t>Title Changed to Hong Kong Shue Yan University—Hong Kong's First Private University</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>In 2006, Shue Yan was approved by the Chief Executive-in-Council to be retitled as change its title to Hong Kong Shue Yan University, becoming Hong Kong's first private university.</t>
-  </si>
-  <si>
-    <t>正名為香港樹仁大學：香港首間私立大學</t>
-  </si>
-  <si>
-    <t>正名为香港树仁大学：香港首间私立大学</t>
-  </si>
-  <si>
-    <t>2006年，树仁获行政长官会同行政会议批准正名为香港树仁大学，成为香港首间私立大学。</t>
-  </si>
-  <si>
-    <t>T28</t>
-  </si>
-  <si>
-    <t>新校名正式啟用：進入大學發展階段</t>
-  </si>
-  <si>
-    <t>新校名正式启用：进入大学发展阶段</t>
-  </si>
-  <si>
-    <t>2007年2月，香港树仁大学举行正名典礼，新校名正式启用，标志树仁由专上学院进入大学发展的新阶段。</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>photo-1</t>
-  </si>
-  <si>
-    <t>photo-2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>photo-3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>photo-4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>photo-5</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P01</t>
-  </si>
-  <si>
-    <r>
-      <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>萬春先</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>先生、阮雁鳴先生</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>胡鸿烈与钟期荣在跑马地成和道创办香港树仁书院，以响应本地专上教育学额不足。</t>
-  </si>
-  <si>
-    <t>树仁成立校董会，汇聚贤达，推动校务与校舍建设。校董会成员包括主席黄宣平议员，校董成员包括邵逸夫先生、来自《星岛日报》的胡仙女士、中华汽车创办人颜成坤议员、香港塑料业厂商会创会人之一丁熊照先生、晏务理博士、安子介议员、白约翰主教、贝纳祺御用大律师、查济民先生、陈普芬议员、陈存仁先生、钟期荣博士、龚乐年神父、胡鸿烈议员、霍宝材先生、烈显伦御用大律师、刘汉栋先生、陆荫百先生、伍秉坚议员、岑才生先生、岑维休先生、曾汉文先生、万春先先生、阮雁鸣先生。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971/image2.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P02</t>
-  </si>
-  <si>
-    <t>1971–1972</t>
-  </si>
-  <si>
-    <t>Shue Yan had already established scholarships in its early years and entered into an academic collaboration with Northeast Louisiana University in the United States, thereby expanding overseas learning opportunities for students.
-Source: (Left) Wah Kiu Yat Po, 29 June 1971 ; (Right) Wah Kiu Yat Po, 4 August 1971</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971-1972/image3.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1971-1972/image4.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P03</t>
-  </si>
-  <si>
-    <t>Shue Yan College Limited adopted its Memorandum and Articles of Association, formally establishing the institution's corporate and governance framework.</t>
-  </si>
-  <si>
-    <t>樹仁書院有限公司通過組織章程大綱及細則，正式確立院校的法人與管治架構。</t>
-  </si>
-  <si>
-    <t>树仁书院有限公司通过组织章程大纲及细则，正式确立院校的法人与管治架构。 </t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image6.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P04</t>
-  </si>
-  <si>
-    <t>校監胡鴻烈代表樹仁書院赴美考察，與多所大學商討學術合作。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image7.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image8.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P05</t>
-  </si>
-  <si>
-    <t>Shue Yan and Northeast Louisiana University jointly launched their first credit-bearing summer programme, taught by visiting scholars and American student tutors.</t>
-  </si>
-  <si>
-    <t>樹仁與美國東北路易斯安那大學合辦首個可計學分暑期課程，由訪港學者及美國學生導師授課。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image9.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image10.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P06</t>
-  </si>
-  <si>
-    <t>The campus at no. 7 Wan Chai Gap Road opened in 1972, serving as Shue Yan's secondary section during the day and its post-secondary evening division at night.</t>
-  </si>
-  <si>
-    <t>灣仔峽道7號校舍啟用，日間供樹仁書院中學部學生上課，晚間則由樹仁書院大專部夜組使用。</t>
-  </si>
-  <si>
-    <t>湾仔峡道7号校舍启用，日间供树仁书院中学部学生上课，晚间则由树仁书院大专部夜组使用。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image11.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1972/image12.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P07</t>
-  </si>
-  <si>
-    <t>Governor Sir Murray MacLehose paid a private visit to the Wan Chai Gap Road campus and learned about Shue Yan’s founding story and development.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>港督麥理浩爵士私人到訪峽道校舍，了解樹仁的創校經過與發展。</t>
-  </si>
-  <si>
-    <t>港督麦理浩爵士私人到访峡道校舍，了解树仁的创校经过与发展。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image13.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image14.jpg</t>
-  </si>
-  <si>
-    <t>P08</t>
-  </si>
-  <si>
-    <t>教育署首次正式到访树仁位于跑马地成和道的专上校舍。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image15.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1974/image16.jpg</t>
-  </si>
-  <si>
-    <t>P09</t>
-  </si>
-  <si>
-    <t>教育署專家首次評核樹仁學術水平，其後教育署署長 K. W. J. Topley 再次視察。 </t>
-  </si>
-  <si>
-    <t>教育署专家首次评核树仁学术水平，其后教育署署长 K. W. J. Topley 再次视察。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1975/image17.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1975/image18.jpg</t>
-  </si>
-  <si>
-    <t>P10</t>
-  </si>
-  <si>
-    <t>Shue Yan was registered under the Post Secondary Colleges Ordinance, became authorised to award post-secondary diplomas, and formally adopted the name Shue Yan College.</t>
-  </si>
-  <si>
-    <t>樹仁按《專上學院條例》註冊，獲准頒授專上文憑，並正式定名為樹仁學院。</t>
-  </si>
-  <si>
-    <t>树仁按《专上学院条例》注册，获准颁授专上文凭，并正式定名为树仁学院。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1976/image20.jpg</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>Governor Sir Murray MacLehose presented Dr. Hu Hung-lick with the insignia of an Officer of the Order of the British Empire in recognition of his public service.</t>
-  </si>
-  <si>
-    <t>港督麥理浩爵士向胡鴻烈頒授大英帝國官佐勳章，表揚其公共服務。</t>
-  </si>
-  <si>
-    <t>港督麦理浩爵士向胡鸿烈颁授大英帝国官佐勋章，表扬其公共服务。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1976/image21.jpg</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>Shue Yan College moved to a seven-storey campus on Monmouth Path in Wan Chai, expanding its teaching space.</t>
-  </si>
-  <si>
-    <t>樹仁學院遷入灣仔萬茂里七層高的獨立校舍，擴充教學空間。</t>
-  </si>
-  <si>
-    <t>树仁学院迁入湾仔万茂里七层高的独立校舍，扩充教学空间。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1977/image22.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1977/image23.jpg</t>
-  </si>
-  <si>
-    <t>P13</t>
-  </si>
-  <si>
-    <t>Students overwhelmingly backed the four-year curriculum; the College declined government funding and rejected the proposed 2-2-1 system.
-Source: (Right) The Kung Sheung Daily News, 4 November 1978</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>學生以壓倒性多數支持四年制；學院拒絕政府資助，不接受建議的「二二一」學制。
-來源: (右) 《香港工商日報》1978年11月4日</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>学生以压倒性多数支持四年制；学院拒绝政府资助，不接受建议的「二二一」学制。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>来源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>: (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>右</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>《香港工商日报》</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1978</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1978/image24.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1978/image25.jpg</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>Shue Yan joined the Association of Southeast Asian Institutions of Higher Learning, gaining regional recognition for its academic standards.</t>
-  </si>
-  <si>
-    <t>樹仁加入東南亞高等教育協會，其學術水平獲區域認可。</t>
-  </si>
-  <si>
-    <t>树仁加入东南亚高等教育协会，其学术水平获区域认可。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image26.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image27.jpg</t>
-  </si>
-  <si>
-    <t>P15</t>
-  </si>
-  <si>
-    <t>Shue Yan and Northeast Louisiana University jointly launched the College’s first  MBA programme, creating a new pathway for postgraduate study.</t>
-  </si>
-  <si>
-    <t>樹仁與東北路易斯安那大學合辦學院首個工商管理碩士課程，開拓研究生進修途徑。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image28.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image29.jpg</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>Student representatives presented the Director of Education, K. W. J. Topley, with a campus-wide petition defending Shue Yan’s four-year curriculum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 學生代表向教育署署長 K. W. J. Topley 遞交全校聯署，捍衛樹仁四年制課程。</t>
-  </si>
-  <si>
-    <t>学生代表向教育署署长 K. W. J. Topley 递交全校联署，捍卫树仁四年制课程。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image30.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image31.jpg</t>
-  </si>
-  <si>
-    <t>P17</t>
-  </si>
-  <si>
-    <t>Acting Governor Sir Denys Roberts visited Shue Yan, meeting staff and students and inspecting its teaching environment.</t>
-  </si>
-  <si>
-    <t>署理港督羅弼時爵士到訪樹仁，會見學院師生並視察教學環境。</t>
-  </si>
-  <si>
-    <t>署理港督罗弼时爵士到访树仁，会见学院师生并视察教学环境。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1980/image32.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1980/image33.jpg</t>
-  </si>
-  <si>
-    <t>P18</t>
-  </si>
-  <si>
-    <t>樹仁與美國阿拉巴馬大學合辦首個社會工作碩士課程，回應專業人才需求。</t>
-  </si>
-  <si>
-    <t>树仁与美国阿拉巴马大学合办首个社会工作硕士课程，响应专业人才需求。 </t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1981/image34.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1981/image35.jpg</t>
-  </si>
-  <si>
-    <t>P19</t>
-  </si>
-  <si>
-    <t>Governor Sir Edward Youde attended the foundation stone-laying ceremony for Shue Yan College’s new Braemar Hill campus. The self-financed development required 176 concrete piles to be driven into the steep hillside, marking a major milestone in the College’s campus development.</t>
-  </si>
-  <si>
-    <t>港督尤德爵士出席樹仁學院寶馬山新校舍奠基禮。這項自資建校工程須在陡峭山坡打下176根水泥樁，標誌學院校園發展邁出重要一步。</t>
-  </si>
-  <si>
-    <t>港督尤德爵士出席树仁学院宝马山新校舍奠基礼。这项自资建校工程须在陡峭山坡打下176根水泥桩，标志学院校园发展迈出重要一步。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1983/image36.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1983/image37.jpg</t>
-  </si>
-  <si>
-    <t>P20</t>
-  </si>
-  <si>
-    <t>Shue Yan College held the topping-off ceremony for its Main Academic Building on the Braemar Hill campus, marking the gradual completion of the new campus construction. </t>
-  </si>
-  <si>
-    <t>樹仁學院於寶馬山教學大樓舉行平頂禮，見證新校舍工程逐步完成。</t>
-  </si>
-  <si>
-    <t>树仁学院于宝马山新教学大楼举行平顶礼，见证新校舍工程逐步完成。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image38.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image39.jpg</t>
-  </si>
-  <si>
-    <t>P21</t>
-  </si>
-  <si>
-    <t>China’s Vice Minister of Education, Huang Xinbai, visited Shue Yan, strengthening the College’s growing academic ties with mainland China.</t>
-  </si>
-  <si>
-    <t>中國教育部副部長黃辛白訪問樹仁，加強學院與內地逐步建立的學術聯繫。</t>
-  </si>
-  <si>
-    <t>中国教育部副部长黄辛白访问树仁，加强学院与内地逐步建立的学术联系。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1984/image40.jpg</t>
-  </si>
-  <si>
-    <t>P22</t>
-  </si>
-  <si>
-    <t>Hu Fai-chung joined Shue Yan College in 1985, beginning a long-term contribution to the University’s administration, teaching and learning development, campus expansion, and pursuit of university status.</t>
-  </si>
-  <si>
-    <t>胡懷中於1985年加入樹仁學院，自此在大學行政管理、教與學發展、校舍擴充及大學正名等方面作出長期貢獻。</t>
-  </si>
-  <si>
-    <t>胡怀中于1985年加入树仁学院，自此在大学行政管理、教与学发展、校舍扩充及大学正名等方面作出长期贡献。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1985/image41.jpg</t>
-  </si>
-  <si>
-    <t>P23</t>
-  </si>
-  <si>
-    <t>The new Shue Yan College campus on Braemar Hill officially opened, providing a permanent base for the College’s teaching and institutional development.</t>
-  </si>
-  <si>
-    <t>樹仁學院寶馬山新校舍正式啟用，為學院教學與長遠發展提供永久校園基礎。</t>
-  </si>
-  <si>
-    <t>树仁学院宝马山新校舍正式启用，为学院教学与长远发展提供永久校园基础。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image42.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image43.jpg</t>
-  </si>
-  <si>
-    <t>P24</t>
-  </si>
-  <si>
-    <t>Shue Yan and Peking University signed a five-year academic cooperation agreement covering faculty and student exchanges, postgraduate training, and legal education.</t>
-  </si>
-  <si>
-    <t>樹仁與北京大學簽署五年學術合作協議，涵蓋師生交流、研究生培養及法律教育。 </t>
-  </si>
-  <si>
-    <t>树仁与北京大学签署五年学术合作协议，涵盖师生交流、研究生培养及法律教育。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image44.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1986/image45.jpg</t>
-  </si>
-  <si>
-    <t>P25</t>
-  </si>
-  <si>
-    <t>國家教育委員會代表團訪問樹仁；北京大學校長丁石孫在歡迎會致辭。</t>
-  </si>
-  <si>
-    <t>国家教育委员会代表团访问树仁；北京大学校长丁石孙在欢迎会致辞。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image46.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P26</t>
-  </si>
-  <si>
-    <t>胡鴻烈於1987年獲委任為第六屆全國政協委員，後續任第七屆委員，並於1993年起出任第八、九屆全國政協常委。</t>
-  </si>
-  <si>
-    <t>胡鸿烈于1987年获委任为第六届全国政协委员，后续任第七届委员，并于1993年起出任第八、九届全国政协常委。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image48.jpg</t>
-  </si>
-  <si>
-    <t>P27</t>
-  </si>
-  <si>
-    <t>胡鴻烈赴北京出席中國人民政治協商會議第六屆全國委員會第五次會議。</t>
-  </si>
-  <si>
-    <t>胡鸿烈赴北京出席中国人民政治协商会议第六届全国委员会第五次会议。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image49.jpg</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987/image50.jpg</t>
-  </si>
-  <si>
-    <t>P28</t>
-  </si>
-  <si>
-    <t>1987—1988</t>
-  </si>
-  <si>
-    <t>Shue Yan and Peking University jointly offered a Bachelor of Laws programme, which became Shue Yan’s first degree programme recognised by China’s State Education Commission.</t>
-  </si>
-  <si>
-    <t>樹仁與北京大學合辦法律學士課程，成為樹仁首個獲中國國家教育委員會認可的學位課程。</t>
-  </si>
-  <si>
-    <t>树仁与北京大学合办法律学士课程，成为树仁首个获中国国家教育委员会认可的学位课程。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1987-1988/image51.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P29</t>
-  </si>
-  <si>
-    <t>China’s State Education Commission donated more than 2,000 volumes on literature and history  to Shue Yan, enriching the College’s academic collection.</t>
-  </si>
-  <si>
-    <t>國家教育委員會向樹仁贈送逾二千冊文史典籍，充實學院的學術館藏。</t>
-  </si>
-  <si>
-    <t>国家教育委员会向树仁赠送逾二千册文史典籍，充实学院的学术馆藏。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image53.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image54.jpg</t>
-  </si>
-  <si>
-    <t>P30</t>
-  </si>
-  <si>
-    <t>Shue Yan students marched against the proposed conversion of Hong Kong’s four-year undergraduate structure to a three-year system.</t>
-  </si>
-  <si>
-    <t>樹仁學生遊行反對把香港四年制大學本科課程改為三年制。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>树仁学生游行反对把香港四年制大学本科课程改为三年制。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1988/image55.jpg</t>
-  </si>
-  <si>
-    <t>P31</t>
-  </si>
-  <si>
-    <t>Student representatives staged a four-day hunger strike after the government excluded Shue Yan from the publicly funded university system.</t>
-  </si>
-  <si>
-    <t>政府把樹仁排除於公立資助大學安排外，學生代表發起四日絕食抗議。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>政府把树仁排除于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+      <t>公立</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="SimSun"/>
         <charset val="134"/>
       </rPr>
-      <t>公立</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
       <t>资助大学安排外，学生代表发起四日绝食抗议。</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -1710,9 +1646,6 @@
   </si>
   <si>
     <t>The first cohort of 81 graduates from Shue Yan and Peking University’s joint Bachelor of Laws programme received their degrees in Beijing.</t>
-  </si>
-  <si>
-    <t>樹仁與北京大學合辦法律學士課程首屆八十一名畢業生在北京獲頒學位。</t>
   </si>
   <si>
     <t>树仁与北京大学合办法律学士课程首届八十一名毕业生在北京获颁学位。</t>
@@ -4533,9 +4466,6 @@
     <t>P110</t>
   </si>
   <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
     <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
   </si>
   <si>
@@ -5013,9 +4943,6 @@
     <t>《公務員薪俸檢討報告書》</t>
   </si>
   <si>
-    <t>公務員薪酬制度調整，提高大学學位持有人的待遇，影響專上学院文憑的認受性。</t>
-  </si>
-  <si>
     <t>《公务员薪俸检讨报告书》</t>
   </si>
   <si>
@@ -5040,11 +4967,152 @@
     <t>《中英联合声明》确立香港于1997年回归中国。</t>
   </si>
   <si>
-    <t>Education Commission Report No. 3</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1988 Report No. 3 standardised Hong Kong's undergraduate degrees to three years and entry to two years of </t>
+    <t>港府發表《教育委員會第三號報告書》</t>
+  </si>
+  <si>
+    <t>報告提出「四改三」，統一香港高等教育學制為三年制課程，入學資格則統一為兩年制預科（中六、中七）畢業。</t>
+  </si>
+  <si>
+    <t>港府发表《教育委员会第三号报告书》</t>
+  </si>
+  <si>
+    <t>报告提出「四改三」，统一香港高等教育学制为三年制课程，入学资格则统一为两年制预科（中六、中七）毕业。</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Hong Kong 1990 Plan</t>
+  </si>
+  <si>
+    <t>The government announced a major expansion of university places, promoting the massification of higher education.</t>
+  </si>
+  <si>
+    <t>《香港1990》計劃</t>
+  </si>
+  <si>
+    <t>政府宣布大幅增加大學學額，推動高等教育由精英化走向大眾化。</t>
+  </si>
+  <si>
+    <t>《香港1990》计划</t>
+  </si>
+  <si>
+    <t>政府宣布大幅增加大学学额，推动高等教育由精英化走向大众化。</t>
+  </si>
+  <si>
+    <r>
+      <t>Wave of</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Upgrading into University</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Several tertiary institutions attained university status, transforming Hong Kong's higher education landscape.</t>
+  </si>
+  <si>
+    <t>香港「大學升格潮」</t>
+  </si>
+  <si>
+    <t>政府資助的專上院校先後升格為大學，重塑香港高等教育版圖。</t>
+  </si>
+  <si>
+    <t>香港「大学升格潮」</t>
+  </si>
+  <si>
+    <t>政府资助的专上院校先后升格为大学，重塑香港高等教育版图。</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>The Establishment of HKSAR</t>
+  </si>
+  <si>
+    <t>The establishment of the Hong Kong Special Administrative Region.</t>
+  </si>
+  <si>
+    <t>香港回歸</t>
+  </si>
+  <si>
+    <t>香港特別行政區成立。</t>
+  </si>
+  <si>
+    <t>香港回归</t>
+  </si>
+  <si>
+    <t>香港特别行政区成立。</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>Education Reform Proposals</t>
+  </si>
+  <si>
+    <t>The government proposed comprehensive education reforms emphasizing lifelong learning and educational quality.</t>
+  </si>
+  <si>
+    <t>《教育改革建議》</t>
+  </si>
+  <si>
+    <t>政府提出全面教育改革，強調終身學習及提升教育質素。</t>
+  </si>
+  <si>
+    <t>《教育改革建议》</t>
+  </si>
+  <si>
+    <t>政府提出全面教育改革，强调终身学习及提升教育质素。</t>
+  </si>
+  <si>
+    <t>Reform Proposals for the Education System in Hong Kong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The reform proposal introduced the "3-3-4" academic structure, restoring four-year undergraduate education while promoting lifelong learning and whole-person development for a knowledge-based society. Hong Kong Shue Yan remained the only local higher education institution to retain a four-year undergraduate curriculum. </t>
+  </si>
+  <si>
+    <t>《教育制度檢討改革方案》</t>
+  </si>
+  <si>
+    <t xml:space="preserve">《教育制度檢討改革方案》提出香港教育改革的新方向，由沿用多年的三年大學學制，逐步改革為「三三四」學制（3年初中、3年高中、4年大學），並倡導由精英教育邁向終身學習及全人教育，以配合知識型社會的發展。樹仁則成為香港唯一一直堅持四年制本科教育的高等院校。 </t>
+  </si>
+  <si>
+    <t>《教育制度检讨改革方案》</t>
+  </si>
+  <si>
+    <t>《教育制度检讨改革方案》提出香港教育改革的新方向，由沿用多年的三年大学学制，逐步改革为「三三四」学制（3年初中、3年高中、4年大学），并倡导由精英教育迈向终身学习及全人教育，以配合知识型社会的发展。树仁则成为香港唯一一直坚持四年制本科教育的高等院校。</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>2000-2002</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Launch of Associate Degree </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Programmes</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>To achieve the goal of 60% post-secondary participation, the Government introduced Associate Degree</t>
     </r>
     <r>
       <rPr>
@@ -5052,166 +5120,28 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">A-level </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>(S6–7).</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>港府發表《教育委員會第三號報告書》</t>
-  </si>
-  <si>
-    <t>報告提出「四改三」，統一香港高等教育學制為三年制課程，入學資格則統一為兩年制預科（中六、中七）畢業。</t>
-  </si>
-  <si>
-    <t>港府发表《教育委员会第三号报告书》</t>
-  </si>
-  <si>
-    <t>报告提出「四改三」，统一香港高等教育学制为三年制课程，入学资格则统一为两年制预科（中六、中七）毕业。</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Hong Kong 1990 Plan</t>
-  </si>
-  <si>
-    <t>The government announced a major expansion of university places, promoting the massification of higher education.</t>
-  </si>
-  <si>
-    <t>《香港1990》計劃</t>
-  </si>
-  <si>
-    <t>政府宣布大幅增加大學學額，推動高等教育由精英化走向大眾化。</t>
-  </si>
-  <si>
-    <t>《香港1990》计划</t>
-  </si>
-  <si>
-    <t>政府宣布大幅增加大学学额，推动高等教育由精英化走向大众化。</t>
-  </si>
-  <si>
-    <r>
-      <t>Wave of</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Upgrading into University</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Several tertiary institutions attained university status, transforming Hong Kong's higher education landscape.</t>
-  </si>
-  <si>
-    <t>香港「大學升格潮」</t>
-  </si>
-  <si>
-    <t>政府資助的專上院校先後升格為大學，重塑香港高等教育版圖。</t>
-  </si>
-  <si>
-    <t>香港「大学升格潮」</t>
-  </si>
-  <si>
-    <t>政府资助的专上院校先后升格为大学，重塑香港高等教育版图。</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>The Establishment of HKSAR</t>
-  </si>
-  <si>
-    <t>The establishment of the Hong Kong Special Administrative Region.</t>
-  </si>
-  <si>
-    <t>香港回歸</t>
-  </si>
-  <si>
-    <t>香港特別行政區成立。</t>
-  </si>
-  <si>
-    <t>香港回归</t>
-  </si>
-  <si>
-    <t>香港特别行政区成立。</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>Education Reform Proposals</t>
-  </si>
-  <si>
-    <t>The government proposed comprehensive education reforms emphasizing lifelong learning and educational quality.</t>
-  </si>
-  <si>
-    <t>《教育改革建議》</t>
-  </si>
-  <si>
-    <t>政府提出全面教育改革，強調終身學習及提升教育質素。</t>
-  </si>
-  <si>
-    <t>《教育改革建议》</t>
-  </si>
-  <si>
-    <t>政府提出全面教育改革，强调终身学习及提升教育质素。</t>
-  </si>
-  <si>
-    <t>Reform Proposals for the Education System in Hong Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The reform proposal introduced the "3-3-4" academic structure, restoring four-year undergraduate education while promoting lifelong learning and whole-person development for a knowledge-based society. Hong Kong Shue Yan remained the only local higher education institution to retain a four-year undergraduate curriculum. </t>
-  </si>
-  <si>
-    <t>《教育制度檢討改革方案》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《教育制度檢討改革方案》提出香港教育改革的新方向，由沿用多年的三年大學學制，逐步改革為「三三四」學制（3年初中、3年高中、4年大學），並倡導由精英教育邁向終身學習及全人教育，以配合知識型社會的發展。樹仁則成為香港唯一一直堅持四年制本科教育的高等院校。 </t>
-  </si>
-  <si>
-    <t>《教育制度检讨改革方案》</t>
-  </si>
-  <si>
-    <t>《教育制度检讨改革方案》提出香港教育改革的新方向，由沿用多年的三年大学学制，逐步改革为「三三四」学制（3年初中、3年高中、4年大学），并倡导由精英教育迈向终身学习及全人教育，以配合知识型社会的发展。树仁则成为香港唯一一直坚持四年制本科教育的高等院校。</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>2000-2002</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Launch of Associate Degree </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>Programmes</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>To achieve the goal of 60% post-secondary participation, the Government introduced Associate Degree</t>
+      <t xml:space="preserve"> programmes in 2000 and encouraged universities and private institutions to offer self-financing post-secondary programmes.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>推行副學士課程項目</t>
+  </si>
+  <si>
+    <t>推行副学士课程项目</t>
+  </si>
+  <si>
+    <t>为达至六成青年接受专上教育的目标，政府于2000年推出副学士课程，鼓励大学及私立院校开办自资专上课程。</t>
+  </si>
+  <si>
+    <t>2004–2007</t>
+  </si>
+  <si>
+    <t>Building Hong Kong as a Regional Education Hub</t>
+  </si>
+  <si>
+    <r>
+      <t>Proposed in the 2004 Policy A</t>
     </r>
     <r>
       <rPr>
@@ -5219,44 +5149,15 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> programmes in 2000 and encouraged universities and private institutions to offer self-financing post-secondary programmes.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>推行副學士課程項目</t>
-  </si>
-  <si>
-    <t>推行副学士课程项目</t>
-  </si>
-  <si>
-    <t>为达至六成青年接受专上教育的目标，政府于2000年推出副学士课程，鼓励大学及私立院校开办自资专上课程。</t>
-  </si>
-  <si>
-    <t>2004–2007</t>
-  </si>
-  <si>
-    <t>Building Hong Kong as a Regional Education Hub</t>
-  </si>
-  <si>
-    <r>
-      <t>Proposed in the 2004 Policy A</t>
+      <t>ddress, advanced by a 2006 cross bureau steering committee, and reaffirmed in 2007,</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
+        <color rgb="FF262626"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>ddress, advanced by a 2006 cross bureau steering committee, and reaffirmed in 2007,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> the regional education hub initiative raised the non-local student quota for UGC-funded universities from 10% to 20%, eased entry rules, offered scholarships, and promoted Hong Kong education overseas. </t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -5266,9 +5167,6 @@
   </si>
   <si>
     <t>提出打造香港成为区域教育枢纽理念</t>
-  </si>
-  <si>
-    <t>2004年《施政报告》首提，2006年设跨局委员会，2007年重申。主要措施包括：教资会资助院校非本地学生学额上限由10%提高至20%、放宽入境、提供奖学金及海外推广。</t>
   </si>
   <si>
     <t>B17</t>
@@ -5763,10 +5661,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>區域教育中心計畫於 2004 年在施政報告中提出，2006 年由跨部門督導委員會推進，2007 年再次確認，該計畫將大學教育資助委員會資助大學的非本地學生配額從 10% 提高到 20%，放寬入學規則，提供獎學金，並促進香港教育走向海外。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>The University celebrated President Dr. Henry Hu Hung-lick’s 101st birthday, honouring his lifelong service.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5887,6 +5781,251 @@
   </si>
   <si>
     <t>The University of Hong Kong awarded Dr. Henry Hu Hung-lick an honorary Doctor of Social Sciences for his long-standing contributions to education and public service.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2006, Shue Yan was approved by the Chief Executive-in-Council to change its title to Hong Kong Shue Yan University, becoming Hong Kong's first private university.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Education Commission Report No. 3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, to be preceded by two years of A-levels (S6-7).</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，工商管理系、輔導及心理學系獲准開辦榮譽學士課程，進一步擴大樹仁的學位課程架構。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004年，經濟學系獲准開辦榮譽學士課程，標誌樹仁的商科課程體系繼續完善。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004年，经济学系获准开办荣誉学士课程，标志树仁的商科课程体系继续完善。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2004, the Department of Economics was approved to offer an honours bachelor's degree programme, marking the continued refinement of Shue Yan's business programme system.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>公務員薪酬制度調整，提高大學學位持有人的待遇，影響專上學院文憑的認受性。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>區域教育中心計劃於 2004 年在施政報告中提出，2006 年由跨部門督導委員會推進，2007 年再次確認，該計劃將大學教育資助委員會資助大學的非本地學生配額從 10% 提高到 20%，放寬入學規則，提供獎學金，並促進香港教育走向海外。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>区域教育中心计划于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2004 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年在施政报告中提出，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2006 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年由跨部门督导委员会推进，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2007 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年再次确认，该计划将大学教育资助委员会资助大学的非本地学生配额从</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提高到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，放宽入学规则，提供奖学金，并促进香港教育走向海外。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁與北京大學合辦法律學士課程，首屆八十一名畢業生在北京獲頒學位。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>樹仁始終堅持以維持四年制教育為接受政府資助的前提，而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1990</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年前後學生爭取政府資助的訴求，則揭示了私立專上教育所面對的學費負擔與教育公平挑戰。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>树仁始终坚持以维持四年制教育为接受政府资助的前提，而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1990</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年前后学生争取政府资助的诉求，则揭示了私立专上教育所面对的学费负担与教育公平挑战。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Student Petitions and Upholding the 4-Year Principle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shue Yan consistently upheld the preservation of its four-year educational system and rejection to changing it as a precondition for receiving government funding. Students’ appeals for government support around 1990 revealed the challenges of tuition affordability and educational equity faced by the private post-secondary education sector.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1987年，树仁与北京大学合办法律本科学士学位课程，成为学院拓展内地学术合作的重要里程碑。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6161,12 +6300,6 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
@@ -6195,6 +6328,13 @@
     <font>
       <sz val="8"/>
       <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="134"/>
@@ -6271,7 +6411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6400,13 +6540,16 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6415,10 +6558,16 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6773,10 +6922,10 @@
         <v>1949</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>1026</v>
+        <v>1009</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>1025</v>
+        <v>1008</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>11</v>
@@ -6808,19 +6957,19 @@
         <v>18</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1027</v>
+        <v>1010</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="G3" s="42" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="41" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>15</v>
@@ -6872,7 +7021,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>1028</v>
+        <v>1011</v>
       </c>
       <c r="E5" s="42" t="s">
         <v>31</v>
@@ -6971,13 +7120,13 @@
         <v>55</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H8" s="38" t="s">
         <v>57</v>
@@ -7095,10 +7244,10 @@
         <v>84</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>1029</v>
+        <v>1012</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>85</v>
@@ -7127,13 +7276,13 @@
         <v>89</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="F13" s="41" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="H13" s="41" t="s">
         <v>91</v>
@@ -7219,7 +7368,7 @@
         <v>109</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>110</v>
@@ -7227,8 +7376,8 @@
       <c r="G16" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="38" t="s">
-        <v>112</v>
+      <c r="H16" s="51" t="s">
+        <v>1031</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>35</v>
@@ -7239,416 +7388,416 @@
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="40">
         <v>1988</v>
       </c>
       <c r="C17" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="E17" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="F17" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="G17" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="H17" s="41" t="s">
         <v>118</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>119</v>
       </c>
       <c r="I17" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="114">
+      <c r="A18" s="40" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="79.8">
-      <c r="A18" s="40" t="s">
-        <v>121</v>
       </c>
       <c r="B18" s="36">
         <v>1990</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="37" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G18" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>127</v>
+      <c r="H18" s="53" t="s">
+        <v>1028</v>
       </c>
       <c r="I18" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="36" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="36" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B19" s="40">
         <v>1995</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="41" t="s">
         <v>130</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>135</v>
       </c>
       <c r="I19" s="40" t="s">
         <v>58</v>
       </c>
       <c r="J19" s="40" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="40" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B20" s="36">
         <v>1996</v>
       </c>
       <c r="C20" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="38" t="s">
         <v>138</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>143</v>
       </c>
       <c r="I20" s="36" t="s">
         <v>51</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="36" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B21" s="40">
         <v>1999</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="41" t="s">
         <v>145</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>150</v>
       </c>
       <c r="I21" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J21" s="40" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="36" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B22" s="36">
         <v>2000</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="38" t="s">
         <v>153</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>158</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="40" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B23" s="40">
         <v>2001</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="41" t="s">
         <v>161</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>166</v>
       </c>
       <c r="I23" s="40" t="s">
         <v>51</v>
       </c>
       <c r="J23" s="40" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="36" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B24" s="36">
         <v>2002</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="38" t="s">
         <v>169</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>174</v>
       </c>
       <c r="I24" s="36" t="s">
         <v>51</v>
       </c>
       <c r="J24" s="36" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="40" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B25" s="40">
         <v>2003</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>180</v>
+        <v>1019</v>
       </c>
       <c r="G25" s="42" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H25" s="41" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I25" s="40" t="s">
         <v>51</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="68.400000000000006">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="57">
       <c r="A26" s="36" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B26" s="36">
         <v>2004</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>185</v>
+        <v>1022</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>187</v>
+        <v>179</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>1020</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>189</v>
+        <v>180</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>1021</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>51</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="36" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B27" s="40">
         <v>2005</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I27" s="40" t="s">
         <v>51</v>
       </c>
       <c r="J27" s="40" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="40" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B28" s="36">
         <v>2006</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>200</v>
+        <v>1016</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="H28" s="38" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="I28" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J28" s="36" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="36" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B29" s="40">
         <v>2007</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="I29" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -7701,19 +7850,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7721,34 +7870,34 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1012</v>
+        <v>995</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1031</v>
+        <v>1014</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1030</v>
+        <v>1013</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
@@ -7758,28 +7907,28 @@
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -7790,25 +7939,25 @@
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
@@ -7817,28 +7966,28 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>1013</v>
+        <v>996</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -7849,28 +7998,28 @@
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -7881,28 +8030,28 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -7913,28 +8062,28 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -7945,28 +8094,28 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -7977,28 +8126,28 @@
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -8009,25 +8158,25 @@
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -8036,25 +8185,25 @@
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -8066,28 +8215,28 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -8098,28 +8247,28 @@
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -8130,28 +8279,28 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8162,28 +8311,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8194,28 +8343,28 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8226,28 +8375,28 @@
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8258,28 +8407,28 @@
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8290,28 +8439,28 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8322,28 +8471,28 @@
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8354,25 +8503,25 @@
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8384,25 +8533,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8414,28 +8563,28 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8446,28 +8595,28 @@
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8478,25 +8627,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8507,25 +8656,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>1014</v>
+        <v>997</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8537,28 +8686,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>1015</v>
+        <v>998</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8569,25 +8718,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8599,28 +8748,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8631,25 +8780,25 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8661,28 +8810,28 @@
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8693,25 +8842,25 @@
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>381</v>
+        <v>1026</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8723,25 +8872,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8753,28 +8902,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8785,28 +8934,28 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8817,25 +8966,25 @@
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8847,28 +8996,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -8879,28 +9028,28 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>1016</v>
+        <v>999</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -8911,25 +9060,25 @@
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -8941,25 +9090,25 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -8971,28 +9120,28 @@
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -9003,28 +9152,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -9035,25 +9184,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -9065,22 +9214,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -9093,28 +9242,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>1017</v>
+        <v>1000</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -9125,28 +9274,28 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9157,25 +9306,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9187,25 +9336,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9217,25 +9366,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9247,28 +9396,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9279,25 +9428,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9309,25 +9458,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9339,25 +9488,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9369,57 +9518,57 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9431,25 +9580,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9461,25 +9610,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9491,87 +9640,87 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9583,25 +9732,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9613,25 +9762,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9643,25 +9792,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9673,25 +9822,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9703,25 +9852,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9733,25 +9882,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9763,28 +9912,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9795,28 +9944,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9827,28 +9976,28 @@
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>1018</v>
+        <v>1001</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -9859,25 +10008,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>1019</v>
+        <v>1002</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -9889,28 +10038,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>1020</v>
+        <v>1003</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -9921,25 +10070,25 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -9951,25 +10100,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>1021</v>
+        <v>1004</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -9981,28 +10130,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -10013,28 +10162,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -10045,22 +10194,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -10073,28 +10222,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -10105,25 +10254,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10135,28 +10284,28 @@
     </row>
     <row r="80" spans="1:14" ht="41.4">
       <c r="A80" s="2" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>1032</v>
+        <v>1015</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10167,25 +10316,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10197,25 +10346,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10227,22 +10376,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10254,88 +10403,88 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>1022</v>
+        <v>1005</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10346,60 +10495,60 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10410,28 +10559,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10442,22 +10591,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10470,28 +10619,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10502,677 +10651,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>1010</v>
+        <v>993</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>1023</v>
+        <v>1006</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>794</v>
+        <v>782</v>
+      </c>
+      <c r="B113" s="5">
+        <v>2026</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>1024</v>
+        <v>1007</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11184,148 +11333,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11333,45 +11482,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="15" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11570,103 +11719,103 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11677,22 +11826,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11703,22 +11852,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11729,22 +11878,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>874</v>
+        <v>861</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>1023</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -11755,334 +11904,334 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>883</v>
+        <v>1017</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>884</v>
+        <v>1018</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B12" s="2">
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>922</v>
+        <v>907</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>929</v>
+        <v>914</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>932</v>
+        <v>917</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>934</v>
+        <v>918</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12175,6 +12324,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12356,24 +12522,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12389,22 +12556,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73290A89-E957-4457-8479-850229D53E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771FB438-8949-411B-B50B-CC2BC7EC7FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -949,33 +949,6 @@
     <t>P01</t>
   </si>
   <si>
-    <r>
-      <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>萬春先</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>先生、阮雁鳴先生</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>胡鸿烈与钟期荣在跑马地成和道创办香港树仁书院，以响应本地专上教育学额不足。</t>
-  </si>
-  <si>
     <t>树仁成立校董会，汇聚贤达，推动校务与校舍建设。校董会成员包括主席黄宣平议员，校董成员包括邵逸夫先生、来自《星岛日报》的胡仙女士、中华汽车创办人颜成坤议员、香港塑料业厂商会创会人之一丁熊照先生、晏务理博士、安子介议员、白约翰主教、贝纳祺御用大律师、查济民先生、陈普芬议员、陈存仁先生、钟期荣博士、龚乐年神父、胡鸿烈议员、霍宝材先生、烈显伦御用大律师、刘汉栋先生、陆荫百先生、伍秉坚议员、岑才生先生、岑维休先生、曾汉文先生、万春先先生、阮雁鸣先生。</t>
   </si>
   <si>
@@ -1105,12 +1078,6 @@
     <t>P09</t>
   </si>
   <si>
-    <t>教育署專家首次評核樹仁學術水平，其後教育署署長 K. W. J. Topley 再次視察。 </t>
-  </si>
-  <si>
-    <t>教育署专家首次评核树仁学术水平，其后教育署署长 K. W. J. Topley 再次视察。</t>
-  </si>
-  <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1975/image17.jpg</t>
   </si>
   <si>
@@ -1322,9 +1289,6 @@
     <t>樹仁加入東南亞高等教育協會，其學術水平獲區域認可。</t>
   </si>
   <si>
-    <t>树仁加入东南亚高等教育协会，其学术水平获区域认可。</t>
-  </si>
-  <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image26.jpg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1352,12 +1316,6 @@
   </si>
   <si>
     <t>Student representatives presented the Director of Education, K. W. J. Topley, with a campus-wide petition defending Shue Yan’s four-year curriculum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 學生代表向教育署署長 K. W. J. Topley 遞交全校聯署，捍衛樹仁四年制課程。</t>
-  </si>
-  <si>
-    <t>学生代表向教育署署长 K. W. J. Topley 递交全校联署，捍卫树仁四年制课程。</t>
   </si>
   <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/1979/image30.jpg</t>
@@ -2789,9 +2747,6 @@
     <t>The Department of English Language and Literature underwent a validation from 27 to 29 April.</t>
   </si>
   <si>
-    <t>英文語文學系於4月27至29日進行課程評審</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -2877,9 +2832,6 @@
     <t>Shue Yan College underwent an institutional review from 10 to 12 May, preparing for university status accreditation.</t>
   </si>
   <si>
-    <t>樹仁學院於5月10至12日進行院校評審，為升格大學作準備</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -3306,11 +3258,6 @@
     <t>P72</t>
   </si>
   <si>
-    <t>大学首次独立开办硕士学位课程——辅导心理学社会科学硕士。
-來源： 《樹仁簡訊》2010年5月刊</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2010/image114.jpg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -3506,9 +3453,6 @@
     <t>P78</t>
   </si>
   <si>
-    <t>A HK$6.75 million grant from the  Research Grants Council‘s Institutional Development Scheme was received to establish Shue Yan’s first interdisciplinary research platform and strengthen its research capacity. </t>
-  </si>
-  <si>
     <t>仁大獲研究資助局的院校發展計劃撥款六百七十五萬港元，建立校內首個跨學科研究平台並提升研究能力。</t>
   </si>
   <si>
@@ -3570,9 +3514,6 @@
   </si>
   <si>
     <t>P82</t>
-  </si>
-  <si>
-    <t>A HK$6.2-million grant was received from the Research Grant Council’s  Institutional Development Scheme to expand interdisciplinary infrastructure for evidence-based practice and research.</t>
   </si>
   <si>
     <t>仁大獲研究資助局的院校發展計劃撥款六百二十萬港元擴充循證實踐及研究的跨學科基礎設施。</t>
@@ -3920,9 +3861,45 @@
     <t>In 2020/21, HKSYU received HK$16.4 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Arts, Culture and Technology.</t>
   </si>
   <si>
-    <t>2020/21 年, 樹仁獲自資專上教育提升及啟動補助金 一千六百四十萬元，發展藝術、文化及科技榮譽社會科學學士課程。</t>
-  </si>
-  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image141.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image142.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P94</t>
+  </si>
+  <si>
+    <t>The Dr. Francis Cheung Business Analytics Research Centre was established with a donation from Dr. Francis Cheung to advance interdisciplinary big-data research and evidence-based decision-making across sectors.</t>
+  </si>
+  <si>
+    <t>由張舜堯博士捐款成立的張舜堯博士商業分析研究中心啟用，致力推動跨學科大數據研究及各界循證決策。</t>
+  </si>
+  <si>
+    <t>由张舜尧博士捐款成立的张舜尧博士商业分析研究中心启用，致力推动跨学科大数据研究及各界循证决策。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image145.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>Shue Yan launched Hong Kong’s first virtual museum of national intangible cultural heritage, digitally showcasing the Yulan Festival. This digital humanities project was selected as one of the 25 representative showcase projects at the Innotech Expo, organised by Our Hong Kong Foundation.  </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>树仁推出香港首个国家级非物质文化遗产虚拟博物馆，以数字形式展示盂兰胜会。该数字人文项目获团结香港基金主办的创科博览选为香港</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -3930,17 +3907,33 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">2020/21 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>年</t>
-    </r>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>个创科代表性展示项目之一。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image146.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image147.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P96</t>
+  </si>
+  <si>
+    <t>In 2022/23, Shue Yan received HK$19.5 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSc (Hons) in Digital Solutions for Entertainment and Game Applications.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -3948,17 +3941,104 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>树仁获自资专上教育提升及启动补助金</t>
-    </r>
+      <t xml:space="preserve">2022/23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>年度，仁大获批自资专上教育提升及启动补助金一千九百五十万元，发展娱乐及游戏应用数码方案荣誉理学士课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image148.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image149.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P97</t>
+  </si>
+  <si>
+    <t>The Social Work Department launched a government-commissioned one-stop digital information gateway for carers, improving timely access to support information.</t>
+  </si>
+  <si>
+    <t>社会工作学系推出政府委托的一站式照顾者数码资讯闸道，改善支援资讯的及时获取。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image150.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>An interdisciplinary conference on youth-identity translated longitudinal research into practical insights for programmes, policy, and evidence-based youth development.</t>
+  </si>
+  <si>
+    <r>
+      <t>跨學科青年身份認同會議把縱向研究轉化為課程、政策及循證青年發展的實務</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洞察</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>。 </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>跨学科青年身份认同会议把纵向研究转化为课程、政策及循证青年发展的实务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洞察</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image151.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>2023/24年，仁大獲批自資專上教育提升及啟動補助一千四百六十萬元，發展法證及偵緝心理學榮譽社會科學學士課程。 </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -3966,57 +4046,81 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>一千六百四十万元，发展艺术、文化及科技荣誉社会科学学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image141.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2021/image142.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P94</t>
-  </si>
-  <si>
-    <t>The Dr. Francis Cheung Business Analytics Research Centre was established with a donation from Dr. Francis Cheung to advance interdisciplinary big-data research and evidence-based decision-making across sectors.</t>
-  </si>
-  <si>
-    <t>由張舜堯博士捐款成立的張舜堯博士商業分析研究中心啟用，致力推動跨學科大數據研究及各界循證決策。</t>
-  </si>
-  <si>
-    <t>由张舜尧博士捐款成立的张舜尧博士商业分析研究中心启用，致力推动跨学科大数据研究及各界循证决策。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image145.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P95</t>
-  </si>
-  <si>
-    <t>Shue Yan launched Hong Kong’s first virtual museum of national intangible cultural heritage, digitally showcasing the Yulan Festival. This digital humanities project was selected as one of the 25 representative showcase projects at the Innotech Expo, organised by Our Hong Kong Foundation.  </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>树仁推出香港首个国家级非物质文化遗产虚拟博物馆，以数字形式展示盂兰胜会。该数字人文项目获团结香港基金主办的创科博览选为香港</t>
+      <t>2023/24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，仁大获批自资专上教育提升及启动补助一千四百六十万元，发展法证及侦缉心理学荣誉社会科学学士课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image152.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image153.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>An AI- and VR-enabled martial arts exhibition documented Ving Tsun and Tai Chi, preserving cultural heritage and encouraging youth participation.</t>
+  </si>
+  <si>
+    <t>結合人工智能及虛擬實境的武術展覽記錄詠春與太極，保存文化並鼓勵青年參與。 </t>
+  </si>
+  <si>
+    <t>结合人工智能及虚拟实境的武术展览记录咏春与太极，保存文化并鼓励青年参与。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image154.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P101</t>
+  </si>
+  <si>
+    <t>The Mrs. Dorothy Koo and Dr. Ti Hua Koo Plaza, redeveloped with their donations, opened with advanced audiovisual facilities.</t>
+  </si>
+  <si>
+    <t>由顧鐵華、費肇芬捐款重建的伉儷廣場啟用，並配備先進影音設施。</t>
+  </si>
+  <si>
+    <t>由顾铁华、费肇芬捐款重建的伉俪广场启用，并配备先进影音设施。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image155.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image156.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P102</t>
+  </si>
+  <si>
+    <t>The Tin Ka Ping Teaching and Research Centre for Filial Piety opened to connect interdisciplinary research, moral education, cultural heritage, and school outreach.</t>
+  </si>
+  <si>
+    <t>田家炳孝道文化教研中心啟用，連結跨學科研究、品德教育、文化傳承及學校外展。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>田家炳孝道文化教研中心启用，连结跨学科研究、品德教育、文化传承及学校外展。</t>
     </r>
     <r>
       <rPr>
@@ -4025,33 +4129,168 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>个创科代表性展示项目之一。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image146.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2022/image147.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P96</t>
-  </si>
-  <si>
-    <t>In 2022/23, Shue Yan received HK$19.5 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSc (Hons) in Digital Solutions for Entertainment and Game Applications.</t>
-  </si>
-  <si>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image157.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image158.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P103</t>
+  </si>
+  <si>
+    <t>The University launched Hong Kong’s first one-year International Foundation Year Programme for international students, with a certificate awarded upon completion.</t>
+  </si>
+  <si>
+    <t>大學推出香港首個專為國際學生而設的一年制大學先修課程證書。</t>
+  </si>
+  <si>
+    <t>大学推出香港首个专为国际学生而设的一年制大学先修课程证书。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image159.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image160.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P104</t>
+  </si>
+  <si>
+    <t>Yang Wei from the Department of Sociology became Shue Yan’s first Doctor of Philosophy graduate, marking a milestone for the Graduate School.</t>
+  </si>
+  <si>
+    <t>社會學系楊薇成為樹仁首位哲學博士畢業生，標誌研究院重要里程碑。 </t>
+  </si>
+  <si>
+    <t>社会学系杨薇成为树仁首位哲学博士毕业生，标志研究院重要里程碑。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image161.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image162.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P105</t>
+  </si>
+  <si>
+    <t>An interdisciplinary esports project promoted youth empowerment while addressing gaming addiction through psychological, social, business, and policy research.</t>
+  </si>
+  <si>
+    <t>跨學科電競項目透過心理、社會、商業及政策研究，在應對遊戲成癮同時促進青年賦權。 </t>
+  </si>
+  <si>
+    <t>跨学科电竞项目透过心理、社会、商业及政策研究，在应对游戏成瘾同时促进青年赋权。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image163.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P106</t>
+  </si>
+  <si>
+    <t>The Emotion World project gamified evidence-based social-emotional learning and invited students to design AI-assisted characters to promote wellbeing education.</t>
+  </si>
+  <si>
+    <t>「情緒世界」把循證社交情緒學習遊戲化，並邀請學生設計人工智能輔助角色，推動福祉教育。 </t>
+  </si>
+  <si>
+    <t>「情绪世界」把循证社交情绪学习游戏化，并邀请学生设计人工智能辅助角色，推动福祉教育。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image164.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P107</t>
+  </si>
+  <si>
+    <t>跨越灰色数码鸿沟研究长者科技使用，推动年龄共融的数码创新。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image165.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P108</t>
+  </si>
+  <si>
+    <t>A longitudinal study of more than 8,000 participants examined resilience across adulthood to inform family, organisational, and public policy.</t>
+  </si>
+  <si>
+    <t>追蹤逾八千人的縱向研究，探討成年各階段的韌性，為家庭、機構及公共政策提供依據。</t>
+  </si>
+  <si>
+    <t>追踪逾八千人的纵向研究，探讨成年各阶段的韧性，为家庭、机构及公共政策提供依据。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image166.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P109</t>
+  </si>
+  <si>
+    <t>創校校監胡鴻烈於一百零五歲逝世，大學社群舉行喪禮及追思會，紀念其貢獻。 </t>
+  </si>
+  <si>
+    <t>创校校监胡鸿烈于一百零五岁逝世，大学社群举行丧礼及追思会，纪念其贡献。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image167.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image168.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P111</t>
+  </si>
+  <si>
+    <t>Shue Yan University participated in a special exhibition at the Guangdong Museum, creating an extension display on digital architectural heritage art.</t>
+  </si>
+  <si>
+    <t>仁大参与广东省博物馆特展，策划数码建筑遗产艺术延伸展区。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image170.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image171.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P112</t>
+  </si>
+  <si>
+    <t>Shue Yan University supported the Hong Kong Maritime Museum’s immersive VR archaeology exhibition “Voyage into Shu”, providing academic and curatorial advice.</t>
+  </si>
+  <si>
+    <t>仁大支持香港海事博物館「浮海探蜀」沉浸式考古VR展，並提供學術與策展顧問。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>仁大支持香港海事博物馆「浮海探蜀」沉浸式考古</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4059,189 +4298,101 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">2022/23 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>年度，仁大获批自资专上教育提升及启动补助金一千九百五十万元，发展娱乐及游戏应用数码方案荣誉理学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image148.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image149.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P97</t>
-  </si>
-  <si>
-    <t>The Social Work Department launched a government-commissioned one-stop digital information gateway for carers, improving timely access to support information.</t>
-  </si>
-  <si>
-    <t>社会工作学系推出政府委托的一站式照顾者数码资讯闸道，改善支援资讯的及时获取。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image150.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P98</t>
-  </si>
-  <si>
-    <t>An interdisciplinary conference on youth-identity translated longitudinal research into practical insights for programmes, policy, and evidence-based youth development.</t>
-  </si>
-  <si>
-    <r>
-      <t>跨學科青年身份認同會議把縱向研究轉化為課程、政策及循證青年發展的實務</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+      <t>VR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>展，并提供学术与策展顾问。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image172.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image173.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P110</t>
+  </si>
+  <si>
+    <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
+  </si>
+  <si>
+    <t>香港树仁大学委任长期服务的常务副校监胡怀中出任校长。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025-2026/image169.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P113</t>
+  </si>
+  <si>
+    <t>2024/2025年，仁大獲批自資專上教育提升及啟動補助金兩千五百一十萬元，發展測量及爭議解決學應用學位課程。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2024/2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>洞察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>。 </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>跨学科青年身份认同会议把纵向研究转化为课程、政策及循证青年发展的实务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>洞察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2023/image151.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P99</t>
-  </si>
-  <si>
-    <t>In 2023/24, Shue Yan received HK$14. 6 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Forensic and Investigative Psychology.</t>
-  </si>
-  <si>
-    <t>2023/24年，仁大獲批自資專上教育提升及啟動補助一千四百六十萬元，發展法證及偵緝心理學榮譽社會科學學士課程。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
+      <t>年，仁大获批自资专上教育提升及启动补助金两千五百一十万元，发展测量及争议解决学应用学位课程。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P114</t>
+  </si>
+  <si>
+    <t>Shue Yan launched a digital humanities project using a virtual-reality and a mixed-reality platform to digitally document, transmit, and promote Cheung Chau’s Jiao Festival, which is a national intangible cultural heritage.</t>
+  </si>
+  <si>
+    <t>仁大开展一项数码人文项目，运用虚拟现实和混合实境平台数字化记录、传承并推广长洲太平清醮这项国家级非物质文化遗产。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image174.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image175.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P115</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A one-stop internship platform </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>2023/24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，仁大获批自资专上教育提升及启动补助一千四百六十万元，发展法证及侦缉心理学荣誉社会科学学士课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image152.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image153.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P100</t>
-  </si>
-  <si>
-    <t>An AI- and VR-enabled martial arts exhibition documented Ving Tsun and Tai Chi, preserving cultural heritage and encouraging youth participation.</t>
-  </si>
-  <si>
-    <t>結合人工智能及虛擬實境的武術展覽記錄詠春與太極，保存文化並鼓勵青年參與。 </t>
-  </si>
-  <si>
-    <t>结合人工智能及虚拟实境的武术展览记录咏春与太极，保存文化并鼓励青年参与。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image154.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P101</t>
-  </si>
-  <si>
-    <t>The Mrs. Dorothy Koo and Dr. Ti Hua Koo Plaza, redeveloped with their donations, opened with advanced audiovisual facilities.</t>
-  </si>
-  <si>
-    <t>由顧鐵華、費肇芬捐款重建的伉儷廣場啟用，並配備先進影音設施。</t>
-  </si>
-  <si>
-    <t>由顾铁华、费肇芬捐款重建的伉俪广场启用，并配备先进影音设施。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image155.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image156.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P102</t>
-  </si>
-  <si>
-    <t>The Tin Ka Ping Teaching and Research Centre for Filial Piety opened to connect interdisciplinary research, moral education, cultural heritage, and school outreach.</t>
-  </si>
-  <si>
-    <t>田家炳孝道文化教研中心啟用，連結跨學科研究、品德教育、文化傳承及學校外展。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>田家炳孝道文化教研中心启用，连结跨学科研究、品德教育、文化传承及学校外展。</t>
+      <t>began its</t>
     </r>
     <r>
       <rPr>
@@ -4250,103 +4401,63 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image157.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image158.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P103</t>
-  </si>
-  <si>
-    <t>The University launched Hong Kong’s first one-year International Foundation Year Programme for international students, with a certificate awarded upon completion.</t>
-  </si>
-  <si>
-    <t>大學推出香港首個專為國際學生而設的一年制大學先修課程證書。</t>
-  </si>
-  <si>
-    <t>大学推出香港首个专为国际学生而设的一年制大学先修课程证书。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image159.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image160.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P104</t>
-  </si>
-  <si>
-    <t>Yang Wei from the Department of Sociology became Shue Yan’s first Doctor of Philosophy graduate, marking a milestone for the Graduate School.</t>
-  </si>
-  <si>
-    <t>社會學系楊薇成為樹仁首位哲學博士畢業生，標誌研究院重要里程碑。 </t>
-  </si>
-  <si>
-    <t>社会学系杨薇成为树仁首位哲学博士毕业生，标志研究院重要里程碑。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image161.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image162.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P105</t>
-  </si>
-  <si>
-    <t>An interdisciplinary esports project promoted youth empowerment while addressing gaming addiction through psychological, social, business, and policy research.</t>
-  </si>
-  <si>
-    <t>跨學科電競項目透過心理、社會、商業及政策研究，在應對遊戲成癮同時促進青年賦權。 </t>
-  </si>
-  <si>
-    <t>跨学科电竞项目透过心理、社会、商业及政策研究，在应对游戏成瘾同时促进青年赋权。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image163.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P106</t>
-  </si>
-  <si>
-    <t>The Emotion World project gamified evidence-based social-emotional learning and invited students to design AI-assisted characters to promote wellbeing education.</t>
-  </si>
-  <si>
-    <t>「情緒世界」把循證社交情緒學習遊戲化，並邀請學生設計人工智能輔助角色，推動福祉教育。 </t>
-  </si>
-  <si>
-    <t>「情绪世界」把循证社交情绪学习游戏化，并邀请学生设计人工智能辅助角色，推动福祉教育。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image164.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P107</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The Bridging Grey Digital Divide and diversity in older ICT users post-COVID project advanced research on older adults’ use of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+      <t xml:space="preserve"> trial operation, integrating e-portfolios, employer connections, learning resources, and AI-assisted job matching.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>一站式實習平台投入試行，整合電子履歷、僱主聯繫、學習資源及人工智能職位配對。</t>
+  </si>
+  <si>
+    <t>一站式实习平台投入试行，整合电子履历、雇主联系、学习资源及人工智能职位配对。</t>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image176.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image177.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P116</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Shue Yan rose to 360th in the QS Asia rankings and entered the QS World University Rankings  in the band of 1001–1200, becoming the first private university in Hong Kong to be listed.</t>
+  </si>
+  <si>
+    <t>仁大在QS亞洲排名升至第360位，並首登QS世界大學排名1001至1200位，成為首所上榜的香港私立大學。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>仁大在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>technology and</t>
+      <t>QS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>亚洲排名升至第</t>
     </r>
     <r>
       <rPr>
@@ -4355,85 +4466,16 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> promoted age-inclusive digital innovation. </t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>跨越灰色数码鸿沟研究长者科技使用，推动年龄共融的数码创新。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2024/image165.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P108</t>
-  </si>
-  <si>
-    <t>A longitudinal study of more than 8,000 participants examined resilience across adulthood to inform family, organisational, and public policy.</t>
-  </si>
-  <si>
-    <t>追蹤逾八千人的縱向研究，探討成年各階段的韌性，為家庭、機構及公共政策提供依據。</t>
-  </si>
-  <si>
-    <t>追踪逾八千人的纵向研究，探讨成年各阶段的韧性，为家庭、机构及公共政策提供依据。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image166.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P109</t>
-  </si>
-  <si>
-    <t>創校校監胡鴻烈於一百零五歲逝世，大學社群舉行喪禮及追思會，紀念其貢獻。 </t>
-  </si>
-  <si>
-    <t>创校校监胡鸿烈于一百零五岁逝世，大学社群举行丧礼及追思会，纪念其贡献。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image167.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image168.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P111</t>
-  </si>
-  <si>
-    <t>Shue Yan University participated in a special exhibition at the Guangdong Museum, creating an extension display on digital architectural heritage art.</t>
-  </si>
-  <si>
-    <t>仁大参与广东省博物馆特展，策划数码建筑遗产艺术延伸展区。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image170.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image171.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P112</t>
-  </si>
-  <si>
-    <t>Shue Yan University supported the Hong Kong Maritime Museum’s immersive VR archaeology exhibition “Voyage into Shu”, providing academic and curatorial advice.</t>
-  </si>
-  <si>
-    <t>仁大支持香港海事博物館「浮海探蜀」沉浸式考古VR展，並提供學術與策展顧問。 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>仁大支持香港海事博物馆「浮海探蜀」沉浸式考古</t>
+      <t>360</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>位，并首登</t>
     </r>
     <r>
       <rPr>
@@ -4442,49 +4484,17 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>VR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>展，并提供学术与策展顾问。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image172.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025/image173.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P110</t>
-  </si>
-  <si>
-    <t>香港樹仁大學委任長期服務的常務副校監胡懷中出任校長。 </t>
-  </si>
-  <si>
-    <t>香港树仁大学委任长期服务的常务副校监胡怀中出任校长。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2025-2026/image169.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P113</t>
-  </si>
-  <si>
-    <t>In 2024/25, Shue Yan University received HK$25.1 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary education to develop an applied degree in Surveying and Dispute Resolution.</t>
-  </si>
-  <si>
-    <t>2024/2025年，仁大獲批自資專上教育提升及啟動補助金兩千五百一十萬元，發展測量及爭議解決學應用學位課程。</t>
-  </si>
-  <si>
+      <t>QS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>世界大学排名</t>
+    </r>
     <r>
       <rPr>
         <sz val="9.5"/>
@@ -4492,101 +4502,58 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>2024/2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年，仁大获批自资专上教育提升及启动补助金两千五百一十万元，发展测量及争议解决学应用学位课程。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image170.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P114</t>
-  </si>
-  <si>
-    <t>Shue Yan launched a digital humanities project using a virtual-reality and a mixed-reality platform to digitally document, transmit, and promote Cheung Chau’s Jiao Festival, which is a national intangible cultural heritage.</t>
-  </si>
-  <si>
-    <t>仁大开展一项数码人文项目，运用虚拟现实和混合实境平台数字化记录、传承并推广长洲太平清醮这项国家级非物质文化遗产。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image174.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image175.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P115</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A one-stop internship platform </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
+      <t>1001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>began its</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
+      <t>1200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>位，成为首所上榜的香港私立大学。</t>
+    </r>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image178.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image179.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P117</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Shue Yan established its fourth Faculty, the Faculty of Communication, Information and Creative Industries. The faculty comprises the Department of Journalism and Communication and the Department of Data Science and Digital Innovation, formerly known as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> trial operation, integrating e-portfolios, employer connections, learning resources, and AI-assisted job matching.</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>一站式實習平台投入試行，整合電子履歷、僱主聯繫、學習資源及人工智能職位配對。</t>
-  </si>
-  <si>
-    <t>一站式实习平台投入试行，整合电子履历、雇主联系、学习资源及人工智能职位配对。</t>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image176.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026/image177.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P116</t>
-  </si>
-  <si>
-    <t>2026-2027</t>
-  </si>
-  <si>
-    <t>Shue Yan rose to 360th in the QS Asia rankings and entered the QS World University Rankings  in the band of 1001–1200, becoming the first private university in Hong Kong to be listed.</t>
-  </si>
-  <si>
-    <t>仁大在QS亞洲排名升至第360位，並首登QS世界大學排名1001至1200位，成為首所上榜的香港私立大學。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>仁大在</t>
+      <t>the Department of Applied Data Science</t>
     </r>
     <r>
       <rPr>
@@ -4595,120 +4562,6 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>QS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>亚洲排名升至第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>360</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>位，并首登</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>QS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>世界大学排名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1001</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-      </rPr>
-      <t>位，成为首所上榜的香港私立大学。</t>
-    </r>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image178.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2027/image179.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P117</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Shue Yan established its fourth Faculty, the Faculty of Communication, Information and Creative Industries. The faculty comprises the Department of Journalism and Communication and the Department of Data Science and Digital Innovation, formerly known as </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>the Department of Applied Data Science</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t>.</t>
     </r>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -4720,59 +4573,6 @@
     <t>P118</t>
   </si>
   <si>
-    <t>2026-2031</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仁大的五年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>(2026-2031)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>策略计划是融数字科技于博雅教育中，提升全球竞争力。五年策略计划（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>ADORN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.5"/>
-        <color rgb="FF262626"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）旨在提升数字能力与跨学科发展，培育具社会影响力的策略性卓越领域；加强与社区及专业界别的联系；透过数码基础设施及可持续实践更新校园设施；并透过文化教育培养具本土与全球视野的公民。</t>
-    </r>
-  </si>
-  <si>
     <t>https://umtimeline.hksyu.edu/Historical_Timeline_Images/2026-2031/image180.jpg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -4801,12 +4601,6 @@
   </si>
   <si>
     <t>Rapid population growth after WWII increased demand for Chinese-medium secondary and post-secondary education opportunities.</t>
-  </si>
-  <si>
-    <t>戰後人口增長與中文高等教育需求上升</t>
-  </si>
-  <si>
-    <t>战后人口增长与中文高等教育需求上升</t>
   </si>
   <si>
     <t>战后从内地进入到香港人口迅速增加，中文中学及专上教育需求大幅上升。</t>
@@ -4949,9 +4743,6 @@
     <t>公务员薪酬制度调整，提高大学学位持有人的待遇，影响专上学院文凭的认受性。</t>
   </si>
   <si>
-    <t>Sino-British Joint Declaration signed on 19 Sept 1984</t>
-  </si>
-  <si>
     <t>The Joint Declaration confirmed Hong Kong's return to China in 1997.</t>
   </si>
   <si>
@@ -4967,13 +4758,7 @@
     <t>《中英联合声明》确立香港于1997年回归中国。</t>
   </si>
   <si>
-    <t>港府發表《教育委員會第三號報告書》</t>
-  </si>
-  <si>
     <t>報告提出「四改三」，統一香港高等教育學制為三年制課程，入學資格則統一為兩年制預科（中六、中七）畢業。</t>
-  </si>
-  <si>
-    <t>港府发表《教育委员会第三号报告书》</t>
   </si>
   <si>
     <t>报告提出「四改三」，统一香港高等教育学制为三年制课程，入学资格则统一为两年制预科（中六、中七）毕业。</t>
@@ -5386,10 +5171,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Education Department's specialists conducted Shue Yan’s first academic assessment, followed by a further inspection by Director K. W. J. Topley.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>教育署首次派專家正式到訪樹仁位於跑馬地成和道的專上校舍。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5510,18 +5291,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>2022/23 年度，仁大獲批自資專上教育提升及啟動補助金一千九百五十萬元，發展娛樂及遊戲應用數字方案榮譽理學士課程。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>社會工作學系推出政府委託的一站式照顧者數字資訊閘道，改善支援資訊的及時獲取。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Shue Yan’s 2026-2031 Five-year Strategic Plan: Enhancing global competence through a digitally enabled liberal arts education. The Strategic Plan ADORN aims to amplify digital competence and interdisciplinarity, develop strategic areas of excellence with social impact, optimize engagement with communities and professional sectors, renew campus facilities with digital infrastructure and sustainable practices, as well as nurture glocal citizens through cultural education. </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>跨越灰色數字鴻溝研究長者科技使用，推動年齡共融的數字創新。 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5535,10 +5308,6 @@
   </si>
   <si>
     <t>仁大成立第四個學院——傳播、資訊及創意產業學院。該學院由新聞與傳播學系，以及前稱應用數據科學的數據科學及數字創新學系組成。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>仁大的五年(2026-2031)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數字基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -5677,10 +5446,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Dr. Henry Hu Hung-lick Hung-lick was appointed a member of the sixth National Committee of the Chinese People’s Political Consultative Conference in 1987. He subsequently served on the Seventh National Committee and, from 1993, as a Standing Committee member of the Eighth and Ninth National Committees.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Dr. Henry Hu Hung-lick attended the fifth session of the sixth National Committee of the Chinese People’s Political Consultative Conference in Beijing.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5772,14 +5537,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>胡鴻烈與鍾期榮在跑馬地成和道創辦香港樹仁書院，以回應本地專上教育學額不足。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shue Yan established its Board of Governors, bringing together prominent leaders to advance university affairs and campus development. The Board of Governors included Chairman Wilfred Wong Sien-bing, and other members such as Sir Run Run Shaw, Ms. Aw Sian from Sing Tao Daily, Mr. Ngan Shing-kwan, founder of China Motor Corporation, Mr. Ting Hsiung-chao, one of the founders of the Hong Kong Plastics Manufacturers Association, Dr. Maurice J. Anderson, Mr. T. K. Ann, Bishop Gilbert Baker, Barrister Brook Bernacchi, Mr. Cha Chi Ming, Mr. Chan Po Fun, Mr. Chen Chan-yen, Dr. Dr. Chung Chi-yung, Rev. Fergus Cronin, Mr. Dr. Henry Hu Hung-lick, Mr. Huo Pao-tsai, Barrister Henry Litton, Mr. Liu Han-tang, Mr. Y. B. Loo, Mr. Peter P. K. Ng, Mr. Shum Choi Sang, Mr. Shum Wai-yau, Mr. Peter H. M. Tsang, Mr. C. S. Wan, and Mr. Yuen Ngan Ming.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>The University of Hong Kong awarded Dr. Henry Hu Hung-lick an honorary Doctor of Social Sciences for his long-standing contributions to education and public service.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5789,10 +5546,6 @@
   </si>
   <si>
     <t>Education Commission Report No. 3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, to be preceded by two years of A-levels (S6-7).</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -6026,6 +5779,306 @@
   </si>
   <si>
     <t>1987年，树仁与北京大学合办法律本科学士学位课程，成为学院拓展内地学术合作的重要里程碑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shue Yan established its Board of Governors, bringing together prominent leaders to advance university affairs and campus development. The Board of Governors included Chairman Wilfred Wong Sien-bing, and other members such as Sir Run Run Shaw, Ms. Aw Sian from Sing Tao Daily, Mr. Ngan Shing-kwan, founder of China Motor Bus Company, Limited, Mr. Ting Hsiung-chao, one of the founders of the Hong Kong Plastics Manufacturers Association, Dr. Maurice J. Anderson, Mr. T. K. Ann, Bishop Gilbert Baker, Barrister Brook Bernacchi, Mr. Cha Chi Ming, Mr. Chan Po Fun, Mr. Chen Chan-yen, Dr. Chung Chi-yung, Rev. Fergus Cronin, Dr. Henry Hu Hung-lick, Mr. Huo Pao-tsai, Barrister Henry Litton, Mr. Liu Han-tang, Mr. Y. B. Loo, Mr. Peter P. K. Ng, Mr. Shum Choi Sang, Mr. Shum Wai-yau, Mr. Peter H. M. Tsang, Mr. C. S. Wan, and Mr. Yuen Ngan Ming.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>樹仁成立校董會，匯聚賢達，推動校務與校舍建設。校董會成員包括主席黃宣平議員，校董成員包括邵逸夫先生、來自《星島日報》的胡仙女士、中華汽車創辦人顏成坤議員、香港塑膠業廠商會創會人之一丁熊照先生、晏務理博士、安子介議員、白約翰主教、貝納祺御用大律師、查濟民先生、陳普芬議員、陳存仁先生、鍾期榮博士、龔樂年神父、胡鴻烈議員、霍寶材先生、烈顯倫御用大律師、劉漢棟先生、陸蔭百先生、伍秉堅議員、岑才生先生、岑維休先生、曾漢文先生、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>萬春先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>先生、阮雁鳴先生。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡鸿烈与钟期荣在跑马地成和道创办香港树仁书院，以应对本地专上教育学额不足的问题。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡鴻烈與鍾期榮在跑馬地成和道創辦香港樹仁書院，以應對本地專上教育學額不足。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Education Department's specialists conducted Shue Yan’s first academic assessment, followed by a further inspection by Director K. W. J. Topley.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>教育署专家首次评核树仁学术水平，其后教育司陶建（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>K. W. J. Topley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）再次视察。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育署專家首次評核樹仁學術水平，其後教育司陶建（K. W. J. Topley）再次視察。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 學生代表向教育司陶建（K. W. J. Topley）遞交全校聯署，捍衛樹仁四年制課程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>树仁加入东南亚高等教育协会，其学术水平获区域认可。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学生代表向教育司陶建（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>K. W. J. Topley</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）递交全校联署，捍卫树仁四年制课程。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, admission after completion of two years of A-levels (S6-7).</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dr. Henry Hu Hung-lick was appointed a member of the sixth National Committee of the Chinese People’s Political Consultative Conference in 1987. He subsequently served on the Seventh National Committee and, from 1993, as a Standing Committee member of the Eighth and Ninth National Committees.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁學院於5月10至12日進行院校評審，為升格大學作準備。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文語文學系於4月27至29日進行課程評審。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大学首次独立开办硕士学位课程——辅导心理学社会科学硕士。
+来源：《樹仁簡訊》2010年5月刊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A HK$6.75 million grant from the  Research Grants Council’s Institutional Development Scheme was received to establish Shue Yan’s first interdisciplinary research platform and strengthen its research capacity. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A HK$6.2-million grant was received from the Research Grants Council’s  Institutional Development Scheme to expand interdisciplinary infrastructure for evidence-based practice and research.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020/21年，樹仁獲自資專上教育提升及啟動補助金一千六百四十萬元，發展藝術、文化及科技榮譽社會科學學士課程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2020/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>年，树仁获自资专上教育提升及启动补助金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+      </rPr>
+      <t>一千六百四十万元，发展艺术、文化及科技荣誉社会科学学士课程。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022/23 年度，仁大獲批自資專上教育提升及啟動補助金一千九百五十萬元，發展娛樂及遊戲應用數碼方案榮譽理學士課程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2023/24, Shue Yan received HK$14.6 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop the BSocSc (Hons) in Forensic and Investigative Psychology.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The project “Mapping the grey digital divide and diversity in older ICT users post-COVID” advanced research on older adults’ use of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>technology and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> promoted age-inclusive digital innovation. </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 2024/25, Shue Yan University received HK$25.1 million from the Enhancement and Start-up Grant Scheme for Self-financing Post-secondary Education to develop an applied degree in Surveying and Dispute Resolution.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Shue Yan’s 2026-2030 Five-year Strategic Plan: Enhancing global competence through a digitally enabled liberal arts education. The Strategic Plan ADORN aims to amplify digital competence and interdisciplinarity, develop strategic areas of excellence with social impact, optimize engagement with communities and professional sectors, renew campus facilities with digital infrastructure and sustainable practices, as well as nurture glocal citizens through cultural education. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁大的五年(2026-2030)策略計劃是融數字科技於博雅教育中，提升全球競爭力。五年策略計劃 （ADORN）旨在提升數字能力與跨學科發展，培育具社會影響力的策略性卓越領域；加強與社區及專業界別的聯繫；透過數字基礎設施及可持續實踐更新校園設施；並透過文化教育培養具本土與全球視野的公民。 </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仁大的五年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2026-2030)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>策略计划是融数字科技于博雅教育中，提升全球竞争力。五年策略计划（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ADORN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.5"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）旨在提升数字能力与跨学科发展，培育具社会影响力的策略性卓越领域；加强与社区及专业界别的联系；透过数码基础设施及可持续实践更新校园设施；并透过文化教育培养具本土与全球视野的公民。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-2030</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰後，由內地遷入香港的人口迅速增加</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>战后，由内地迁入香港的人口迅速增加</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sino-British Joint Declaration signed on 19 December 1984</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>港府發表《教育統籌委員會第三號報告書》</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>港府发表《教育统筹委员会第三号报告书》</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6033,7 +6086,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6339,6 +6392,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF262626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6411,7 +6472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6568,6 +6629,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6922,10 +6989,10 @@
         <v>1949</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>1009</v>
+        <v>980</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>11</v>
@@ -6957,19 +7024,19 @@
         <v>18</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>1010</v>
+        <v>981</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>988</v>
+        <v>960</v>
       </c>
       <c r="G3" s="42" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="41" t="s">
-        <v>989</v>
+        <v>961</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>15</v>
@@ -7021,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>1011</v>
+        <v>982</v>
       </c>
       <c r="E5" s="42" t="s">
         <v>31</v>
@@ -7120,13 +7187,13 @@
         <v>55</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>985</v>
+        <v>957</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>986</v>
+        <v>958</v>
       </c>
       <c r="H8" s="38" t="s">
         <v>57</v>
@@ -7244,10 +7311,10 @@
         <v>84</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>85</v>
@@ -7276,13 +7343,13 @@
         <v>89</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="F13" s="41" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>991</v>
+        <v>963</v>
       </c>
       <c r="H13" s="41" t="s">
         <v>91</v>
@@ -7368,7 +7435,7 @@
         <v>109</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>110</v>
@@ -7377,7 +7444,7 @@
         <v>111</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>1031</v>
+        <v>999</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>35</v>
@@ -7426,22 +7493,22 @@
         <v>1990</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>1029</v>
+        <v>997</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>1030</v>
+        <v>998</v>
       </c>
       <c r="E18" s="39" t="s">
         <v>121</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
       <c r="G18" s="39" t="s">
         <v>122</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>1028</v>
+        <v>996</v>
       </c>
       <c r="I18" s="36" t="s">
         <v>35</v>
@@ -7657,7 +7724,7 @@
         <v>174</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
       <c r="G25" s="42" t="s">
         <v>175</v>
@@ -7683,19 +7750,19 @@
         <v>178</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>1022</v>
+        <v>990</v>
       </c>
       <c r="E26" s="39" t="s">
         <v>179</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>1020</v>
+        <v>988</v>
       </c>
       <c r="G26" s="39" t="s">
         <v>180</v>
       </c>
       <c r="H26" s="51" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>51</v>
@@ -7747,13 +7814,13 @@
         <v>190</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>1016</v>
+        <v>985</v>
       </c>
       <c r="E28" s="39" t="s">
         <v>191</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
       <c r="G28" s="39" t="s">
         <v>192</v>
@@ -7776,16 +7843,16 @@
         <v>2007</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>983</v>
+        <v>955</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>984</v>
+        <v>956</v>
       </c>
       <c r="E29" s="42" t="s">
         <v>195</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
       <c r="G29" s="42" t="s">
         <v>196</v>
@@ -7876,28 +7943,28 @@
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>995</v>
+        <v>967</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="F2" s="28" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="14" t="s">
+        <v>934</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>958</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>208</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
@@ -7907,28 +7974,28 @@
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>949</v>
+        <v>925</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>950</v>
+        <v>926</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -7939,25 +8006,25 @@
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
@@ -7966,28 +8033,28 @@
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>996</v>
+        <v>968</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -7998,28 +8065,28 @@
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>951</v>
+        <v>927</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -8030,28 +8097,28 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>231</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>233</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -8062,28 +8129,28 @@
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>237</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>239</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -8094,28 +8161,28 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>241</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
@@ -8126,28 +8193,28 @@
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>960</v>
+        <v>1004</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>245</v>
+        <v>1006</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="11" t="s">
-        <v>246</v>
+      <c r="H10" s="30" t="s">
+        <v>1005</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
@@ -8158,25 +8225,25 @@
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
@@ -8185,25 +8252,25 @@
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -8215,28 +8282,28 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -8247,28 +8314,28 @@
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -8279,28 +8346,28 @@
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
-        <v>274</v>
+      <c r="H15" s="29" t="s">
+        <v>1008</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8311,28 +8378,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8343,28 +8410,28 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>284</v>
+        <v>1007</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="15" t="s">
-        <v>285</v>
+      <c r="H17" s="54" t="s">
+        <v>1009</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -8375,28 +8442,28 @@
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8407,28 +8474,28 @@
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>962</v>
+        <v>937</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8439,28 +8506,28 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
@@ -8471,28 +8538,28 @@
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -8503,25 +8570,25 @@
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8533,25 +8600,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8563,28 +8630,28 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
@@ -8595,28 +8662,28 @@
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8627,25 +8694,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8656,25 +8723,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>997</v>
+        <v>1011</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8686,28 +8753,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>998</v>
+        <v>969</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8718,25 +8785,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8748,28 +8815,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8780,25 +8847,25 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
@@ -8810,28 +8877,28 @@
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -8842,25 +8909,25 @@
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>1026</v>
+        <v>994</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8872,25 +8939,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8902,28 +8969,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -8934,28 +9001,28 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
@@ -8966,25 +9033,25 @@
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -8996,28 +9063,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -9028,28 +9095,28 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>999</v>
+        <v>970</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
@@ -9060,25 +9127,25 @@
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -9090,25 +9157,25 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -9120,28 +9187,28 @@
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>956</v>
+        <v>932</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -9152,28 +9219,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -9184,25 +9251,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -9214,22 +9281,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -9242,28 +9309,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>1000</v>
+        <v>971</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -9274,28 +9341,28 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9306,25 +9373,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9336,25 +9403,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9366,25 +9433,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9396,28 +9463,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9428,25 +9495,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9458,25 +9525,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9488,25 +9555,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9518,57 +9585,57 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9580,25 +9647,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9610,25 +9677,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9640,87 +9707,87 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9732,25 +9799,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9762,25 +9829,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>529</v>
+        <v>1013</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9792,25 +9859,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>534</v>
+        <v>1012</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9822,25 +9889,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9852,25 +9919,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9882,25 +9949,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>965</v>
+        <v>940</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -9912,28 +9979,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>964</v>
+        <v>939</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -9944,28 +10011,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -9976,28 +10043,28 @@
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>1001</v>
+        <v>972</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -10008,25 +10075,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>1002</v>
+        <v>973</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -10038,28 +10105,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>1003</v>
+        <v>974</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -10070,25 +10137,25 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>966</v>
+        <v>941</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>967</v>
+        <v>942</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>577</v>
+        <v>1014</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -10100,25 +10167,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>1004</v>
+        <v>975</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -10130,28 +10197,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -10162,28 +10229,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -10194,22 +10261,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -10222,28 +10289,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -10254,25 +10321,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>605</v>
+        <v>1015</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10284,28 +10351,28 @@
     </row>
     <row r="80" spans="1:14" ht="41.4">
       <c r="A80" s="2" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>1015</v>
+        <v>984</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10316,25 +10383,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10346,25 +10413,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10376,22 +10443,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>625</v>
+        <v>1016</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10403,88 +10470,88 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>1005</v>
+        <v>976</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10495,60 +10562,60 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>969</v>
+        <v>944</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>970</v>
+        <v>945</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10559,28 +10626,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10591,22 +10658,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10619,28 +10686,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10651,677 +10718,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>993</v>
+        <v>965</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>973</v>
+        <v>948</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>684</v>
+        <v>1017</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>685</v>
+        <v>1018</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>974</v>
+        <v>949</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>975</v>
+        <v>1019</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>713</v>
+        <v>1020</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>723</v>
+        <v>708</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>725</v>
+        <v>710</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>733</v>
+        <v>718</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>742</v>
+        <v>727</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>743</v>
+        <v>728</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>748</v>
+        <v>733</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>752</v>
+        <v>737</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>758</v>
+        <v>1021</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>978</v>
+        <v>951</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>1006</v>
+        <v>977</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>994</v>
+        <v>966</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>979</v>
+        <v>952</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="B113" s="5">
         <v>2026</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>1007</v>
+        <v>978</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11333,148 +11400,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>787</v>
+        <v>1022</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>788</v>
+        <v>771</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>980</v>
+        <v>953</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>797</v>
+        <v>780</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>799</v>
+        <v>782</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>808</v>
+        <v>791</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>803</v>
+        <v>786</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>981</v>
+        <v>954</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11482,45 +11549,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>813</v>
+        <v>1026</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>977</v>
+        <v>1023</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>982</v>
+        <v>1024</v>
       </c>
       <c r="G119" s="15"/>
-      <c r="H119" s="15" t="s">
-        <v>814</v>
+      <c r="H119" s="54" t="s">
+        <v>1025</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11719,103 +11786,103 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>823</v>
+        <v>803</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>1027</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>987</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>824</v>
+        <v>959</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>1028</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>845</v>
+        <v>824</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11826,22 +11893,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>848</v>
+        <v>827</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>849</v>
+        <v>828</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11852,22 +11919,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>854</v>
+        <v>833</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>856</v>
+        <v>835</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>857</v>
+        <v>836</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>858</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11878,22 +11945,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>861</v>
+        <v>840</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>863</v>
+        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -11904,22 +11971,22 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>864</v>
+        <v>1029</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>865</v>
+        <v>843</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>867</v>
+        <v>845</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>868</v>
+        <v>846</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>869</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
@@ -11930,48 +11997,48 @@
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1017</v>
+        <v>986</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>870</v>
+        <v>1010</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>1030</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>872</v>
+        <v>848</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>1031</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>874</v>
+        <v>850</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>877</v>
+        <v>853</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>880</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
@@ -11982,74 +12049,74 @@
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>881</v>
+        <v>857</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>882</v>
+        <v>858</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>883</v>
+        <v>859</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>884</v>
+        <v>860</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>886</v>
+        <v>862</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>888</v>
+        <v>864</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>889</v>
+        <v>865</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>890</v>
+        <v>866</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>891</v>
+        <v>867</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>892</v>
+        <v>868</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>893</v>
+        <v>869</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>894</v>
+        <v>870</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>895</v>
+        <v>871</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>897</v>
+        <v>873</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>898</v>
+        <v>874</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>900</v>
+        <v>876</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
@@ -12060,48 +12127,48 @@
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>903</v>
+        <v>879</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>908</v>
+        <v>884</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>909</v>
+        <v>885</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>910</v>
+        <v>886</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>911</v>
+        <v>887</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
@@ -12109,129 +12176,129 @@
         <v>198</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>914</v>
+        <v>890</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>915</v>
+        <v>891</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>916</v>
+        <v>892</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>917</v>
+        <v>893</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>918</v>
+        <v>894</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>919</v>
+        <v>895</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>920</v>
+        <v>896</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>921</v>
+        <v>897</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>924</v>
+        <v>900</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>925</v>
+        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>928</v>
+        <v>904</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>930</v>
+        <v>906</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>931</v>
+        <v>907</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>933</v>
+        <v>909</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>934</v>
+        <v>910</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>935</v>
+        <v>911</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>938</v>
+        <v>914</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>939</v>
+        <v>915</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>945</v>
+        <v>921</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>946</v>
+        <v>922</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>947</v>
+        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12324,23 +12391,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12522,25 +12572,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12556,4 +12605,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771FB438-8949-411B-B50B-CC2BC7EC7FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56FA2C5-C148-4444-ACC0-580FA4C3AB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="樹仁校史" sheetId="1" r:id="rId1"/>
@@ -295,9 +295,6 @@
     <t>注册为专上学院：取得制度认可</t>
   </si>
   <si>
-    <t>1976年，树仁依《专上学院条例》注册为专上学院，正式取得颁授专上文凭的制度资格。</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -311,12 +308,6 @@
   </si>
   <si>
     <t>Shue Yan relocated to Monmouth Path in Wan Chai and, after years of application, was granted a permanent campus site at Braemar Hill, laying the foundation for long-term campus development.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樹仁遷往灣仔萬茂徑，並在經過多年申請後獲批寶馬山永久校址，為長遠校園建設奠定基礎。 </t>
-  </si>
-  <si>
-    <t>树仁迁往湾仔万茂径，并在经过多年申请后获批宝马山永久校址，为长远校园建设奠定基础。</t>
   </si>
   <si>
     <t>A</t>
@@ -5482,15 +5473,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu fai-chung as President.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>After the war, Dr. Henry Hu Hung-lick and Dr. Chung Chi-yung went to France to further their studies in law. Their exposure to different legal systems, social institutions, and educational philosophies in Europe laid the foundation for their later efforts to address youth and social issues through institutional reform.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hu Hung-lick and Chung Chi-yung Studied in Europe: From Law to Educational Commitment</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -5898,10 +5881,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, admission after completion of two years of A-levels (S6-7).</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Dr. Henry Hu Hung-lick was appointed a member of the sixth National Committee of the Chinese People’s Political Consultative Conference in 1987. He subsequently served on the Seventh National Committee and, from 1993, as a Standing Committee member of the Eighth and Ninth National Committees.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -6079,6 +6058,60 @@
   </si>
   <si>
     <t>港府发表《教育统筹委员会第三号报告书》</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Henry Hu Hung-lick and Chung Chi-yung Studied in Europe: From Law to Educational Commitment</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hong Kong Shue Yan University appointed long-serving Deputy President Hu Fai-chung as President.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>樹仁遷往灣仔萬茂里，並在經過多年申請後獲批寶馬山永久校址，為長遠校園建設奠定基礎。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1976</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，树仁依《专上学院条例》注册为专上学院，正式取得颁授专上文凭的制度资格。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>树仁迁往湾仔万茂里，并在经过多年申请后获批宝马山永久校址，为长远校园建设奠定基础。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, after completion of two years of A-levels (S6-7).</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6989,10 +7022,10 @@
         <v>1949</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>980</v>
+        <v>1026</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>11</v>
@@ -7024,19 +7057,19 @@
         <v>18</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="G3" s="42" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="41" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>15</v>
@@ -7088,7 +7121,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="E5" s="42" t="s">
         <v>31</v>
@@ -7164,707 +7197,707 @@
         <v>49</v>
       </c>
       <c r="H7" s="41" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="J7" s="40" t="s">
         <v>51</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57">
       <c r="A8" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="36">
         <v>1977</v>
       </c>
       <c r="C8" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="E8" s="47" t="s">
+        <v>954</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>955</v>
+      </c>
+      <c r="H8" s="51" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I8" s="36" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>957</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>958</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>58</v>
       </c>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:10" ht="68.400000000000006">
       <c r="A9" s="36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B9" s="40">
         <v>1978</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="G9" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="H9" s="41" t="s">
         <v>62</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>65</v>
       </c>
       <c r="I9" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="40" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="68.400000000000006">
       <c r="A10" s="40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B10" s="36">
         <v>1979</v>
       </c>
       <c r="C10" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="G10" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="H10" s="38" t="s">
         <v>70</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>73</v>
       </c>
       <c r="I10" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57">
       <c r="A11" s="36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B11" s="40">
         <v>1980</v>
       </c>
       <c r="C11" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="G11" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="F11" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>81</v>
-      </c>
       <c r="I11" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="79.8">
       <c r="A12" s="36" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B12" s="36">
         <v>1982</v>
       </c>
       <c r="C12" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>925</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>978</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>928</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>983</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>86</v>
-      </c>
       <c r="I12" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.8">
       <c r="A13" s="40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B13" s="40">
         <v>1983</v>
       </c>
       <c r="C13" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>959</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>960</v>
+      </c>
+      <c r="H13" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>962</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>963</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>91</v>
-      </c>
       <c r="I13" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="68.400000000000006">
       <c r="A14" s="36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B14" s="36">
         <v>1985</v>
       </c>
       <c r="C14" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="G14" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="H14" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="I14" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="36" t="s">
         <v>96</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57">
       <c r="A15" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B15" s="40">
         <v>1986</v>
       </c>
       <c r="C15" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="G15" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>106</v>
-      </c>
       <c r="I15" s="40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B16" s="36">
         <v>1987</v>
       </c>
       <c r="C16" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>926</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>929</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>111</v>
-      </c>
       <c r="H16" s="51" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.8">
       <c r="A17" s="36" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B17" s="40">
         <v>1988</v>
       </c>
       <c r="C17" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="G17" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="H17" s="41" t="s">
         <v>115</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="41" t="s">
-        <v>118</v>
       </c>
       <c r="I17" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="114">
       <c r="A18" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B18" s="36">
         <v>1990</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="I18" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B19" s="40">
         <v>1995</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="G19" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="H19" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="I19" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="40" t="s">
         <v>128</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="40" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="91.2">
       <c r="A20" s="40" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B20" s="36">
         <v>1996</v>
       </c>
       <c r="C20" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="G20" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="H20" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>138</v>
-      </c>
       <c r="I20" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68.400000000000006">
       <c r="A21" s="36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B21" s="40">
         <v>1999</v>
       </c>
       <c r="C21" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="G21" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="H21" s="41" t="s">
         <v>142</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="41" t="s">
-        <v>145</v>
       </c>
       <c r="I21" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J21" s="40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="79.8">
       <c r="A22" s="36" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B22" s="36">
         <v>2000</v>
       </c>
       <c r="C22" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="G22" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="H22" s="38" t="s">
         <v>150</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>153</v>
       </c>
       <c r="I22" s="36"/>
       <c r="J22" s="36" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="68.400000000000006">
       <c r="A23" s="40" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B23" s="40">
         <v>2001</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="G23" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="H23" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="I23" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="40" t="s">
         <v>159</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="68.400000000000006">
       <c r="A24" s="36" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B24" s="36">
         <v>2002</v>
       </c>
       <c r="C24" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="G24" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="H24" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="I24" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="36" t="s">
         <v>167</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="68.400000000000006">
       <c r="A25" s="40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B25" s="40">
         <v>2003</v>
       </c>
       <c r="C25" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>982</v>
+      </c>
+      <c r="G25" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="H25" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="E25" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>987</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>176</v>
-      </c>
       <c r="I25" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="57">
       <c r="A26" s="36" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B26" s="36">
         <v>2004</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H26" s="51" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="68.400000000000006">
       <c r="A27" s="36" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B27" s="40">
         <v>2005</v>
       </c>
       <c r="C27" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="F27" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="G27" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="H27" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="I27" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="40" t="s">
         <v>185</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="J27" s="40" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="57">
       <c r="A28" s="40" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B28" s="36">
         <v>2006</v>
       </c>
       <c r="C28" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>980</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>928</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="38" t="s">
         <v>190</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>985</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>931</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>193</v>
       </c>
       <c r="I28" s="36" t="s">
         <v>35</v>
       </c>
       <c r="J28" s="36" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="68.400000000000006">
       <c r="A29" s="36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B29" s="40">
         <v>2007</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I29" s="40" t="s">
         <v>35</v>
       </c>
       <c r="J29" s="40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -7917,19 +7950,19 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -7937,65 +7970,65 @@
     </row>
     <row r="2" spans="1:14" ht="151.80000000000001">
       <c r="A2" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B2" s="2">
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="82.8">
       <c r="A3" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -8006,55 +8039,55 @@
     </row>
     <row r="4" spans="1:14" ht="37.799999999999997">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4" s="2">
         <v>1972</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J4" s="14"/>
       <c r="N4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.8">
       <c r="A5" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B5" s="5">
         <v>1972</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -8065,28 +8098,28 @@
     </row>
     <row r="6" spans="1:14" ht="37.799999999999997">
       <c r="A6" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B6" s="2">
         <v>1972</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
@@ -8097,60 +8130,60 @@
     </row>
     <row r="7" spans="1:14" ht="28.8">
       <c r="A7" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B7" s="5">
         <v>1972</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8">
       <c r="A8" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B8" s="2">
         <v>1974</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -8161,116 +8194,116 @@
     </row>
     <row r="9" spans="1:14" ht="28.8">
       <c r="A9" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B9" s="5">
         <v>1974</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8">
       <c r="A10" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B10" s="2">
         <v>1975</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="30" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="41.4">
       <c r="A11" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B11" s="5">
         <v>1976</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="16" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J11" s="14"/>
       <c r="N11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8">
       <c r="A12" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B12" s="2">
         <v>1976</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="2"/>
@@ -8282,92 +8315,92 @@
     </row>
     <row r="13" spans="1:14" ht="28.8">
       <c r="A13" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B13" s="5">
         <v>1977</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="55.2">
       <c r="A14" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B14" s="2">
         <v>1978</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8">
       <c r="A15" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B15" s="5">
         <v>1979</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="16" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="29" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -8378,28 +8411,28 @@
     </row>
     <row r="16" spans="1:14" ht="28.8">
       <c r="A16" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B16" s="2">
         <v>1979</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="22" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -8410,60 +8443,60 @@
     </row>
     <row r="17" spans="1:14" ht="28.8">
       <c r="A17" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B17" s="5">
         <v>1979</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="54" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8">
       <c r="A18" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B18" s="2">
         <v>1980</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
@@ -8474,28 +8507,28 @@
     </row>
     <row r="19" spans="1:14" ht="41.4">
       <c r="A19" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B19" s="5">
         <v>1981</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -8506,89 +8539,89 @@
     </row>
     <row r="20" spans="1:14" ht="55.2">
       <c r="A20" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B20" s="2">
         <v>1983</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4">
       <c r="A21" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B21" s="5">
         <v>1984</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B22" s="2">
         <v>1984</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J22" s="14"/>
       <c r="K22" s="2"/>
@@ -8600,25 +8633,25 @@
     </row>
     <row r="23" spans="1:14" ht="41.4">
       <c r="A23" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B23" s="5">
         <v>1985</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="16" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J23" s="14"/>
       <c r="K23" s="17"/>
@@ -8630,60 +8663,60 @@
     </row>
     <row r="24" spans="1:14" ht="28.8">
       <c r="A24" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B24" s="2">
         <v>1986</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4">
       <c r="A25" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B25" s="5">
         <v>1986</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="16" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
@@ -8694,25 +8727,25 @@
     </row>
     <row r="26" spans="1:14" ht="28.8">
       <c r="A26" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B26" s="2">
         <v>1987</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -8723,25 +8756,25 @@
     </row>
     <row r="27" spans="1:14" ht="55.2">
       <c r="A27" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B27" s="5">
         <v>1987</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="17"/>
@@ -8753,28 +8786,28 @@
     </row>
     <row r="28" spans="1:14" ht="28.8">
       <c r="A28" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B28" s="2">
         <v>1987</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
@@ -8785,25 +8818,25 @@
     </row>
     <row r="29" spans="1:14" ht="41.4">
       <c r="A29" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="16" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17"/>
@@ -8815,28 +8848,28 @@
     </row>
     <row r="30" spans="1:14" ht="28.8">
       <c r="A30" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B30" s="2">
         <v>1988</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="12" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K30" s="19"/>
       <c r="L30" s="19"/>
@@ -8847,87 +8880,87 @@
     </row>
     <row r="31" spans="1:14" ht="28.8">
       <c r="A31" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B31" s="5">
         <v>1988</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="16" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8">
       <c r="A32" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B32" s="2">
         <v>1990</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="12" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="27" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8">
       <c r="A33" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B33" s="5">
         <v>1991</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="17"/>
@@ -8939,25 +8972,25 @@
     </row>
     <row r="34" spans="1:14" ht="28.8">
       <c r="A34" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B34" s="2">
         <v>1991</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="12" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="2"/>
@@ -8969,28 +9002,28 @@
     </row>
     <row r="35" spans="1:14" ht="28.8">
       <c r="A35" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B35" s="5">
         <v>1992</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
@@ -9001,57 +9034,57 @@
     </row>
     <row r="36" spans="1:14" ht="28.8">
       <c r="A36" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B36" s="2">
         <v>1992</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="12" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="K36" s="19"/>
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8">
       <c r="A37" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B37" s="5">
         <v>1993</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="16" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="23" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="17"/>
@@ -9063,28 +9096,28 @@
     </row>
     <row r="38" spans="1:14" ht="41.4">
       <c r="A38" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B38" s="2">
         <v>1994</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="11" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="19"/>
@@ -9095,57 +9128,57 @@
     </row>
     <row r="39" spans="1:14" ht="41.4">
       <c r="A39" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B39" s="5">
         <v>1995</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="23" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8">
       <c r="A40" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B40" s="2">
         <v>1995</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="12" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -9157,58 +9190,58 @@
     </row>
     <row r="41" spans="1:14" ht="28.8">
       <c r="A41" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B41" s="5">
         <v>1995</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8">
       <c r="A42" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B42" s="2">
         <v>1996</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K42" s="19"/>
       <c r="L42" s="19"/>
@@ -9219,28 +9252,28 @@
     </row>
     <row r="43" spans="1:14" ht="41.4">
       <c r="A43" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B43" s="5">
         <v>1997</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="16" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -9251,25 +9284,25 @@
     </row>
     <row r="44" spans="1:14" ht="28.8">
       <c r="A44" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B44" s="2">
         <v>1997</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="12" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -9281,22 +9314,22 @@
     </row>
     <row r="45" spans="1:14" ht="27.6">
       <c r="A45" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B45" s="5">
         <v>1997</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
@@ -9309,28 +9342,28 @@
     </row>
     <row r="46" spans="1:14" ht="28.8">
       <c r="A46" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B46" s="2">
         <v>1998</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
@@ -9341,87 +9374,87 @@
     </row>
     <row r="47" spans="1:14" ht="41.4">
       <c r="A47" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B47" s="5">
         <v>1999</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9433,638 +9466,638 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -10075,25 +10108,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -10105,28 +10138,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -10137,25 +10170,25 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -10167,25 +10200,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -10197,28 +10230,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -10229,28 +10262,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -10261,22 +10294,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -10289,28 +10322,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -10321,25 +10354,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10351,28 +10384,28 @@
     </row>
     <row r="80" spans="1:14" ht="41.4">
       <c r="A80" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10383,25 +10416,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10413,25 +10446,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10443,22 +10476,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10470,152 +10503,152 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
       <c r="N86" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10626,28 +10659,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10658,22 +10691,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10686,28 +10719,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10718,677 +10751,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B113" s="5">
         <v>2026</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>978</v>
+        <v>1027</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11400,148 +11433,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11549,45 +11582,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="54" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="I119" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="J119" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>795</v>
+      </c>
+      <c r="L119" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="J119" s="17" t="s">
+      <c r="M119" s="17" t="s">
         <v>797</v>
       </c>
-      <c r="K119" s="17" t="s">
-        <v>798</v>
-      </c>
-      <c r="L119" s="17" t="s">
-        <v>799</v>
-      </c>
-      <c r="M119" s="17" t="s">
-        <v>800</v>
-      </c>
       <c r="N119" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11786,519 +11819,519 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>956</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>801</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>959</v>
-      </c>
-      <c r="G2" s="55" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>808</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>821</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>822</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>824</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2">
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>828</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B7" s="5">
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>832</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>833</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>834</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>836</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2">
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>986</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>991</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B9" s="5">
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>844</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>846</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B10" s="2">
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>851</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>853</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2">
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>859</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>860</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>864</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>866</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>867</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>873</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>874</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B15" s="5">
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>877</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>878</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>879</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>880</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="F16" s="49" t="s">
+        <v>961</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>886</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>964</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="F17" s="50" t="s">
+        <v>987</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>891</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>892</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>992</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>894</v>
-      </c>
       <c r="H17" s="52" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>898</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>903</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>905</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>907</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="H20" s="4" t="s">
         <v>913</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>920</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>922</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12391,6 +12424,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12572,24 +12622,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12605,22 +12656,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/HKSYU Timeline.xlsx
+++ b/HKSYU Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCodingProject\HKSYU Museum Timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56FA2C5-C148-4444-ACC0-580FA4C3AB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E476E21A-9C2C-48A7-9A2A-583D039D43EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1856,9 +1856,6 @@
     <t>Shue Yan launched a coordinated campaign for private-university status, including a signature collection, staff forums, programme validation, and advocacy in the Legislative Council.</t>
   </si>
   <si>
-    <t>樹仁發起爭取私立大學地位的協同行動，包括聯署、教職員論壇、課程評審及立法會倡議。</t>
-  </si>
-  <si>
     <t>树仁发起争取私立大学地位的协同行动，包括联署、教职员论坛、课程评审及立法会倡议。</t>
   </si>
   <si>
@@ -1869,12 +1866,6 @@
   </si>
   <si>
     <t>P47</t>
-  </si>
-  <si>
-    <t>In 1999, Andrea Hope joined Shue Yan to lead the programme validation and support the College’s progress towards university status.</t>
-  </si>
-  <si>
-    <t>1999年，何珮顏加入樹仁，負責課程評審，推動學院升格為大學。</t>
   </si>
   <si>
     <r>
@@ -4854,16 +4845,7 @@
     <t xml:space="preserve">The reform proposal introduced the "3-3-4" academic structure, restoring four-year undergraduate education while promoting lifelong learning and whole-person development for a knowledge-based society. Hong Kong Shue Yan remained the only local higher education institution to retain a four-year undergraduate curriculum. </t>
   </si>
   <si>
-    <t>《教育制度檢討改革方案》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《教育制度檢討改革方案》提出香港教育改革的新方向，由沿用多年的三年大學學制，逐步改革為「三三四」學制（3年初中、3年高中、4年大學），並倡導由精英教育邁向終身學習及全人教育，以配合知識型社會的發展。樹仁則成為香港唯一一直堅持四年制本科教育的高等院校。 </t>
-  </si>
-  <si>
     <t>《教育制度检讨改革方案》</t>
-  </si>
-  <si>
-    <t>《教育制度检讨改革方案》提出香港教育改革的新方向，由沿用多年的三年大学学制，逐步改革为「三三四」学制（3年初中、3年高中、4年大学），并倡导由精英教育迈向终身学习及全人教育，以配合知识型社会的发展。树仁则成为香港唯一一直坚持四年制本科教育的高等院校。</t>
   </si>
   <si>
     <t>B15</t>
@@ -5336,10 +5318,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>從戰後内地進入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1955</t>
     </r>
@@ -6112,6 +6090,175 @@
   </si>
   <si>
     <t>Report No. 3 in 1988 standardised Hong Kong's undergraduate degrees to three years, after completion of two years of A-levels (S6-7).</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰後從内地進入到香港人口迅速增加，中文中學及專上教育需求大幅上升。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《教育制度检讨改革方案》提出香港教育改革的新方向，由沿用多年的三年大学学制，逐步改革为「三三四」学制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年初中、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年高中、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年大学），并倡导由精英教育迈向终身学习及全人教育，以配合知识型社会的发展。树仁则成为香港唯一一直坚持四年制本科教育的高等院校。</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>In 1999, Andrea Hope joined Shue Yan to lead the programme validation and support the College’s progress towards university status.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>樹仁發起爭取私立大學地位的協同行動，包括聯署、教職員論壇、課程評審及立法會倡議。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1999年，何珮顏加入樹仁，負責課程評審，推動學院升格為大學。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>《教育制度檢討改革方案》</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《教育制度檢討改革方案》提出香港教育改革的新方向，由沿用多年的三年大學學制，逐步改革為「三三四」學制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年初中、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年高中、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年大學），並倡導由精英教育邁向終身學習及全人教育，以配合知識型社會的發展。樹仁則成為香港唯一一直堅持四年制本科教育的高等院校。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF262626"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6505,7 +6652,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6668,6 +6815,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7022,10 +7172,10 @@
         <v>1949</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>11</v>
@@ -7057,19 +7207,19 @@
         <v>18</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="G3" s="42" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="41" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="I3" s="40" t="s">
         <v>15</v>
@@ -7121,7 +7271,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="E5" s="42" t="s">
         <v>31</v>
@@ -7197,7 +7347,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="I7" s="40" t="s">
         <v>50</v>
@@ -7220,16 +7370,16 @@
         <v>54</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="G8" s="45" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="I8" s="36" t="s">
         <v>55</v>
@@ -7344,10 +7494,10 @@
         <v>81</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>82</v>
@@ -7376,13 +7526,13 @@
         <v>86</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="F13" s="41" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="H13" s="41" t="s">
         <v>88</v>
@@ -7468,7 +7618,7 @@
         <v>106</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>107</v>
@@ -7477,7 +7627,7 @@
         <v>108</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>35</v>
@@ -7526,22 +7676,22 @@
         <v>1990</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="E18" s="39" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="G18" s="39" t="s">
         <v>119</v>
       </c>
       <c r="H18" s="53" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="I18" s="36" t="s">
         <v>35</v>
@@ -7757,7 +7907,7 @@
         <v>171</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="G25" s="42" t="s">
         <v>172</v>
@@ -7783,19 +7933,19 @@
         <v>175</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E26" s="39" t="s">
         <v>176</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="G26" s="39" t="s">
         <v>177</v>
       </c>
       <c r="H26" s="51" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="I26" s="36" t="s">
         <v>50</v>
@@ -7847,13 +7997,13 @@
         <v>187</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E28" s="39" t="s">
         <v>188</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="G28" s="39" t="s">
         <v>189</v>
@@ -7876,16 +8026,16 @@
         <v>2007</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="E29" s="42" t="s">
         <v>192</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G29" s="42" t="s">
         <v>193</v>
@@ -7976,25 +8126,25 @@
         <v>1971</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="H2" s="13" t="s">
         <v>202</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>203</v>
@@ -8018,11 +8168,11 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="29" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>207</v>
@@ -8073,7 +8223,7 @@
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
@@ -8081,7 +8231,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="20" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>216</v>
@@ -8113,7 +8263,7 @@
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="30" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="I6" s="14" t="s">
         <v>221</v>
@@ -8201,11 +8351,11 @@
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="16" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
@@ -8233,15 +8383,15 @@
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="30" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>240</v>
@@ -8394,7 +8544,7 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="29" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>267</v>
@@ -8426,7 +8576,7 @@
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>272</v>
@@ -8454,11 +8604,11 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="54" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>276</v>
@@ -8514,7 +8664,7 @@
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="11" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="16" t="s">
@@ -8734,7 +8884,7 @@
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="12" t="s">
@@ -8763,7 +8913,7 @@
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
@@ -8793,7 +8943,7 @@
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="12" t="s">
@@ -8953,7 +9103,7 @@
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="16" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15" t="s">
@@ -9135,7 +9285,7 @@
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="11" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="16" t="s">
@@ -9238,7 +9388,7 @@
         <v>409</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="J42" s="19" t="s">
         <v>410</v>
@@ -9349,7 +9499,7 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="E46" s="11"/>
       <c r="F46" s="12" t="s">
@@ -9385,17 +9535,17 @@
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="16" t="s">
-        <v>433</v>
+        <v>1028</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="I47" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="I47" s="17" t="s">
+      <c r="J47" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
@@ -9406,25 +9556,25 @@
     </row>
     <row r="48" spans="1:14" ht="28.8">
       <c r="A48" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B48" s="2">
         <v>1999</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11" t="s">
-        <v>438</v>
+        <v>1027</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="12" t="s">
-        <v>439</v>
+        <v>1029</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="11" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -9436,25 +9586,25 @@
     </row>
     <row r="49" spans="1:14" ht="28.8">
       <c r="A49" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B49" s="5">
         <v>2000</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="16" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="16" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
@@ -9466,25 +9616,25 @@
     </row>
     <row r="50" spans="1:14" ht="28.8">
       <c r="A50" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B50" s="2">
         <v>2000</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="12" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="12" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -9496,28 +9646,28 @@
     </row>
     <row r="51" spans="1:14" ht="28.8">
       <c r="A51" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B51" s="5">
         <v>2000</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="15" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="16" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
@@ -9528,25 +9678,25 @@
     </row>
     <row r="52" spans="1:14" ht="28.8">
       <c r="A52" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B52" s="2">
         <v>2001</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="12" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="11" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -9558,25 +9708,25 @@
     </row>
     <row r="53" spans="1:14" ht="28.8">
       <c r="A53" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B53" s="5">
         <v>2001</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="15" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="16" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
@@ -9588,25 +9738,25 @@
     </row>
     <row r="54" spans="1:14" ht="28.8">
       <c r="A54" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B54" s="2">
         <v>2001</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="12" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G54" s="11"/>
       <c r="H54" s="11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -9618,57 +9768,57 @@
     </row>
     <row r="55" spans="1:14" ht="28.8">
       <c r="A55" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B55" s="2">
         <v>2001</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="12" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="12" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J55" s="19" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="35" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.8">
       <c r="A56" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B56" s="5">
         <v>2003</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="16" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
@@ -9680,25 +9830,25 @@
     </row>
     <row r="57" spans="1:14" ht="28.8">
       <c r="A57" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B57" s="2">
         <v>2003</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
@@ -9710,25 +9860,25 @@
     </row>
     <row r="58" spans="1:14" ht="28.8">
       <c r="A58" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B58" s="5">
         <v>2004</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
@@ -9740,87 +9890,87 @@
     </row>
     <row r="59" spans="1:14" ht="28.8">
       <c r="A59" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B59" s="5">
         <v>2004</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="15" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" s="35" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="28.8">
       <c r="A60" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B60" s="5">
         <v>2004</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="24" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="35" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.8">
       <c r="A61" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B61" s="2">
         <v>2005</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="11" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
@@ -9832,25 +9982,25 @@
     </row>
     <row r="62" spans="1:14" ht="28.8">
       <c r="A62" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B62" s="5">
         <v>2005</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="15" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
@@ -9862,25 +10012,25 @@
     </row>
     <row r="63" spans="1:14" ht="28.8">
       <c r="A63" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B63" s="2">
         <v>2005</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="12" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
@@ -9892,25 +10042,25 @@
     </row>
     <row r="64" spans="1:14" ht="28.8">
       <c r="A64" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B64" s="5">
         <v>2006</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="15" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="16" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="15" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
@@ -9922,25 +10072,25 @@
     </row>
     <row r="65" spans="1:14" ht="28.8">
       <c r="A65" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B65" s="2">
         <v>2006</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="12" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="12" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
@@ -9952,25 +10102,25 @@
     </row>
     <row r="66" spans="1:14" ht="28.8">
       <c r="A66" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B66" s="5">
         <v>2006</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="16" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="12" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
@@ -9982,25 +10132,25 @@
     </row>
     <row r="67" spans="1:14" ht="28.8">
       <c r="A67" s="5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B67" s="2">
         <v>2006</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="12" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G67" s="11"/>
       <c r="H67" s="12" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
@@ -10012,28 +10162,28 @@
     </row>
     <row r="68" spans="1:14" ht="28.8">
       <c r="A68" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B68" s="2">
         <v>2006</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="12" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
@@ -10044,28 +10194,28 @@
     </row>
     <row r="69" spans="1:14" ht="41.4">
       <c r="A69" s="5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B69" s="5">
         <v>2007</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="16" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G69" s="15"/>
       <c r="H69" s="16" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
@@ -10076,28 +10226,28 @@
     </row>
     <row r="70" spans="1:14" ht="41.4">
       <c r="A70" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B70" s="2">
         <v>2007</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G70" s="11"/>
       <c r="H70" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J70" s="17" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
@@ -10108,25 +10258,25 @@
     </row>
     <row r="71" spans="1:14" ht="28.8">
       <c r="A71" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B71" s="5">
         <v>2007</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="16" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
@@ -10138,28 +10288,28 @@
     </row>
     <row r="72" spans="1:14" ht="28.8">
       <c r="A72" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B72" s="2">
         <v>2008</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="12" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="12" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J72" s="17" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
@@ -10170,25 +10320,25 @@
     </row>
     <row r="73" spans="1:14" ht="41.4">
       <c r="A73" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B73" s="5">
         <v>2010</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="16" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G73" s="15"/>
       <c r="H73" s="16" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
@@ -10200,25 +10350,25 @@
     </row>
     <row r="74" spans="1:14" ht="41.4">
       <c r="A74" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B74" s="2">
         <v>2010</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="12" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="12" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
@@ -10230,28 +10380,28 @@
     </row>
     <row r="75" spans="1:14" ht="28.8">
       <c r="A75" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B75" s="5">
         <v>2011</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="16" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G75" s="15"/>
       <c r="H75" s="15" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
@@ -10262,28 +10412,28 @@
     </row>
     <row r="76" spans="1:14" ht="55.2">
       <c r="A76" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B76" s="2">
         <v>2012</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="12" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="G76" s="11"/>
       <c r="H76" s="11" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J76" s="17" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
@@ -10294,22 +10444,22 @@
     </row>
     <row r="77" spans="1:14" ht="41.4">
       <c r="A77" s="5" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B77" s="5">
         <v>2013</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="16" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G77" s="15"/>
       <c r="H77" s="16" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -10322,28 +10472,28 @@
     </row>
     <row r="78" spans="1:14" ht="28.8">
       <c r="A78" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B78" s="2">
         <v>2014</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="12" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -10354,25 +10504,25 @@
     </row>
     <row r="79" spans="1:14" ht="41.4">
       <c r="A79" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B79" s="5">
         <v>2015</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="16" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="G79" s="15"/>
       <c r="H79" s="16" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
@@ -10384,28 +10534,28 @@
     </row>
     <row r="80" spans="1:14" ht="41.4">
       <c r="A80" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B80" s="2">
         <v>2015</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="12" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="12" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="J80" s="17" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
@@ -10416,25 +10566,25 @@
     </row>
     <row r="81" spans="1:14" ht="28.8">
       <c r="A81" s="5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B81" s="5">
         <v>2015</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="16" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
@@ -10446,25 +10596,25 @@
     </row>
     <row r="82" spans="1:14" ht="28.8">
       <c r="A82" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B82" s="2">
         <v>2017</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="12" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G82" s="11"/>
       <c r="H82" s="12" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -10476,22 +10626,22 @@
     </row>
     <row r="83" spans="1:14" ht="41.4">
       <c r="A83" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B83" s="5">
         <v>2017</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="16" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="16" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -10503,88 +10653,88 @@
     </row>
     <row r="84" spans="1:14" ht="41.4">
       <c r="A84" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B84" s="2">
         <v>2017</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="12" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="12" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="35" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="28.8">
       <c r="A85" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B85" s="5">
         <v>2017</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="16" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="16" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" s="35" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="41.4">
       <c r="A86" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B86" s="2">
         <v>2017</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="12" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G86" s="11"/>
       <c r="H86" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -10595,60 +10745,60 @@
     </row>
     <row r="87" spans="1:14" ht="28.8">
       <c r="A87" s="5" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="16" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="16" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
       <c r="N87" s="35" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="41.4">
       <c r="A88" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B88" s="2">
         <v>2018</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="E88" s="11"/>
       <c r="F88" s="12" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="G88" s="11"/>
       <c r="H88" s="11" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
@@ -10659,28 +10809,28 @@
     </row>
     <row r="89" spans="1:14" ht="28.8">
       <c r="A89" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="11" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="16" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
@@ -10691,22 +10841,22 @@
     </row>
     <row r="90" spans="1:14" ht="41.4">
       <c r="A90" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B90" s="2">
         <v>2020</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="12" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
@@ -10719,28 +10869,28 @@
     </row>
     <row r="91" spans="1:14" ht="28.8">
       <c r="A91" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B91" s="5">
         <v>2020</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="16" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="16" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
@@ -10751,677 +10901,677 @@
     </row>
     <row r="92" spans="1:14" ht="28.8">
       <c r="A92" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B92" s="2">
         <v>2021</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="11" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="12" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G92" s="11"/>
       <c r="H92" s="12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="93" spans="1:14" ht="28.8">
       <c r="A93" s="33" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="E93" s="11"/>
       <c r="F93" s="12" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G93" s="11"/>
       <c r="H93" s="12" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
       <c r="N93" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="94" spans="1:14" ht="41.4">
       <c r="A94" s="34" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B94" s="5">
         <v>2021</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E94" s="15"/>
       <c r="F94" s="16" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="95" spans="1:14" ht="41.4">
       <c r="A95" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B95" s="5">
         <v>2022</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="15" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="16" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="16" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="55.2">
       <c r="A96" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B96" s="2">
         <v>2022</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E96" s="11"/>
       <c r="F96" s="12" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="G96" s="11"/>
       <c r="H96" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="I96" s="31" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
       <c r="N96" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="97" spans="1:14" ht="41.4">
       <c r="A97" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B97" s="5">
         <v>2023</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="16" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="41.4">
       <c r="A98" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B98" s="2">
         <v>2023</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E98" s="11"/>
       <c r="F98" s="12" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="G98" s="11"/>
       <c r="H98" s="12" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="41.4">
       <c r="A99" s="5" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B99" s="5">
         <v>2023</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="15" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="12" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="G99" s="15"/>
       <c r="H99" s="12" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="41.4">
       <c r="A100" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B100" s="2">
         <v>2024</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="E100" s="11"/>
       <c r="F100" s="12" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G100" s="11"/>
       <c r="H100" s="11" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="28.8">
       <c r="A101" s="5" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B101" s="5">
         <v>2024</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="15" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="16" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G101" s="15"/>
       <c r="H101" s="16" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="28.8">
       <c r="A102" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B102" s="2">
         <v>2024</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E102" s="11"/>
       <c r="F102" s="12" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="G102" s="11"/>
       <c r="H102" s="12" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="28.8">
       <c r="A103" s="5" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B103" s="5">
         <v>2024</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="15" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="16" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="G103" s="15"/>
       <c r="H103" s="15" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J103" s="17" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="104" spans="1:14" ht="28.8">
       <c r="A104" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B104" s="2">
         <v>2024</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E104" s="11"/>
       <c r="F104" s="12" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="G104" s="11"/>
       <c r="H104" s="12" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J104" s="17" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="28.8">
       <c r="A105" s="5" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B105" s="5">
         <v>2024</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="16" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G105" s="15"/>
       <c r="H105" s="16" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="J105" s="17" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="41.4">
       <c r="A106" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B106" s="2">
         <v>2024</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E106" s="11"/>
       <c r="F106" s="12" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="G106" s="11"/>
       <c r="H106" s="12" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
       <c r="N106" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="28.8">
       <c r="A107" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B107" s="5">
         <v>2024</v>
       </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="16" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="G107" s="15"/>
       <c r="H107" s="16" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
       <c r="N107" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="41.4">
       <c r="A108" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B108" s="2">
         <v>2024</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="12" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="G108" s="11"/>
       <c r="H108" s="12" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
       <c r="N108" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="28.8">
       <c r="A109" s="5" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B109" s="5">
         <v>2025</v>
       </c>
       <c r="C109" s="15"/>
       <c r="D109" s="15" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="16" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G109" s="15"/>
       <c r="H109" s="16" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="28.8">
       <c r="A110" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B110" s="2">
         <v>2025</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="E110" s="11"/>
       <c r="F110" s="12" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="12" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="J110" s="17" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
       <c r="N110" s="5" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="28.8">
       <c r="A111" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B111" s="2">
         <v>2025</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="12" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="G111" s="11"/>
       <c r="H111" s="12" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
       <c r="N111" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="41.4">
       <c r="A112" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B112" s="5">
         <v>2025</v>
       </c>
       <c r="C112" s="15"/>
       <c r="D112" s="15" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E112" s="15"/>
       <c r="F112" s="16" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G112" s="15"/>
       <c r="H112" s="15" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
       <c r="N112" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="28.8">
       <c r="A113" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B113" s="5">
         <v>2026</v>
       </c>
       <c r="C113" s="15"/>
       <c r="D113" s="15" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="16" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G113" s="15"/>
       <c r="H113" s="16" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
@@ -11433,148 +11583,148 @@
     </row>
     <row r="114" spans="1:14" ht="41.4">
       <c r="A114" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B114" s="2">
         <v>2026</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="E114" s="11"/>
       <c r="F114" s="12" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="G114" s="11"/>
       <c r="H114" s="11" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
       <c r="N114" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="41.4">
       <c r="A115" s="5" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B115" s="5">
         <v>2026</v>
       </c>
       <c r="C115" s="15"/>
       <c r="D115" s="15" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="16" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="16" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="28.8">
       <c r="A116" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B116" s="2">
         <v>2026</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E116" s="11"/>
       <c r="F116" s="12" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="G116" s="11"/>
       <c r="H116" s="12" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
       <c r="N116" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="41.4">
       <c r="A117" s="5" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C117" s="15"/>
       <c r="D117" s="15" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="16" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
       <c r="N117" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="118" spans="1:14" ht="55.2">
       <c r="A118" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E118" s="11"/>
       <c r="F118" s="12" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="G118" s="11"/>
       <c r="H118" s="12" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="I118" s="17"/>
       <c r="J118" s="17"/>
@@ -11582,45 +11732,45 @@
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
       <c r="N118" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="82.8">
       <c r="A119" s="5" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="C119" s="15"/>
       <c r="D119" s="15" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="16" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="G119" s="15"/>
       <c r="H119" s="54" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="I119" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="J119" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="L119" s="17" t="s">
         <v>793</v>
       </c>
-      <c r="J119" s="17" t="s">
+      <c r="M119" s="17" t="s">
         <v>794</v>
       </c>
-      <c r="K119" s="17" t="s">
-        <v>795</v>
-      </c>
-      <c r="L119" s="17" t="s">
-        <v>796</v>
-      </c>
-      <c r="M119" s="17" t="s">
-        <v>797</v>
-      </c>
       <c r="N119" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11783,9 +11933,9 @@
     <col min="3" max="3" width="101.88671875" customWidth="1"/>
     <col min="4" max="4" width="128.109375" customWidth="1"/>
     <col min="5" max="5" width="77.88671875" customWidth="1"/>
-    <col min="6" max="6" width="110.44140625" customWidth="1"/>
+    <col min="6" max="6" width="71.109375" customWidth="1"/>
     <col min="7" max="7" width="77.88671875" customWidth="1"/>
-    <col min="8" max="8" width="110.44140625" customWidth="1"/>
+    <col min="8" max="8" width="70.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.1" customHeight="1">
@@ -11819,103 +11969,103 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>798</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>956</v>
-      </c>
-      <c r="G2" s="55" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24.75" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B3" s="5">
         <v>1952</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>803</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>804</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>805</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B4" s="2">
         <v>1957</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>812</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B5" s="5">
         <v>1959</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>818</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1">
@@ -11926,22 +12076,22 @@
         <v>1960</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>825</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1">
@@ -11952,22 +12102,22 @@
         <v>1978</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>831</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.75" customHeight="1">
@@ -11978,22 +12128,22 @@
         <v>1979</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>979</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>836</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>986</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.75" customHeight="1">
@@ -12004,22 +12154,22 @@
         <v>1984</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>841</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>843</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.75" customHeight="1">
@@ -12030,48 +12180,48 @@
         <v>1988</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="24.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B11" s="5">
         <v>1989</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>848</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>850</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1">
@@ -12082,74 +12232,74 @@
         <v>1990</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>856</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B13" s="5">
         <v>1997</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>861</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>862</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>864</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B14" s="2">
         <v>1999</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>870</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.75" customHeight="1">
@@ -12160,48 +12310,48 @@
         <v>2000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>875</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>876</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>877</v>
+        <v>872</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>1031</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>879</v>
+        <v>873</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.75" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>954</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>880</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>883</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>961</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="36.75" customHeight="1">
@@ -12209,129 +12359,129 @@
         <v>195</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="H17" s="52" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="B18" s="2">
         <v>2009</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="B19" s="5">
         <v>2012</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>907</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="B21" s="5">
         <v>2023</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
@@ -12424,23 +12574,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文件" ma:contentTypeID="0x0101005EC3A37483B7B547A940034302017F33" ma:contentTypeVersion="10" ma:contentTypeDescription="建立新的文件。" ma:contentTypeScope="" ma:versionID="93fcf810e015f48fca49c23ac2fc7a57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c0936b0b-42c4-462d-8635-df8965f1a9bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39a2b522396ecdd984e75ede5b30ab94" ns3:_="">
     <xsd:import namespace="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
@@ -12622,25 +12755,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c0936b0b-42c4-462d-8635-df8965f1a9bd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1DA92D2-9CB9-46E6-B1CE-0CD1A50A6A3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12656,4 +12788,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93501E32-1D12-4703-A0F1-F2438CAEE261}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80C042D-11D4-4B82-A524-EE8E0C828FA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0936b0b-42c4-462d-8635-df8965f1a9bd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>